--- a/public/blog/seo-report-template/geotoolbox-seo-report-template.xlsx
+++ b/public/blog/seo-report-template/geotoolbox-seo-report-template.xlsx
@@ -158,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -187,6 +187,8 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -754,11 +756,11 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Paste your top queries. The sheet checks each one against the brand terms above (wildcard characters are escaped, so a term is matched as typed) and totals clicks. Take total non-branded clicks for the scorecard straight from Search Console (query filter that excludes your brand terms).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
+          <t>Paste your top queries. The sheet checks each one against the brand terms above (wildcard characters are escaped, so a term is matched as typed) and totals clicks. Take total non-branded clicks for the scorecard straight from Search Console (query filter that excludes your brand terms). Two flags help you choose what to work on: Opportunity marks non-branded queries at position 4 to 5 (Almost top 3) or 11 to 15 (Page 2 push), and CTR check marks queries whose CTR is under half of the expected CTR for their position. The expected-CTR column is a set of starting values you should replace with your own site's curve, and a low CTR can mean a weak title or an answer box taking the click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Tab 3 Landing Pages</t>
@@ -766,7 +768,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Top organic landing pages with sessions, key events, clicks, impressions and one line on what changed.</t>
+          <t>Top organic landing pages with sessions, key events, clicks, impressions and one line on what changed. A flag marks pages that lost more than the set share of last month's clicks (default 20%), as a prompt to look, not a verdict.</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1450,6 +1452,10 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1489,6 +1495,34 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Flag settings</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>&lt;- minimum impressions before a query is flagged</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>&lt;- flag when CTR is below this share of the expected CTR for its position</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Expected CTR by position (starting values, replace with your own site's curve)</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
@@ -1535,6 +1569,26 @@
           <t>Clicks change</t>
         </is>
       </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>Opportunity</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>CTR check</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>Expected CTR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -1561,7 +1615,7 @@
         <v/>
       </c>
       <c r="G8" s="8" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>25</v>
@@ -1570,6 +1624,20 @@
         <f>IFERROR((C8-H8)/H8,"")</f>
         <v/>
       </c>
+      <c r="J8" s="10">
+        <f>IF(OR(B8&lt;&gt;"Non-branded",NOT(ISNUMBER(D8)),NOT(ISNUMBER(G8))),"",IF(D8&lt;$B$6,"",IF(AND(ROUND(G8,0)&gt;=4,ROUND(G8,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G8,0)&gt;=11,ROUND(G8,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K8" s="10">
+        <f>IF(OR(B8&lt;&gt;"Non-branded",NOT(ISNUMBER(C8)),NOT(ISNUMBER(D8)),NOT(ISNUMBER(G8))),"",IF(D8&lt;$B$6,"",IF(OR(ROUND(G8,0)&lt;1,ROUND(G8,0)&gt;20),"",IF(C8/D8&lt;$F$6*VLOOKUP(ROUND(G8,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="23" t="n">
+        <v>0.298</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -1605,6 +1673,20 @@
         <f>IFERROR((C9-H9)/H9,"")</f>
         <v/>
       </c>
+      <c r="J9" s="10">
+        <f>IF(OR(B9&lt;&gt;"Non-branded",NOT(ISNUMBER(D9)),NOT(ISNUMBER(G9))),"",IF(D9&lt;$B$6,"",IF(AND(ROUND(G9,0)&gt;=4,ROUND(G9,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G9,0)&gt;=11,ROUND(G9,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K9" s="10">
+        <f>IF(OR(B9&lt;&gt;"Non-branded",NOT(ISNUMBER(C9)),NOT(ISNUMBER(D9)),NOT(ISNUMBER(G9))),"",IF(D9&lt;$B$6,"",IF(OR(ROUND(G9,0)&lt;1,ROUND(G9,0)&gt;20),"",IF(C9/D9&lt;$F$6*VLOOKUP(ROUND(G9,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="23" t="n">
+        <v>0.153</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -1631,7 +1713,7 @@
         <v/>
       </c>
       <c r="G10" s="8" t="n">
-        <v>9.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>10</v>
@@ -1640,15 +1722,37 @@
         <f>IFERROR((C10-H10)/H10,"")</f>
         <v/>
       </c>
+      <c r="J10" s="10">
+        <f>IF(OR(B10&lt;&gt;"Non-branded",NOT(ISNUMBER(D10)),NOT(ISNUMBER(G10))),"",IF(D10&lt;$B$6,"",IF(AND(ROUND(G10,0)&gt;=4,ROUND(G10,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G10,0)&gt;=11,ROUND(G10,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K10" s="10">
+        <f>IF(OR(B10&lt;&gt;"Non-branded",NOT(ISNUMBER(C10)),NOT(ISNUMBER(D10)),NOT(ISNUMBER(G10))),"",IF(D10&lt;$B$6,"",IF(OR(ROUND(G10,0)&lt;1,ROUND(G10,0)&gt;20),"",IF(C10/D10&lt;$F$6*VLOOKUP(ROUND(G10,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" s="23" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>EXAMPLE seo reporting tool</t>
+        </is>
+      </c>
       <c r="B11" s="10">
         <f>IF(A11="","",IF(OR(AND('Start Here'!$B$10&lt;&gt;"",ISNUMBER(SEARCH('Start Here'!$B$10,A11))),AND('Start Here'!$C$10&lt;&gt;"",ISNUMBER(SEARCH('Start Here'!$C$10,A11))),AND('Start Here'!$D$10&lt;&gt;"",ISNUMBER(SEARCH('Start Here'!$D$10,A11))),AND('Start Here'!$E$10&lt;&gt;"",ISNUMBER(SEARCH('Start Here'!$E$10,A11))),AND('Start Here'!$F$10&lt;&gt;"",ISNUMBER(SEARCH('Start Here'!$F$10,A11)))),"Branded","Non-branded"))</f>
         <v/>
       </c>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
+      <c r="C11" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>500</v>
+      </c>
       <c r="E11" s="16">
         <f>IFERROR(C11/D11,"")</f>
         <v/>
@@ -1657,11 +1761,29 @@
         <f>IF(B11="Non-branded",C11,0)</f>
         <v/>
       </c>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
+      <c r="G11" s="8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="I11" s="16">
         <f>IFERROR((C11-H11)/H11,"")</f>
         <v/>
+      </c>
+      <c r="J11" s="10">
+        <f>IF(OR(B11&lt;&gt;"Non-branded",NOT(ISNUMBER(D11)),NOT(ISNUMBER(G11))),"",IF(D11&lt;$B$6,"",IF(AND(ROUND(G11,0)&gt;=4,ROUND(G11,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G11,0)&gt;=11,ROUND(G11,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K11" s="10">
+        <f>IF(OR(B11&lt;&gt;"Non-branded",NOT(ISNUMBER(C11)),NOT(ISNUMBER(D11)),NOT(ISNUMBER(G11))),"",IF(D11&lt;$B$6,"",IF(OR(ROUND(G11,0)&lt;1,ROUND(G11,0)&gt;20),"",IF(C11/D11&lt;$F$6*VLOOKUP(ROUND(G11,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" s="23" t="n">
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1686,6 +1808,20 @@
         <f>IFERROR((C12-H12)/H12,"")</f>
         <v/>
       </c>
+      <c r="J12" s="10">
+        <f>IF(OR(B12&lt;&gt;"Non-branded",NOT(ISNUMBER(D12)),NOT(ISNUMBER(G12))),"",IF(D12&lt;$B$6,"",IF(AND(ROUND(G12,0)&gt;=4,ROUND(G12,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G12,0)&gt;=11,ROUND(G12,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K12" s="10">
+        <f>IF(OR(B12&lt;&gt;"Non-branded",NOT(ISNUMBER(C12)),NOT(ISNUMBER(D12)),NOT(ISNUMBER(G12))),"",IF(D12&lt;$B$6,"",IF(OR(ROUND(G12,0)&lt;1,ROUND(G12,0)&gt;20),"",IF(C12/D12&lt;$F$6*VLOOKUP(ROUND(G12,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" s="23" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n"/>
@@ -1709,6 +1845,20 @@
         <f>IFERROR((C13-H13)/H13,"")</f>
         <v/>
       </c>
+      <c r="J13" s="10">
+        <f>IF(OR(B13&lt;&gt;"Non-branded",NOT(ISNUMBER(D13)),NOT(ISNUMBER(G13))),"",IF(D13&lt;$B$6,"",IF(AND(ROUND(G13,0)&gt;=4,ROUND(G13,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G13,0)&gt;=11,ROUND(G13,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K13" s="10">
+        <f>IF(OR(B13&lt;&gt;"Non-branded",NOT(ISNUMBER(C13)),NOT(ISNUMBER(D13)),NOT(ISNUMBER(G13))),"",IF(D13&lt;$B$6,"",IF(OR(ROUND(G13,0)&lt;1,ROUND(G13,0)&gt;20),"",IF(C13/D13&lt;$F$6*VLOOKUP(ROUND(G13,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M13" t="n">
+        <v>6</v>
+      </c>
+      <c r="N13" s="23" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n"/>
@@ -1732,6 +1882,20 @@
         <f>IFERROR((C14-H14)/H14,"")</f>
         <v/>
       </c>
+      <c r="J14" s="10">
+        <f>IF(OR(B14&lt;&gt;"Non-branded",NOT(ISNUMBER(D14)),NOT(ISNUMBER(G14))),"",IF(D14&lt;$B$6,"",IF(AND(ROUND(G14,0)&gt;=4,ROUND(G14,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G14,0)&gt;=11,ROUND(G14,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K14" s="10">
+        <f>IF(OR(B14&lt;&gt;"Non-branded",NOT(ISNUMBER(C14)),NOT(ISNUMBER(D14)),NOT(ISNUMBER(G14))),"",IF(D14&lt;$B$6,"",IF(OR(ROUND(G14,0)&lt;1,ROUND(G14,0)&gt;20),"",IF(C14/D14&lt;$F$6*VLOOKUP(ROUND(G14,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" s="23" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n"/>
@@ -1755,6 +1919,20 @@
         <f>IFERROR((C15-H15)/H15,"")</f>
         <v/>
       </c>
+      <c r="J15" s="10">
+        <f>IF(OR(B15&lt;&gt;"Non-branded",NOT(ISNUMBER(D15)),NOT(ISNUMBER(G15))),"",IF(D15&lt;$B$6,"",IF(AND(ROUND(G15,0)&gt;=4,ROUND(G15,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G15,0)&gt;=11,ROUND(G15,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K15" s="10">
+        <f>IF(OR(B15&lt;&gt;"Non-branded",NOT(ISNUMBER(C15)),NOT(ISNUMBER(D15)),NOT(ISNUMBER(G15))),"",IF(D15&lt;$B$6,"",IF(OR(ROUND(G15,0)&lt;1,ROUND(G15,0)&gt;20),"",IF(C15/D15&lt;$F$6*VLOOKUP(ROUND(G15,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M15" t="n">
+        <v>8</v>
+      </c>
+      <c r="N15" s="23" t="n">
+        <v>0.024</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n"/>
@@ -1778,6 +1956,20 @@
         <f>IFERROR((C16-H16)/H16,"")</f>
         <v/>
       </c>
+      <c r="J16" s="10">
+        <f>IF(OR(B16&lt;&gt;"Non-branded",NOT(ISNUMBER(D16)),NOT(ISNUMBER(G16))),"",IF(D16&lt;$B$6,"",IF(AND(ROUND(G16,0)&gt;=4,ROUND(G16,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G16,0)&gt;=11,ROUND(G16,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K16" s="10">
+        <f>IF(OR(B16&lt;&gt;"Non-branded",NOT(ISNUMBER(C16)),NOT(ISNUMBER(D16)),NOT(ISNUMBER(G16))),"",IF(D16&lt;$B$6,"",IF(OR(ROUND(G16,0)&lt;1,ROUND(G16,0)&gt;20),"",IF(C16/D16&lt;$F$6*VLOOKUP(ROUND(G16,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M16" t="n">
+        <v>9</v>
+      </c>
+      <c r="N16" s="23" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n"/>
@@ -1801,6 +1993,20 @@
         <f>IFERROR((C17-H17)/H17,"")</f>
         <v/>
       </c>
+      <c r="J17" s="10">
+        <f>IF(OR(B17&lt;&gt;"Non-branded",NOT(ISNUMBER(D17)),NOT(ISNUMBER(G17))),"",IF(D17&lt;$B$6,"",IF(AND(ROUND(G17,0)&gt;=4,ROUND(G17,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G17,0)&gt;=11,ROUND(G17,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K17" s="10">
+        <f>IF(OR(B17&lt;&gt;"Non-branded",NOT(ISNUMBER(C17)),NOT(ISNUMBER(D17)),NOT(ISNUMBER(G17))),"",IF(D17&lt;$B$6,"",IF(OR(ROUND(G17,0)&lt;1,ROUND(G17,0)&gt;20),"",IF(C17/D17&lt;$F$6*VLOOKUP(ROUND(G17,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M17" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" s="23" t="n">
+        <v>0.017</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n"/>
@@ -1824,6 +2030,20 @@
         <f>IFERROR((C18-H18)/H18,"")</f>
         <v/>
       </c>
+      <c r="J18" s="10">
+        <f>IF(OR(B18&lt;&gt;"Non-branded",NOT(ISNUMBER(D18)),NOT(ISNUMBER(G18))),"",IF(D18&lt;$B$6,"",IF(AND(ROUND(G18,0)&gt;=4,ROUND(G18,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G18,0)&gt;=11,ROUND(G18,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K18" s="10">
+        <f>IF(OR(B18&lt;&gt;"Non-branded",NOT(ISNUMBER(C18)),NOT(ISNUMBER(D18)),NOT(ISNUMBER(G18))),"",IF(D18&lt;$B$6,"",IF(OR(ROUND(G18,0)&lt;1,ROUND(G18,0)&gt;20),"",IF(C18/D18&lt;$F$6*VLOOKUP(ROUND(G18,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M18" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" s="23" t="n">
+        <v>0.014</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n"/>
@@ -1847,6 +2067,20 @@
         <f>IFERROR((C19-H19)/H19,"")</f>
         <v/>
       </c>
+      <c r="J19" s="10">
+        <f>IF(OR(B19&lt;&gt;"Non-branded",NOT(ISNUMBER(D19)),NOT(ISNUMBER(G19))),"",IF(D19&lt;$B$6,"",IF(AND(ROUND(G19,0)&gt;=4,ROUND(G19,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G19,0)&gt;=11,ROUND(G19,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K19" s="10">
+        <f>IF(OR(B19&lt;&gt;"Non-branded",NOT(ISNUMBER(C19)),NOT(ISNUMBER(D19)),NOT(ISNUMBER(G19))),"",IF(D19&lt;$B$6,"",IF(OR(ROUND(G19,0)&lt;1,ROUND(G19,0)&gt;20),"",IF(C19/D19&lt;$F$6*VLOOKUP(ROUND(G19,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M19" t="n">
+        <v>12</v>
+      </c>
+      <c r="N19" s="23" t="n">
+        <v>0.012</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n"/>
@@ -1870,6 +2104,20 @@
         <f>IFERROR((C20-H20)/H20,"")</f>
         <v/>
       </c>
+      <c r="J20" s="10">
+        <f>IF(OR(B20&lt;&gt;"Non-branded",NOT(ISNUMBER(D20)),NOT(ISNUMBER(G20))),"",IF(D20&lt;$B$6,"",IF(AND(ROUND(G20,0)&gt;=4,ROUND(G20,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G20,0)&gt;=11,ROUND(G20,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K20" s="10">
+        <f>IF(OR(B20&lt;&gt;"Non-branded",NOT(ISNUMBER(C20)),NOT(ISNUMBER(D20)),NOT(ISNUMBER(G20))),"",IF(D20&lt;$B$6,"",IF(OR(ROUND(G20,0)&lt;1,ROUND(G20,0)&gt;20),"",IF(C20/D20&lt;$F$6*VLOOKUP(ROUND(G20,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M20" t="n">
+        <v>13</v>
+      </c>
+      <c r="N20" s="23" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n"/>
@@ -1893,6 +2141,20 @@
         <f>IFERROR((C21-H21)/H21,"")</f>
         <v/>
       </c>
+      <c r="J21" s="10">
+        <f>IF(OR(B21&lt;&gt;"Non-branded",NOT(ISNUMBER(D21)),NOT(ISNUMBER(G21))),"",IF(D21&lt;$B$6,"",IF(AND(ROUND(G21,0)&gt;=4,ROUND(G21,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G21,0)&gt;=11,ROUND(G21,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K21" s="10">
+        <f>IF(OR(B21&lt;&gt;"Non-branded",NOT(ISNUMBER(C21)),NOT(ISNUMBER(D21)),NOT(ISNUMBER(G21))),"",IF(D21&lt;$B$6,"",IF(OR(ROUND(G21,0)&lt;1,ROUND(G21,0)&gt;20),"",IF(C21/D21&lt;$F$6*VLOOKUP(ROUND(G21,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M21" t="n">
+        <v>14</v>
+      </c>
+      <c r="N21" s="23" t="n">
+        <v>0.008999999999999999</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n"/>
@@ -1916,6 +2178,28 @@
         <f>IFERROR((C22-H22)/H22,"")</f>
         <v/>
       </c>
+      <c r="J22" s="10">
+        <f>IF(OR(B22&lt;&gt;"Non-branded",NOT(ISNUMBER(D22)),NOT(ISNUMBER(G22))),"",IF(D22&lt;$B$6,"",IF(AND(ROUND(G22,0)&gt;=4,ROUND(G22,0)&lt;=5),"Almost top 3",IF(AND(ROUND(G22,0)&gt;=11,ROUND(G22,0)&lt;=15),"Page 2 push",""))))</f>
+        <v/>
+      </c>
+      <c r="K22" s="10">
+        <f>IF(OR(B22&lt;&gt;"Non-branded",NOT(ISNUMBER(C22)),NOT(ISNUMBER(D22)),NOT(ISNUMBER(G22))),"",IF(D22&lt;$B$6,"",IF(OR(ROUND(G22,0)&lt;1,ROUND(G22,0)&gt;20),"",IF(C22/D22&lt;$F$6*VLOOKUP(ROUND(G22,0),$M$8:$N$27,2,FALSE),"Low CTR for position",""))))</f>
+        <v/>
+      </c>
+      <c r="M22" t="n">
+        <v>15</v>
+      </c>
+      <c r="N22" s="23" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="M23" t="n">
+        <v>16</v>
+      </c>
+      <c r="N23" s="23" t="n">
+        <v>0.007</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1931,7 +2215,7 @@
         <f>SUM(D8:D22)</f>
         <v/>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="24">
         <f>IFERROR(C24/D24,"")</f>
         <v/>
       </c>
@@ -1939,6 +2223,12 @@
         <f>SUM(F8:F22)</f>
         <v/>
       </c>
+      <c r="M24" t="n">
+        <v>17</v>
+      </c>
+      <c r="N24" s="23" t="n">
+        <v>0.006</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1950,6 +2240,12 @@
         <f>SUMIF(B8:B22,"Branded",C8:C22)</f>
         <v/>
       </c>
+      <c r="M25" t="n">
+        <v>18</v>
+      </c>
+      <c r="N25" s="23" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1957,14 +2253,30 @@
           <t>Non-branded share of listed clicks</t>
         </is>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="24">
         <f>IFERROR(F24/C24,"")</f>
         <v/>
       </c>
+      <c r="M26" t="n">
+        <v>19</v>
+      </c>
+      <c r="N26" s="23" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="M27" t="n">
+        <v>20</v>
+      </c>
+      <c r="N27" s="23" t="n">
+        <v>0.004</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="C6:E6"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1977,7 +2289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2300,9 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2004,6 +2319,21 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Flag pages losing more than</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>&lt;- share of last month's clicks that triggers the Flag column</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -2045,6 +2375,21 @@
           <t>What changed</t>
         </is>
       </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Last month clicks</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Clicks change</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -2072,10 +2417,21 @@
         <f>IF(OR(E5="",F5=""),"",IFERROR(E5/F5,""))</f>
         <v/>
       </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>EXAMPLE: refreshed intro and added FAQ on the 12th</t>
-        </is>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>EXAMPLE: refreshed intro on the 12th; clicks fell after an answer box appeared for the main query</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="J5" s="16">
+        <f>IF(OR(E5="",I5="",I5=0),"",(E5-I5)/I5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="10">
+        <f>IF(J5="","",IF(J5&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -2093,6 +2449,15 @@
         <v/>
       </c>
       <c r="H6" s="17" t="n"/>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="16">
+        <f>IF(OR(E6="",I6="",I6=0),"",(E6-I6)/I6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="10">
+        <f>IF(J6="","",IF(J6&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n"/>
@@ -2109,6 +2474,15 @@
         <v/>
       </c>
       <c r="H7" s="17" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="16">
+        <f>IF(OR(E7="",I7="",I7=0),"",(E7-I7)/I7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="10">
+        <f>IF(J7="","",IF(J7&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n"/>
@@ -2125,6 +2499,15 @@
         <v/>
       </c>
       <c r="H8" s="17" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="16">
+        <f>IF(OR(E8="",I8="",I8=0),"",(E8-I8)/I8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="10">
+        <f>IF(J8="","",IF(J8&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n"/>
@@ -2141,6 +2524,15 @@
         <v/>
       </c>
       <c r="H9" s="17" t="n"/>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="16">
+        <f>IF(OR(E9="",I9="",I9=0),"",(E9-I9)/I9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="10">
+        <f>IF(J9="","",IF(J9&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n"/>
@@ -2157,6 +2549,15 @@
         <v/>
       </c>
       <c r="H10" s="17" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="16">
+        <f>IF(OR(E10="",I10="",I10=0),"",(E10-I10)/I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="10">
+        <f>IF(J10="","",IF(J10&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n"/>
@@ -2173,6 +2574,15 @@
         <v/>
       </c>
       <c r="H11" s="17" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="16">
+        <f>IF(OR(E11="",I11="",I11=0),"",(E11-I11)/I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="10">
+        <f>IF(J11="","",IF(J11&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n"/>
@@ -2189,6 +2599,15 @@
         <v/>
       </c>
       <c r="H12" s="17" t="n"/>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="16">
+        <f>IF(OR(E12="",I12="",I12=0),"",(E12-I12)/I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="10">
+        <f>IF(J12="","",IF(J12&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n"/>
@@ -2205,6 +2624,15 @@
         <v/>
       </c>
       <c r="H13" s="17" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="16">
+        <f>IF(OR(E13="",I13="",I13=0),"",(E13-I13)/I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="10">
+        <f>IF(J13="","",IF(J13&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n"/>
@@ -2221,6 +2649,15 @@
         <v/>
       </c>
       <c r="H14" s="17" t="n"/>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="16">
+        <f>IF(OR(E14="",I14="",I14=0),"",(E14-I14)/I14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="10">
+        <f>IF(J14="","",IF(J14&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n"/>
@@ -2237,6 +2674,15 @@
         <v/>
       </c>
       <c r="H15" s="17" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="16">
+        <f>IF(OR(E15="",I15="",I15=0),"",(E15-I15)/I15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="10">
+        <f>IF(J15="","",IF(J15&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n"/>
@@ -2253,8 +2699,20 @@
         <v/>
       </c>
       <c r="H16" s="17" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="16">
+        <f>IF(OR(E16="",I16="",I16=0),"",(E16-I16)/I16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="10">
+        <f>IF(J16="","",IF(J16&lt;-$B$3,"Losing clicks",""))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C3:H3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3091,32 +3549,32 @@
       </c>
     </row>
     <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Search Console: impressions in AI Overviews and AI Mode</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Search Console &gt; Generative AI performance report (Search). Discover has a separate report.</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="25" t="n">
         <v>12000</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="25" t="n">
         <v>9500</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="27">
         <f>IF(OR(C6="",D6=""),"n/a",IFERROR((C6-D6)/D6,"n/a"))</f>
         <v/>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>Your URLs were shown in Google's generative AI features</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>Clicks or triggering queries: Google's help page describes impressions by page, country, device and date only.</t>
         </is>
@@ -3130,64 +3588,64 @@
       </c>
     </row>
     <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>Bing: average cited pages per day</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Bing Webmaster Tools &gt; AI Performance</t>
         </is>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="27">
         <f>IF(OR(C8="",D8=""),"n/a",IFERROR((C8-D8)/D8,"n/a"))</f>
         <v/>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>Copilot, AI summaries in Bing and select partners cited your pages</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t>Rankings, authority or the cause of a change. Bing says the data is a sample and trends cannot be tied to one cause.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>Bing: total citations</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Bing Webmaster Tools &gt; AI Performance</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="27">
         <f>IF(OR(C9="",D9=""),"n/a",IFERROR((C9-D9)/D9,"n/a"))</f>
         <v/>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>How often pages were displayed as sources</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t>Traffic or engagement: a citation is not a visit.</t>
         </is>
@@ -3245,82 +3703,82 @@
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>AI Assistant channel: key events</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>GA4 &gt; Acquisition &gt; Traffic acquisition &gt; Session default channel group = AI Assistant</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="27">
         <f>IF(OR(C13="",D13=""),"n/a",IFERROR((C13-D13)/D13,"n/a"))</f>
         <v/>
       </c>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="24" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
     </row>
     <row r="14" ht="92" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>AI Assistant channel: sessions</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>same view</t>
         </is>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="27">
         <f>IF(OR(C14="",D14=""),"n/a",IFERROR((C14-D14)/D14,"n/a"))</f>
         <v/>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F14" s="26" t="inlineStr">
         <is>
           <t>Visitors arrived in a session GA4 placed in the AI Assistant channel</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t>Total AI exposure. The channel takes sessions whose medium is ai-assistant (set when the referrer matches Google's list of assistants) and excludes Google's AI Overviews and AI Mode. Treat it as a count of what GA4 can attribute, and note the date if Google's list changes.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>AI Assistant: key events per session</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="25">
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="27">
         <f>IF(OR(C13="",C14=""),"n/a",IFERROR(C13/C14,"n/a"))</f>
         <v/>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="27">
         <f>IF(OR(D13="",D14=""),"n/a",IFERROR(D13/D14,"n/a"))</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="28">
         <f>IF(AND(ISNUMBER(C15),ISNUMBER(D15)),(C15-D15)*100,"n/a")</f>
         <v/>
       </c>
-      <c r="F15" s="24" t="n"/>
-      <c r="G15" s="24" t="n"/>
+      <c r="F15" s="26" t="n"/>
+      <c r="G15" s="26" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3335,7 +3793,7 @@
           <t>Panel version</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
@@ -3347,7 +3805,7 @@
           <t>Change log</t>
         </is>
       </c>
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>EXAMPLE: v1 created 2026-08-01 with 20 prompts. Record every add or drop here and start a new trend line. Only rows with 1 or 0 in all three outcome columns count as runs.</t>
         </is>
@@ -3400,19 +3858,19 @@
         <f>COUNTIFS($B$34:$B$633,A23,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")</f>
         <v/>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="31">
         <f>IFERROR(SUMIFS($E$34:$E$633,$B$34:$B$633,A23,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B23,"n/a")</f>
         <v/>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A23,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B23,"n/a")</f>
         <v/>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="31">
         <f>IFERROR(SUMIFS($G$34:$G$633,$B$34:$B$633,A23,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B23,"n/a")</f>
         <v/>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A23,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/COUNTIFS($B$34:$B$633,A23,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0"),"n/a")</f>
         <v/>
       </c>
@@ -3428,19 +3886,19 @@
         <f>COUNTIFS($B$34:$B$633,A24,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")</f>
         <v/>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="31">
         <f>IFERROR(SUMIFS($E$34:$E$633,$B$34:$B$633,A24,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B24,"n/a")</f>
         <v/>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A24,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B24,"n/a")</f>
         <v/>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="31">
         <f>IFERROR(SUMIFS($G$34:$G$633,$B$34:$B$633,A24,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B24,"n/a")</f>
         <v/>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A24,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/COUNTIFS($B$34:$B$633,A24,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0"),"n/a")</f>
         <v/>
       </c>
@@ -3456,19 +3914,19 @@
         <f>COUNTIFS($B$34:$B$633,A25,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")</f>
         <v/>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="31">
         <f>IFERROR(SUMIFS($E$34:$E$633,$B$34:$B$633,A25,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B25,"n/a")</f>
         <v/>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A25,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B25,"n/a")</f>
         <v/>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="31">
         <f>IFERROR(SUMIFS($G$34:$G$633,$B$34:$B$633,A25,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B25,"n/a")</f>
         <v/>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A25,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/COUNTIFS($B$34:$B$633,A25,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0"),"n/a")</f>
         <v/>
       </c>
@@ -3484,19 +3942,19 @@
         <f>COUNTIFS($B$34:$B$633,A26,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")</f>
         <v/>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="31">
         <f>IFERROR(SUMIFS($E$34:$E$633,$B$34:$B$633,A26,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B26,"n/a")</f>
         <v/>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A26,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B26,"n/a")</f>
         <v/>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="31">
         <f>IFERROR(SUMIFS($G$34:$G$633,$B$34:$B$633,A26,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B26,"n/a")</f>
         <v/>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A26,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/COUNTIFS($B$34:$B$633,A26,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0"),"n/a")</f>
         <v/>
       </c>
@@ -3512,19 +3970,19 @@
         <f>COUNTIFS($B$34:$B$633,A27,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")</f>
         <v/>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="31">
         <f>IFERROR(SUMIFS($E$34:$E$633,$B$34:$B$633,A27,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B27,"n/a")</f>
         <v/>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A27,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B27,"n/a")</f>
         <v/>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="31">
         <f>IFERROR(SUMIFS($G$34:$G$633,$B$34:$B$633,A27,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B27,"n/a")</f>
         <v/>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A27,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/COUNTIFS($B$34:$B$633,A27,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0"),"n/a")</f>
         <v/>
       </c>
@@ -3540,26 +3998,26 @@
         <f>COUNTIFS($B$34:$B$633,A28,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")</f>
         <v/>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="31">
         <f>IFERROR(SUMIFS($E$34:$E$633,$B$34:$B$633,A28,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B28,"n/a")</f>
         <v/>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A28,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B28,"n/a")</f>
         <v/>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="31">
         <f>IFERROR(SUMIFS($G$34:$G$633,$B$34:$B$633,A28,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B28,"n/a")</f>
         <v/>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$B$34:$B$633,A28,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/COUNTIFS($B$34:$B$633,A28,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0"),"n/a")</f>
         <v/>
       </c>
       <c r="G28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>All engines (includes any run logged as Other)</t>
         </is>
@@ -3568,19 +4026,19 @@
         <f>COUNTIFS($C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")</f>
         <v/>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="31">
         <f>IFERROR(SUMIFS($E$34:$E$633,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B29,"n/a")</f>
         <v/>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B29,"n/a")</f>
         <v/>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="31">
         <f>IFERROR(SUMIFS($G$34:$G$633,$C$34:$C$633,'Start Here'!$B$5,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/B29,"n/a")</f>
         <v/>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="31">
         <f>IFERROR(SUMIFS($F$34:$F$633,$C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0")/COUNTIFS($C$34:$C$633,'Start Here'!$B$6,$E$34:$E$633,"&gt;=0",$F$34:$F$633,"&gt;=0",$G$34:$G$633,"&gt;=0"),"n/a")</f>
         <v/>
       </c>
@@ -3784,7 +4242,7 @@
     <row r="39">
       <c r="A39" s="9" t="n"/>
       <c r="B39" s="9" t="n"/>
-      <c r="C39" s="31" t="n"/>
+      <c r="C39" s="33" t="n"/>
       <c r="D39" s="9" t="n"/>
       <c r="E39" s="9" t="n"/>
       <c r="F39" s="9" t="n"/>
@@ -3793,7 +4251,7 @@
     <row r="40">
       <c r="A40" s="9" t="n"/>
       <c r="B40" s="9" t="n"/>
-      <c r="C40" s="31" t="n"/>
+      <c r="C40" s="33" t="n"/>
       <c r="D40" s="9" t="n"/>
       <c r="E40" s="9" t="n"/>
       <c r="F40" s="9" t="n"/>
@@ -3802,7 +4260,7 @@
     <row r="41">
       <c r="A41" s="9" t="n"/>
       <c r="B41" s="9" t="n"/>
-      <c r="C41" s="31" t="n"/>
+      <c r="C41" s="33" t="n"/>
       <c r="D41" s="9" t="n"/>
       <c r="E41" s="9" t="n"/>
       <c r="F41" s="9" t="n"/>
@@ -3811,7 +4269,7 @@
     <row r="42">
       <c r="A42" s="9" t="n"/>
       <c r="B42" s="9" t="n"/>
-      <c r="C42" s="31" t="n"/>
+      <c r="C42" s="33" t="n"/>
       <c r="D42" s="9" t="n"/>
       <c r="E42" s="9" t="n"/>
       <c r="F42" s="9" t="n"/>
@@ -3820,7 +4278,7 @@
     <row r="43">
       <c r="A43" s="9" t="n"/>
       <c r="B43" s="9" t="n"/>
-      <c r="C43" s="31" t="n"/>
+      <c r="C43" s="33" t="n"/>
       <c r="D43" s="9" t="n"/>
       <c r="E43" s="9" t="n"/>
       <c r="F43" s="9" t="n"/>
@@ -3829,7 +4287,7 @@
     <row r="44">
       <c r="A44" s="9" t="n"/>
       <c r="B44" s="9" t="n"/>
-      <c r="C44" s="31" t="n"/>
+      <c r="C44" s="33" t="n"/>
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="n"/>
       <c r="F44" s="9" t="n"/>
@@ -3838,7 +4296,7 @@
     <row r="45">
       <c r="A45" s="9" t="n"/>
       <c r="B45" s="9" t="n"/>
-      <c r="C45" s="31" t="n"/>
+      <c r="C45" s="33" t="n"/>
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="9" t="n"/>
@@ -3847,7 +4305,7 @@
     <row r="46">
       <c r="A46" s="9" t="n"/>
       <c r="B46" s="9" t="n"/>
-      <c r="C46" s="31" t="n"/>
+      <c r="C46" s="33" t="n"/>
       <c r="D46" s="9" t="n"/>
       <c r="E46" s="9" t="n"/>
       <c r="F46" s="9" t="n"/>
@@ -3856,7 +4314,7 @@
     <row r="47">
       <c r="A47" s="9" t="n"/>
       <c r="B47" s="9" t="n"/>
-      <c r="C47" s="31" t="n"/>
+      <c r="C47" s="33" t="n"/>
       <c r="D47" s="9" t="n"/>
       <c r="E47" s="9" t="n"/>
       <c r="F47" s="9" t="n"/>
@@ -3865,7 +4323,7 @@
     <row r="48">
       <c r="A48" s="9" t="n"/>
       <c r="B48" s="9" t="n"/>
-      <c r="C48" s="31" t="n"/>
+      <c r="C48" s="33" t="n"/>
       <c r="D48" s="9" t="n"/>
       <c r="E48" s="9" t="n"/>
       <c r="F48" s="9" t="n"/>
@@ -3874,7 +4332,7 @@
     <row r="49">
       <c r="A49" s="9" t="n"/>
       <c r="B49" s="9" t="n"/>
-      <c r="C49" s="31" t="n"/>
+      <c r="C49" s="33" t="n"/>
       <c r="D49" s="9" t="n"/>
       <c r="E49" s="9" t="n"/>
       <c r="F49" s="9" t="n"/>
@@ -3883,7 +4341,7 @@
     <row r="50">
       <c r="A50" s="9" t="n"/>
       <c r="B50" s="9" t="n"/>
-      <c r="C50" s="31" t="n"/>
+      <c r="C50" s="33" t="n"/>
       <c r="D50" s="9" t="n"/>
       <c r="E50" s="9" t="n"/>
       <c r="F50" s="9" t="n"/>
@@ -3892,7 +4350,7 @@
     <row r="51">
       <c r="A51" s="9" t="n"/>
       <c r="B51" s="9" t="n"/>
-      <c r="C51" s="31" t="n"/>
+      <c r="C51" s="33" t="n"/>
       <c r="D51" s="9" t="n"/>
       <c r="E51" s="9" t="n"/>
       <c r="F51" s="9" t="n"/>
@@ -3901,7 +4359,7 @@
     <row r="52">
       <c r="A52" s="9" t="n"/>
       <c r="B52" s="9" t="n"/>
-      <c r="C52" s="31" t="n"/>
+      <c r="C52" s="33" t="n"/>
       <c r="D52" s="9" t="n"/>
       <c r="E52" s="9" t="n"/>
       <c r="F52" s="9" t="n"/>
@@ -3910,7 +4368,7 @@
     <row r="53">
       <c r="A53" s="9" t="n"/>
       <c r="B53" s="9" t="n"/>
-      <c r="C53" s="31" t="n"/>
+      <c r="C53" s="33" t="n"/>
       <c r="D53" s="9" t="n"/>
       <c r="E53" s="9" t="n"/>
       <c r="F53" s="9" t="n"/>
@@ -3919,7 +4377,7 @@
     <row r="54">
       <c r="A54" s="9" t="n"/>
       <c r="B54" s="9" t="n"/>
-      <c r="C54" s="31" t="n"/>
+      <c r="C54" s="33" t="n"/>
       <c r="D54" s="9" t="n"/>
       <c r="E54" s="9" t="n"/>
       <c r="F54" s="9" t="n"/>
@@ -3928,7 +4386,7 @@
     <row r="55">
       <c r="A55" s="9" t="n"/>
       <c r="B55" s="9" t="n"/>
-      <c r="C55" s="31" t="n"/>
+      <c r="C55" s="33" t="n"/>
       <c r="D55" s="9" t="n"/>
       <c r="E55" s="9" t="n"/>
       <c r="F55" s="9" t="n"/>
@@ -3937,7 +4395,7 @@
     <row r="56">
       <c r="A56" s="9" t="n"/>
       <c r="B56" s="9" t="n"/>
-      <c r="C56" s="31" t="n"/>
+      <c r="C56" s="33" t="n"/>
       <c r="D56" s="9" t="n"/>
       <c r="E56" s="9" t="n"/>
       <c r="F56" s="9" t="n"/>
@@ -3946,7 +4404,7 @@
     <row r="57">
       <c r="A57" s="9" t="n"/>
       <c r="B57" s="9" t="n"/>
-      <c r="C57" s="31" t="n"/>
+      <c r="C57" s="33" t="n"/>
       <c r="D57" s="9" t="n"/>
       <c r="E57" s="9" t="n"/>
       <c r="F57" s="9" t="n"/>
@@ -3955,7 +4413,7 @@
     <row r="58">
       <c r="A58" s="9" t="n"/>
       <c r="B58" s="9" t="n"/>
-      <c r="C58" s="31" t="n"/>
+      <c r="C58" s="33" t="n"/>
       <c r="D58" s="9" t="n"/>
       <c r="E58" s="9" t="n"/>
       <c r="F58" s="9" t="n"/>
@@ -3964,7 +4422,7 @@
     <row r="59">
       <c r="A59" s="9" t="n"/>
       <c r="B59" s="9" t="n"/>
-      <c r="C59" s="31" t="n"/>
+      <c r="C59" s="33" t="n"/>
       <c r="D59" s="9" t="n"/>
       <c r="E59" s="9" t="n"/>
       <c r="F59" s="9" t="n"/>
@@ -3973,7 +4431,7 @@
     <row r="60">
       <c r="A60" s="9" t="n"/>
       <c r="B60" s="9" t="n"/>
-      <c r="C60" s="31" t="n"/>
+      <c r="C60" s="33" t="n"/>
       <c r="D60" s="9" t="n"/>
       <c r="E60" s="9" t="n"/>
       <c r="F60" s="9" t="n"/>
@@ -3982,7 +4440,7 @@
     <row r="61">
       <c r="A61" s="9" t="n"/>
       <c r="B61" s="9" t="n"/>
-      <c r="C61" s="31" t="n"/>
+      <c r="C61" s="33" t="n"/>
       <c r="D61" s="9" t="n"/>
       <c r="E61" s="9" t="n"/>
       <c r="F61" s="9" t="n"/>
@@ -3991,7 +4449,7 @@
     <row r="62">
       <c r="A62" s="9" t="n"/>
       <c r="B62" s="9" t="n"/>
-      <c r="C62" s="31" t="n"/>
+      <c r="C62" s="33" t="n"/>
       <c r="D62" s="9" t="n"/>
       <c r="E62" s="9" t="n"/>
       <c r="F62" s="9" t="n"/>
@@ -4000,7 +4458,7 @@
     <row r="63">
       <c r="A63" s="9" t="n"/>
       <c r="B63" s="9" t="n"/>
-      <c r="C63" s="31" t="n"/>
+      <c r="C63" s="33" t="n"/>
       <c r="D63" s="9" t="n"/>
       <c r="E63" s="9" t="n"/>
       <c r="F63" s="9" t="n"/>
@@ -4009,7 +4467,7 @@
     <row r="64">
       <c r="A64" s="9" t="n"/>
       <c r="B64" s="9" t="n"/>
-      <c r="C64" s="31" t="n"/>
+      <c r="C64" s="33" t="n"/>
       <c r="D64" s="9" t="n"/>
       <c r="E64" s="9" t="n"/>
       <c r="F64" s="9" t="n"/>
@@ -4018,7 +4476,7 @@
     <row r="65">
       <c r="A65" s="9" t="n"/>
       <c r="B65" s="9" t="n"/>
-      <c r="C65" s="31" t="n"/>
+      <c r="C65" s="33" t="n"/>
       <c r="D65" s="9" t="n"/>
       <c r="E65" s="9" t="n"/>
       <c r="F65" s="9" t="n"/>
@@ -4027,7 +4485,7 @@
     <row r="66">
       <c r="A66" s="9" t="n"/>
       <c r="B66" s="9" t="n"/>
-      <c r="C66" s="31" t="n"/>
+      <c r="C66" s="33" t="n"/>
       <c r="D66" s="9" t="n"/>
       <c r="E66" s="9" t="n"/>
       <c r="F66" s="9" t="n"/>
@@ -4036,7 +4494,7 @@
     <row r="67">
       <c r="A67" s="9" t="n"/>
       <c r="B67" s="9" t="n"/>
-      <c r="C67" s="31" t="n"/>
+      <c r="C67" s="33" t="n"/>
       <c r="D67" s="9" t="n"/>
       <c r="E67" s="9" t="n"/>
       <c r="F67" s="9" t="n"/>
@@ -4045,7 +4503,7 @@
     <row r="68">
       <c r="A68" s="9" t="n"/>
       <c r="B68" s="9" t="n"/>
-      <c r="C68" s="31" t="n"/>
+      <c r="C68" s="33" t="n"/>
       <c r="D68" s="9" t="n"/>
       <c r="E68" s="9" t="n"/>
       <c r="F68" s="9" t="n"/>
@@ -4054,7 +4512,7 @@
     <row r="69">
       <c r="A69" s="9" t="n"/>
       <c r="B69" s="9" t="n"/>
-      <c r="C69" s="31" t="n"/>
+      <c r="C69" s="33" t="n"/>
       <c r="D69" s="9" t="n"/>
       <c r="E69" s="9" t="n"/>
       <c r="F69" s="9" t="n"/>
@@ -4063,7 +4521,7 @@
     <row r="70">
       <c r="A70" s="9" t="n"/>
       <c r="B70" s="9" t="n"/>
-      <c r="C70" s="31" t="n"/>
+      <c r="C70" s="33" t="n"/>
       <c r="D70" s="9" t="n"/>
       <c r="E70" s="9" t="n"/>
       <c r="F70" s="9" t="n"/>
@@ -4072,7 +4530,7 @@
     <row r="71">
       <c r="A71" s="9" t="n"/>
       <c r="B71" s="9" t="n"/>
-      <c r="C71" s="31" t="n"/>
+      <c r="C71" s="33" t="n"/>
       <c r="D71" s="9" t="n"/>
       <c r="E71" s="9" t="n"/>
       <c r="F71" s="9" t="n"/>
@@ -4081,7 +4539,7 @@
     <row r="72">
       <c r="A72" s="9" t="n"/>
       <c r="B72" s="9" t="n"/>
-      <c r="C72" s="31" t="n"/>
+      <c r="C72" s="33" t="n"/>
       <c r="D72" s="9" t="n"/>
       <c r="E72" s="9" t="n"/>
       <c r="F72" s="9" t="n"/>
@@ -4090,7 +4548,7 @@
     <row r="73">
       <c r="A73" s="9" t="n"/>
       <c r="B73" s="9" t="n"/>
-      <c r="C73" s="31" t="n"/>
+      <c r="C73" s="33" t="n"/>
       <c r="D73" s="9" t="n"/>
       <c r="E73" s="9" t="n"/>
       <c r="F73" s="9" t="n"/>
@@ -4099,7 +4557,7 @@
     <row r="74">
       <c r="A74" s="9" t="n"/>
       <c r="B74" s="9" t="n"/>
-      <c r="C74" s="31" t="n"/>
+      <c r="C74" s="33" t="n"/>
       <c r="D74" s="9" t="n"/>
       <c r="E74" s="9" t="n"/>
       <c r="F74" s="9" t="n"/>
@@ -4108,7 +4566,7 @@
     <row r="75">
       <c r="A75" s="9" t="n"/>
       <c r="B75" s="9" t="n"/>
-      <c r="C75" s="31" t="n"/>
+      <c r="C75" s="33" t="n"/>
       <c r="D75" s="9" t="n"/>
       <c r="E75" s="9" t="n"/>
       <c r="F75" s="9" t="n"/>
@@ -4117,7 +4575,7 @@
     <row r="76">
       <c r="A76" s="9" t="n"/>
       <c r="B76" s="9" t="n"/>
-      <c r="C76" s="31" t="n"/>
+      <c r="C76" s="33" t="n"/>
       <c r="D76" s="9" t="n"/>
       <c r="E76" s="9" t="n"/>
       <c r="F76" s="9" t="n"/>
@@ -4126,7 +4584,7 @@
     <row r="77">
       <c r="A77" s="9" t="n"/>
       <c r="B77" s="9" t="n"/>
-      <c r="C77" s="31" t="n"/>
+      <c r="C77" s="33" t="n"/>
       <c r="D77" s="9" t="n"/>
       <c r="E77" s="9" t="n"/>
       <c r="F77" s="9" t="n"/>
@@ -4135,7 +4593,7 @@
     <row r="78">
       <c r="A78" s="9" t="n"/>
       <c r="B78" s="9" t="n"/>
-      <c r="C78" s="31" t="n"/>
+      <c r="C78" s="33" t="n"/>
       <c r="D78" s="9" t="n"/>
       <c r="E78" s="9" t="n"/>
       <c r="F78" s="9" t="n"/>
@@ -4144,7 +4602,7 @@
     <row r="79">
       <c r="A79" s="9" t="n"/>
       <c r="B79" s="9" t="n"/>
-      <c r="C79" s="31" t="n"/>
+      <c r="C79" s="33" t="n"/>
       <c r="D79" s="9" t="n"/>
       <c r="E79" s="9" t="n"/>
       <c r="F79" s="9" t="n"/>
@@ -4153,7 +4611,7 @@
     <row r="80">
       <c r="A80" s="9" t="n"/>
       <c r="B80" s="9" t="n"/>
-      <c r="C80" s="31" t="n"/>
+      <c r="C80" s="33" t="n"/>
       <c r="D80" s="9" t="n"/>
       <c r="E80" s="9" t="n"/>
       <c r="F80" s="9" t="n"/>
@@ -4162,7 +4620,7 @@
     <row r="81">
       <c r="A81" s="9" t="n"/>
       <c r="B81" s="9" t="n"/>
-      <c r="C81" s="31" t="n"/>
+      <c r="C81" s="33" t="n"/>
       <c r="D81" s="9" t="n"/>
       <c r="E81" s="9" t="n"/>
       <c r="F81" s="9" t="n"/>
@@ -4171,7 +4629,7 @@
     <row r="82">
       <c r="A82" s="9" t="n"/>
       <c r="B82" s="9" t="n"/>
-      <c r="C82" s="31" t="n"/>
+      <c r="C82" s="33" t="n"/>
       <c r="D82" s="9" t="n"/>
       <c r="E82" s="9" t="n"/>
       <c r="F82" s="9" t="n"/>
@@ -4180,7 +4638,7 @@
     <row r="83">
       <c r="A83" s="9" t="n"/>
       <c r="B83" s="9" t="n"/>
-      <c r="C83" s="31" t="n"/>
+      <c r="C83" s="33" t="n"/>
       <c r="D83" s="9" t="n"/>
       <c r="E83" s="9" t="n"/>
       <c r="F83" s="9" t="n"/>
@@ -4189,7 +4647,7 @@
     <row r="84">
       <c r="A84" s="9" t="n"/>
       <c r="B84" s="9" t="n"/>
-      <c r="C84" s="31" t="n"/>
+      <c r="C84" s="33" t="n"/>
       <c r="D84" s="9" t="n"/>
       <c r="E84" s="9" t="n"/>
       <c r="F84" s="9" t="n"/>
@@ -4198,7 +4656,7 @@
     <row r="85">
       <c r="A85" s="9" t="n"/>
       <c r="B85" s="9" t="n"/>
-      <c r="C85" s="31" t="n"/>
+      <c r="C85" s="33" t="n"/>
       <c r="D85" s="9" t="n"/>
       <c r="E85" s="9" t="n"/>
       <c r="F85" s="9" t="n"/>
@@ -4207,7 +4665,7 @@
     <row r="86">
       <c r="A86" s="9" t="n"/>
       <c r="B86" s="9" t="n"/>
-      <c r="C86" s="31" t="n"/>
+      <c r="C86" s="33" t="n"/>
       <c r="D86" s="9" t="n"/>
       <c r="E86" s="9" t="n"/>
       <c r="F86" s="9" t="n"/>
@@ -4216,7 +4674,7 @@
     <row r="87">
       <c r="A87" s="9" t="n"/>
       <c r="B87" s="9" t="n"/>
-      <c r="C87" s="31" t="n"/>
+      <c r="C87" s="33" t="n"/>
       <c r="D87" s="9" t="n"/>
       <c r="E87" s="9" t="n"/>
       <c r="F87" s="9" t="n"/>
@@ -4225,7 +4683,7 @@
     <row r="88">
       <c r="A88" s="9" t="n"/>
       <c r="B88" s="9" t="n"/>
-      <c r="C88" s="31" t="n"/>
+      <c r="C88" s="33" t="n"/>
       <c r="D88" s="9" t="n"/>
       <c r="E88" s="9" t="n"/>
       <c r="F88" s="9" t="n"/>
@@ -4234,7 +4692,7 @@
     <row r="89">
       <c r="A89" s="9" t="n"/>
       <c r="B89" s="9" t="n"/>
-      <c r="C89" s="31" t="n"/>
+      <c r="C89" s="33" t="n"/>
       <c r="D89" s="9" t="n"/>
       <c r="E89" s="9" t="n"/>
       <c r="F89" s="9" t="n"/>
@@ -4243,7 +4701,7 @@
     <row r="90">
       <c r="A90" s="9" t="n"/>
       <c r="B90" s="9" t="n"/>
-      <c r="C90" s="31" t="n"/>
+      <c r="C90" s="33" t="n"/>
       <c r="D90" s="9" t="n"/>
       <c r="E90" s="9" t="n"/>
       <c r="F90" s="9" t="n"/>
@@ -4252,7 +4710,7 @@
     <row r="91">
       <c r="A91" s="9" t="n"/>
       <c r="B91" s="9" t="n"/>
-      <c r="C91" s="31" t="n"/>
+      <c r="C91" s="33" t="n"/>
       <c r="D91" s="9" t="n"/>
       <c r="E91" s="9" t="n"/>
       <c r="F91" s="9" t="n"/>
@@ -4261,7 +4719,7 @@
     <row r="92">
       <c r="A92" s="9" t="n"/>
       <c r="B92" s="9" t="n"/>
-      <c r="C92" s="31" t="n"/>
+      <c r="C92" s="33" t="n"/>
       <c r="D92" s="9" t="n"/>
       <c r="E92" s="9" t="n"/>
       <c r="F92" s="9" t="n"/>
@@ -4270,7 +4728,7 @@
     <row r="93">
       <c r="A93" s="9" t="n"/>
       <c r="B93" s="9" t="n"/>
-      <c r="C93" s="31" t="n"/>
+      <c r="C93" s="33" t="n"/>
       <c r="D93" s="9" t="n"/>
       <c r="E93" s="9" t="n"/>
       <c r="F93" s="9" t="n"/>
@@ -4279,7 +4737,7 @@
     <row r="94">
       <c r="A94" s="9" t="n"/>
       <c r="B94" s="9" t="n"/>
-      <c r="C94" s="31" t="n"/>
+      <c r="C94" s="33" t="n"/>
       <c r="D94" s="9" t="n"/>
       <c r="E94" s="9" t="n"/>
       <c r="F94" s="9" t="n"/>
@@ -4288,7 +4746,7 @@
     <row r="95">
       <c r="A95" s="9" t="n"/>
       <c r="B95" s="9" t="n"/>
-      <c r="C95" s="31" t="n"/>
+      <c r="C95" s="33" t="n"/>
       <c r="D95" s="9" t="n"/>
       <c r="E95" s="9" t="n"/>
       <c r="F95" s="9" t="n"/>
@@ -4297,7 +4755,7 @@
     <row r="96">
       <c r="A96" s="9" t="n"/>
       <c r="B96" s="9" t="n"/>
-      <c r="C96" s="31" t="n"/>
+      <c r="C96" s="33" t="n"/>
       <c r="D96" s="9" t="n"/>
       <c r="E96" s="9" t="n"/>
       <c r="F96" s="9" t="n"/>
@@ -4306,7 +4764,7 @@
     <row r="97">
       <c r="A97" s="9" t="n"/>
       <c r="B97" s="9" t="n"/>
-      <c r="C97" s="31" t="n"/>
+      <c r="C97" s="33" t="n"/>
       <c r="D97" s="9" t="n"/>
       <c r="E97" s="9" t="n"/>
       <c r="F97" s="9" t="n"/>
@@ -4315,7 +4773,7 @@
     <row r="98">
       <c r="A98" s="9" t="n"/>
       <c r="B98" s="9" t="n"/>
-      <c r="C98" s="31" t="n"/>
+      <c r="C98" s="33" t="n"/>
       <c r="D98" s="9" t="n"/>
       <c r="E98" s="9" t="n"/>
       <c r="F98" s="9" t="n"/>
@@ -4324,7 +4782,7 @@
     <row r="99">
       <c r="A99" s="9" t="n"/>
       <c r="B99" s="9" t="n"/>
-      <c r="C99" s="31" t="n"/>
+      <c r="C99" s="33" t="n"/>
       <c r="D99" s="9" t="n"/>
       <c r="E99" s="9" t="n"/>
       <c r="F99" s="9" t="n"/>
@@ -4333,7 +4791,7 @@
     <row r="100">
       <c r="A100" s="9" t="n"/>
       <c r="B100" s="9" t="n"/>
-      <c r="C100" s="31" t="n"/>
+      <c r="C100" s="33" t="n"/>
       <c r="D100" s="9" t="n"/>
       <c r="E100" s="9" t="n"/>
       <c r="F100" s="9" t="n"/>
@@ -4342,7 +4800,7 @@
     <row r="101">
       <c r="A101" s="9" t="n"/>
       <c r="B101" s="9" t="n"/>
-      <c r="C101" s="31" t="n"/>
+      <c r="C101" s="33" t="n"/>
       <c r="D101" s="9" t="n"/>
       <c r="E101" s="9" t="n"/>
       <c r="F101" s="9" t="n"/>
@@ -4351,7 +4809,7 @@
     <row r="102">
       <c r="A102" s="9" t="n"/>
       <c r="B102" s="9" t="n"/>
-      <c r="C102" s="31" t="n"/>
+      <c r="C102" s="33" t="n"/>
       <c r="D102" s="9" t="n"/>
       <c r="E102" s="9" t="n"/>
       <c r="F102" s="9" t="n"/>
@@ -4360,7 +4818,7 @@
     <row r="103">
       <c r="A103" s="9" t="n"/>
       <c r="B103" s="9" t="n"/>
-      <c r="C103" s="31" t="n"/>
+      <c r="C103" s="33" t="n"/>
       <c r="D103" s="9" t="n"/>
       <c r="E103" s="9" t="n"/>
       <c r="F103" s="9" t="n"/>
@@ -4369,7 +4827,7 @@
     <row r="104">
       <c r="A104" s="9" t="n"/>
       <c r="B104" s="9" t="n"/>
-      <c r="C104" s="31" t="n"/>
+      <c r="C104" s="33" t="n"/>
       <c r="D104" s="9" t="n"/>
       <c r="E104" s="9" t="n"/>
       <c r="F104" s="9" t="n"/>
@@ -4378,7 +4836,7 @@
     <row r="105">
       <c r="A105" s="9" t="n"/>
       <c r="B105" s="9" t="n"/>
-      <c r="C105" s="31" t="n"/>
+      <c r="C105" s="33" t="n"/>
       <c r="D105" s="9" t="n"/>
       <c r="E105" s="9" t="n"/>
       <c r="F105" s="9" t="n"/>
@@ -4387,7 +4845,7 @@
     <row r="106">
       <c r="A106" s="9" t="n"/>
       <c r="B106" s="9" t="n"/>
-      <c r="C106" s="31" t="n"/>
+      <c r="C106" s="33" t="n"/>
       <c r="D106" s="9" t="n"/>
       <c r="E106" s="9" t="n"/>
       <c r="F106" s="9" t="n"/>
@@ -4396,7 +4854,7 @@
     <row r="107">
       <c r="A107" s="9" t="n"/>
       <c r="B107" s="9" t="n"/>
-      <c r="C107" s="31" t="n"/>
+      <c r="C107" s="33" t="n"/>
       <c r="D107" s="9" t="n"/>
       <c r="E107" s="9" t="n"/>
       <c r="F107" s="9" t="n"/>
@@ -4405,7 +4863,7 @@
     <row r="108">
       <c r="A108" s="9" t="n"/>
       <c r="B108" s="9" t="n"/>
-      <c r="C108" s="31" t="n"/>
+      <c r="C108" s="33" t="n"/>
       <c r="D108" s="9" t="n"/>
       <c r="E108" s="9" t="n"/>
       <c r="F108" s="9" t="n"/>
@@ -4414,7 +4872,7 @@
     <row r="109">
       <c r="A109" s="9" t="n"/>
       <c r="B109" s="9" t="n"/>
-      <c r="C109" s="31" t="n"/>
+      <c r="C109" s="33" t="n"/>
       <c r="D109" s="9" t="n"/>
       <c r="E109" s="9" t="n"/>
       <c r="F109" s="9" t="n"/>
@@ -4423,7 +4881,7 @@
     <row r="110">
       <c r="A110" s="9" t="n"/>
       <c r="B110" s="9" t="n"/>
-      <c r="C110" s="31" t="n"/>
+      <c r="C110" s="33" t="n"/>
       <c r="D110" s="9" t="n"/>
       <c r="E110" s="9" t="n"/>
       <c r="F110" s="9" t="n"/>
@@ -4432,7 +4890,7 @@
     <row r="111">
       <c r="A111" s="9" t="n"/>
       <c r="B111" s="9" t="n"/>
-      <c r="C111" s="31" t="n"/>
+      <c r="C111" s="33" t="n"/>
       <c r="D111" s="9" t="n"/>
       <c r="E111" s="9" t="n"/>
       <c r="F111" s="9" t="n"/>
@@ -4441,7 +4899,7 @@
     <row r="112">
       <c r="A112" s="9" t="n"/>
       <c r="B112" s="9" t="n"/>
-      <c r="C112" s="31" t="n"/>
+      <c r="C112" s="33" t="n"/>
       <c r="D112" s="9" t="n"/>
       <c r="E112" s="9" t="n"/>
       <c r="F112" s="9" t="n"/>
@@ -4450,7 +4908,7 @@
     <row r="113">
       <c r="A113" s="9" t="n"/>
       <c r="B113" s="9" t="n"/>
-      <c r="C113" s="31" t="n"/>
+      <c r="C113" s="33" t="n"/>
       <c r="D113" s="9" t="n"/>
       <c r="E113" s="9" t="n"/>
       <c r="F113" s="9" t="n"/>
@@ -4459,7 +4917,7 @@
     <row r="114">
       <c r="A114" s="9" t="n"/>
       <c r="B114" s="9" t="n"/>
-      <c r="C114" s="31" t="n"/>
+      <c r="C114" s="33" t="n"/>
       <c r="D114" s="9" t="n"/>
       <c r="E114" s="9" t="n"/>
       <c r="F114" s="9" t="n"/>
@@ -4468,7 +4926,7 @@
     <row r="115">
       <c r="A115" s="9" t="n"/>
       <c r="B115" s="9" t="n"/>
-      <c r="C115" s="31" t="n"/>
+      <c r="C115" s="33" t="n"/>
       <c r="D115" s="9" t="n"/>
       <c r="E115" s="9" t="n"/>
       <c r="F115" s="9" t="n"/>
@@ -4477,7 +4935,7 @@
     <row r="116">
       <c r="A116" s="9" t="n"/>
       <c r="B116" s="9" t="n"/>
-      <c r="C116" s="31" t="n"/>
+      <c r="C116" s="33" t="n"/>
       <c r="D116" s="9" t="n"/>
       <c r="E116" s="9" t="n"/>
       <c r="F116" s="9" t="n"/>
@@ -4486,7 +4944,7 @@
     <row r="117">
       <c r="A117" s="9" t="n"/>
       <c r="B117" s="9" t="n"/>
-      <c r="C117" s="31" t="n"/>
+      <c r="C117" s="33" t="n"/>
       <c r="D117" s="9" t="n"/>
       <c r="E117" s="9" t="n"/>
       <c r="F117" s="9" t="n"/>
@@ -4495,7 +4953,7 @@
     <row r="118">
       <c r="A118" s="9" t="n"/>
       <c r="B118" s="9" t="n"/>
-      <c r="C118" s="31" t="n"/>
+      <c r="C118" s="33" t="n"/>
       <c r="D118" s="9" t="n"/>
       <c r="E118" s="9" t="n"/>
       <c r="F118" s="9" t="n"/>
@@ -4504,7 +4962,7 @@
     <row r="119">
       <c r="A119" s="9" t="n"/>
       <c r="B119" s="9" t="n"/>
-      <c r="C119" s="31" t="n"/>
+      <c r="C119" s="33" t="n"/>
       <c r="D119" s="9" t="n"/>
       <c r="E119" s="9" t="n"/>
       <c r="F119" s="9" t="n"/>
@@ -4513,7 +4971,7 @@
     <row r="120">
       <c r="A120" s="9" t="n"/>
       <c r="B120" s="9" t="n"/>
-      <c r="C120" s="31" t="n"/>
+      <c r="C120" s="33" t="n"/>
       <c r="D120" s="9" t="n"/>
       <c r="E120" s="9" t="n"/>
       <c r="F120" s="9" t="n"/>
@@ -4522,7 +4980,7 @@
     <row r="121">
       <c r="A121" s="9" t="n"/>
       <c r="B121" s="9" t="n"/>
-      <c r="C121" s="31" t="n"/>
+      <c r="C121" s="33" t="n"/>
       <c r="D121" s="9" t="n"/>
       <c r="E121" s="9" t="n"/>
       <c r="F121" s="9" t="n"/>
@@ -4531,7 +4989,7 @@
     <row r="122">
       <c r="A122" s="9" t="n"/>
       <c r="B122" s="9" t="n"/>
-      <c r="C122" s="31" t="n"/>
+      <c r="C122" s="33" t="n"/>
       <c r="D122" s="9" t="n"/>
       <c r="E122" s="9" t="n"/>
       <c r="F122" s="9" t="n"/>
@@ -4540,7 +4998,7 @@
     <row r="123">
       <c r="A123" s="9" t="n"/>
       <c r="B123" s="9" t="n"/>
-      <c r="C123" s="31" t="n"/>
+      <c r="C123" s="33" t="n"/>
       <c r="D123" s="9" t="n"/>
       <c r="E123" s="9" t="n"/>
       <c r="F123" s="9" t="n"/>
@@ -4549,7 +5007,7 @@
     <row r="124">
       <c r="A124" s="9" t="n"/>
       <c r="B124" s="9" t="n"/>
-      <c r="C124" s="31" t="n"/>
+      <c r="C124" s="33" t="n"/>
       <c r="D124" s="9" t="n"/>
       <c r="E124" s="9" t="n"/>
       <c r="F124" s="9" t="n"/>
@@ -4558,7 +5016,7 @@
     <row r="125">
       <c r="A125" s="9" t="n"/>
       <c r="B125" s="9" t="n"/>
-      <c r="C125" s="31" t="n"/>
+      <c r="C125" s="33" t="n"/>
       <c r="D125" s="9" t="n"/>
       <c r="E125" s="9" t="n"/>
       <c r="F125" s="9" t="n"/>
@@ -4567,7 +5025,7 @@
     <row r="126">
       <c r="A126" s="9" t="n"/>
       <c r="B126" s="9" t="n"/>
-      <c r="C126" s="31" t="n"/>
+      <c r="C126" s="33" t="n"/>
       <c r="D126" s="9" t="n"/>
       <c r="E126" s="9" t="n"/>
       <c r="F126" s="9" t="n"/>
@@ -4576,7 +5034,7 @@
     <row r="127">
       <c r="A127" s="9" t="n"/>
       <c r="B127" s="9" t="n"/>
-      <c r="C127" s="31" t="n"/>
+      <c r="C127" s="33" t="n"/>
       <c r="D127" s="9" t="n"/>
       <c r="E127" s="9" t="n"/>
       <c r="F127" s="9" t="n"/>
@@ -4585,7 +5043,7 @@
     <row r="128">
       <c r="A128" s="9" t="n"/>
       <c r="B128" s="9" t="n"/>
-      <c r="C128" s="31" t="n"/>
+      <c r="C128" s="33" t="n"/>
       <c r="D128" s="9" t="n"/>
       <c r="E128" s="9" t="n"/>
       <c r="F128" s="9" t="n"/>
@@ -4594,7 +5052,7 @@
     <row r="129">
       <c r="A129" s="9" t="n"/>
       <c r="B129" s="9" t="n"/>
-      <c r="C129" s="31" t="n"/>
+      <c r="C129" s="33" t="n"/>
       <c r="D129" s="9" t="n"/>
       <c r="E129" s="9" t="n"/>
       <c r="F129" s="9" t="n"/>
@@ -4603,7 +5061,7 @@
     <row r="130">
       <c r="A130" s="9" t="n"/>
       <c r="B130" s="9" t="n"/>
-      <c r="C130" s="31" t="n"/>
+      <c r="C130" s="33" t="n"/>
       <c r="D130" s="9" t="n"/>
       <c r="E130" s="9" t="n"/>
       <c r="F130" s="9" t="n"/>
@@ -4612,7 +5070,7 @@
     <row r="131">
       <c r="A131" s="9" t="n"/>
       <c r="B131" s="9" t="n"/>
-      <c r="C131" s="31" t="n"/>
+      <c r="C131" s="33" t="n"/>
       <c r="D131" s="9" t="n"/>
       <c r="E131" s="9" t="n"/>
       <c r="F131" s="9" t="n"/>
@@ -4621,7 +5079,7 @@
     <row r="132">
       <c r="A132" s="9" t="n"/>
       <c r="B132" s="9" t="n"/>
-      <c r="C132" s="31" t="n"/>
+      <c r="C132" s="33" t="n"/>
       <c r="D132" s="9" t="n"/>
       <c r="E132" s="9" t="n"/>
       <c r="F132" s="9" t="n"/>
@@ -4630,7 +5088,7 @@
     <row r="133">
       <c r="A133" s="9" t="n"/>
       <c r="B133" s="9" t="n"/>
-      <c r="C133" s="31" t="n"/>
+      <c r="C133" s="33" t="n"/>
       <c r="D133" s="9" t="n"/>
       <c r="E133" s="9" t="n"/>
       <c r="F133" s="9" t="n"/>
@@ -4639,7 +5097,7 @@
     <row r="134">
       <c r="A134" s="9" t="n"/>
       <c r="B134" s="9" t="n"/>
-      <c r="C134" s="31" t="n"/>
+      <c r="C134" s="33" t="n"/>
       <c r="D134" s="9" t="n"/>
       <c r="E134" s="9" t="n"/>
       <c r="F134" s="9" t="n"/>
@@ -4648,7 +5106,7 @@
     <row r="135">
       <c r="A135" s="9" t="n"/>
       <c r="B135" s="9" t="n"/>
-      <c r="C135" s="31" t="n"/>
+      <c r="C135" s="33" t="n"/>
       <c r="D135" s="9" t="n"/>
       <c r="E135" s="9" t="n"/>
       <c r="F135" s="9" t="n"/>
@@ -4657,7 +5115,7 @@
     <row r="136">
       <c r="A136" s="9" t="n"/>
       <c r="B136" s="9" t="n"/>
-      <c r="C136" s="31" t="n"/>
+      <c r="C136" s="33" t="n"/>
       <c r="D136" s="9" t="n"/>
       <c r="E136" s="9" t="n"/>
       <c r="F136" s="9" t="n"/>
@@ -4666,7 +5124,7 @@
     <row r="137">
       <c r="A137" s="9" t="n"/>
       <c r="B137" s="9" t="n"/>
-      <c r="C137" s="31" t="n"/>
+      <c r="C137" s="33" t="n"/>
       <c r="D137" s="9" t="n"/>
       <c r="E137" s="9" t="n"/>
       <c r="F137" s="9" t="n"/>
@@ -4675,7 +5133,7 @@
     <row r="138">
       <c r="A138" s="9" t="n"/>
       <c r="B138" s="9" t="n"/>
-      <c r="C138" s="31" t="n"/>
+      <c r="C138" s="33" t="n"/>
       <c r="D138" s="9" t="n"/>
       <c r="E138" s="9" t="n"/>
       <c r="F138" s="9" t="n"/>
@@ -4684,7 +5142,7 @@
     <row r="139">
       <c r="A139" s="9" t="n"/>
       <c r="B139" s="9" t="n"/>
-      <c r="C139" s="31" t="n"/>
+      <c r="C139" s="33" t="n"/>
       <c r="D139" s="9" t="n"/>
       <c r="E139" s="9" t="n"/>
       <c r="F139" s="9" t="n"/>
@@ -4693,7 +5151,7 @@
     <row r="140">
       <c r="A140" s="9" t="n"/>
       <c r="B140" s="9" t="n"/>
-      <c r="C140" s="31" t="n"/>
+      <c r="C140" s="33" t="n"/>
       <c r="D140" s="9" t="n"/>
       <c r="E140" s="9" t="n"/>
       <c r="F140" s="9" t="n"/>
@@ -4702,7 +5160,7 @@
     <row r="141">
       <c r="A141" s="9" t="n"/>
       <c r="B141" s="9" t="n"/>
-      <c r="C141" s="31" t="n"/>
+      <c r="C141" s="33" t="n"/>
       <c r="D141" s="9" t="n"/>
       <c r="E141" s="9" t="n"/>
       <c r="F141" s="9" t="n"/>
@@ -4711,7 +5169,7 @@
     <row r="142">
       <c r="A142" s="9" t="n"/>
       <c r="B142" s="9" t="n"/>
-      <c r="C142" s="31" t="n"/>
+      <c r="C142" s="33" t="n"/>
       <c r="D142" s="9" t="n"/>
       <c r="E142" s="9" t="n"/>
       <c r="F142" s="9" t="n"/>
@@ -4720,7 +5178,7 @@
     <row r="143">
       <c r="A143" s="9" t="n"/>
       <c r="B143" s="9" t="n"/>
-      <c r="C143" s="31" t="n"/>
+      <c r="C143" s="33" t="n"/>
       <c r="D143" s="9" t="n"/>
       <c r="E143" s="9" t="n"/>
       <c r="F143" s="9" t="n"/>
@@ -4729,7 +5187,7 @@
     <row r="144">
       <c r="A144" s="9" t="n"/>
       <c r="B144" s="9" t="n"/>
-      <c r="C144" s="31" t="n"/>
+      <c r="C144" s="33" t="n"/>
       <c r="D144" s="9" t="n"/>
       <c r="E144" s="9" t="n"/>
       <c r="F144" s="9" t="n"/>
@@ -4738,7 +5196,7 @@
     <row r="145">
       <c r="A145" s="9" t="n"/>
       <c r="B145" s="9" t="n"/>
-      <c r="C145" s="31" t="n"/>
+      <c r="C145" s="33" t="n"/>
       <c r="D145" s="9" t="n"/>
       <c r="E145" s="9" t="n"/>
       <c r="F145" s="9" t="n"/>
@@ -4747,7 +5205,7 @@
     <row r="146">
       <c r="A146" s="9" t="n"/>
       <c r="B146" s="9" t="n"/>
-      <c r="C146" s="31" t="n"/>
+      <c r="C146" s="33" t="n"/>
       <c r="D146" s="9" t="n"/>
       <c r="E146" s="9" t="n"/>
       <c r="F146" s="9" t="n"/>
@@ -4756,7 +5214,7 @@
     <row r="147">
       <c r="A147" s="9" t="n"/>
       <c r="B147" s="9" t="n"/>
-      <c r="C147" s="31" t="n"/>
+      <c r="C147" s="33" t="n"/>
       <c r="D147" s="9" t="n"/>
       <c r="E147" s="9" t="n"/>
       <c r="F147" s="9" t="n"/>
@@ -4765,7 +5223,7 @@
     <row r="148">
       <c r="A148" s="9" t="n"/>
       <c r="B148" s="9" t="n"/>
-      <c r="C148" s="31" t="n"/>
+      <c r="C148" s="33" t="n"/>
       <c r="D148" s="9" t="n"/>
       <c r="E148" s="9" t="n"/>
       <c r="F148" s="9" t="n"/>
@@ -4774,7 +5232,7 @@
     <row r="149">
       <c r="A149" s="9" t="n"/>
       <c r="B149" s="9" t="n"/>
-      <c r="C149" s="31" t="n"/>
+      <c r="C149" s="33" t="n"/>
       <c r="D149" s="9" t="n"/>
       <c r="E149" s="9" t="n"/>
       <c r="F149" s="9" t="n"/>
@@ -4783,7 +5241,7 @@
     <row r="150">
       <c r="A150" s="9" t="n"/>
       <c r="B150" s="9" t="n"/>
-      <c r="C150" s="31" t="n"/>
+      <c r="C150" s="33" t="n"/>
       <c r="D150" s="9" t="n"/>
       <c r="E150" s="9" t="n"/>
       <c r="F150" s="9" t="n"/>
@@ -4792,7 +5250,7 @@
     <row r="151">
       <c r="A151" s="9" t="n"/>
       <c r="B151" s="9" t="n"/>
-      <c r="C151" s="31" t="n"/>
+      <c r="C151" s="33" t="n"/>
       <c r="D151" s="9" t="n"/>
       <c r="E151" s="9" t="n"/>
       <c r="F151" s="9" t="n"/>
@@ -4801,7 +5259,7 @@
     <row r="152">
       <c r="A152" s="9" t="n"/>
       <c r="B152" s="9" t="n"/>
-      <c r="C152" s="31" t="n"/>
+      <c r="C152" s="33" t="n"/>
       <c r="D152" s="9" t="n"/>
       <c r="E152" s="9" t="n"/>
       <c r="F152" s="9" t="n"/>
@@ -4810,7 +5268,7 @@
     <row r="153">
       <c r="A153" s="9" t="n"/>
       <c r="B153" s="9" t="n"/>
-      <c r="C153" s="31" t="n"/>
+      <c r="C153" s="33" t="n"/>
       <c r="D153" s="9" t="n"/>
       <c r="E153" s="9" t="n"/>
       <c r="F153" s="9" t="n"/>
@@ -4819,7 +5277,7 @@
     <row r="154">
       <c r="A154" s="9" t="n"/>
       <c r="B154" s="9" t="n"/>
-      <c r="C154" s="31" t="n"/>
+      <c r="C154" s="33" t="n"/>
       <c r="D154" s="9" t="n"/>
       <c r="E154" s="9" t="n"/>
       <c r="F154" s="9" t="n"/>
@@ -4828,7 +5286,7 @@
     <row r="155">
       <c r="A155" s="9" t="n"/>
       <c r="B155" s="9" t="n"/>
-      <c r="C155" s="31" t="n"/>
+      <c r="C155" s="33" t="n"/>
       <c r="D155" s="9" t="n"/>
       <c r="E155" s="9" t="n"/>
       <c r="F155" s="9" t="n"/>
@@ -4837,7 +5295,7 @@
     <row r="156">
       <c r="A156" s="9" t="n"/>
       <c r="B156" s="9" t="n"/>
-      <c r="C156" s="31" t="n"/>
+      <c r="C156" s="33" t="n"/>
       <c r="D156" s="9" t="n"/>
       <c r="E156" s="9" t="n"/>
       <c r="F156" s="9" t="n"/>
@@ -4846,7 +5304,7 @@
     <row r="157">
       <c r="A157" s="9" t="n"/>
       <c r="B157" s="9" t="n"/>
-      <c r="C157" s="31" t="n"/>
+      <c r="C157" s="33" t="n"/>
       <c r="D157" s="9" t="n"/>
       <c r="E157" s="9" t="n"/>
       <c r="F157" s="9" t="n"/>
@@ -4855,7 +5313,7 @@
     <row r="158">
       <c r="A158" s="9" t="n"/>
       <c r="B158" s="9" t="n"/>
-      <c r="C158" s="31" t="n"/>
+      <c r="C158" s="33" t="n"/>
       <c r="D158" s="9" t="n"/>
       <c r="E158" s="9" t="n"/>
       <c r="F158" s="9" t="n"/>
@@ -4864,7 +5322,7 @@
     <row r="159">
       <c r="A159" s="9" t="n"/>
       <c r="B159" s="9" t="n"/>
-      <c r="C159" s="31" t="n"/>
+      <c r="C159" s="33" t="n"/>
       <c r="D159" s="9" t="n"/>
       <c r="E159" s="9" t="n"/>
       <c r="F159" s="9" t="n"/>
@@ -4873,7 +5331,7 @@
     <row r="160">
       <c r="A160" s="9" t="n"/>
       <c r="B160" s="9" t="n"/>
-      <c r="C160" s="31" t="n"/>
+      <c r="C160" s="33" t="n"/>
       <c r="D160" s="9" t="n"/>
       <c r="E160" s="9" t="n"/>
       <c r="F160" s="9" t="n"/>
@@ -4882,7 +5340,7 @@
     <row r="161">
       <c r="A161" s="9" t="n"/>
       <c r="B161" s="9" t="n"/>
-      <c r="C161" s="31" t="n"/>
+      <c r="C161" s="33" t="n"/>
       <c r="D161" s="9" t="n"/>
       <c r="E161" s="9" t="n"/>
       <c r="F161" s="9" t="n"/>
@@ -4891,7 +5349,7 @@
     <row r="162">
       <c r="A162" s="9" t="n"/>
       <c r="B162" s="9" t="n"/>
-      <c r="C162" s="31" t="n"/>
+      <c r="C162" s="33" t="n"/>
       <c r="D162" s="9" t="n"/>
       <c r="E162" s="9" t="n"/>
       <c r="F162" s="9" t="n"/>
@@ -4900,7 +5358,7 @@
     <row r="163">
       <c r="A163" s="9" t="n"/>
       <c r="B163" s="9" t="n"/>
-      <c r="C163" s="31" t="n"/>
+      <c r="C163" s="33" t="n"/>
       <c r="D163" s="9" t="n"/>
       <c r="E163" s="9" t="n"/>
       <c r="F163" s="9" t="n"/>
@@ -4909,7 +5367,7 @@
     <row r="164">
       <c r="A164" s="9" t="n"/>
       <c r="B164" s="9" t="n"/>
-      <c r="C164" s="31" t="n"/>
+      <c r="C164" s="33" t="n"/>
       <c r="D164" s="9" t="n"/>
       <c r="E164" s="9" t="n"/>
       <c r="F164" s="9" t="n"/>
@@ -4918,7 +5376,7 @@
     <row r="165">
       <c r="A165" s="9" t="n"/>
       <c r="B165" s="9" t="n"/>
-      <c r="C165" s="31" t="n"/>
+      <c r="C165" s="33" t="n"/>
       <c r="D165" s="9" t="n"/>
       <c r="E165" s="9" t="n"/>
       <c r="F165" s="9" t="n"/>
@@ -4927,7 +5385,7 @@
     <row r="166">
       <c r="A166" s="9" t="n"/>
       <c r="B166" s="9" t="n"/>
-      <c r="C166" s="31" t="n"/>
+      <c r="C166" s="33" t="n"/>
       <c r="D166" s="9" t="n"/>
       <c r="E166" s="9" t="n"/>
       <c r="F166" s="9" t="n"/>
@@ -4936,7 +5394,7 @@
     <row r="167">
       <c r="A167" s="9" t="n"/>
       <c r="B167" s="9" t="n"/>
-      <c r="C167" s="31" t="n"/>
+      <c r="C167" s="33" t="n"/>
       <c r="D167" s="9" t="n"/>
       <c r="E167" s="9" t="n"/>
       <c r="F167" s="9" t="n"/>
@@ -4945,7 +5403,7 @@
     <row r="168">
       <c r="A168" s="9" t="n"/>
       <c r="B168" s="9" t="n"/>
-      <c r="C168" s="31" t="n"/>
+      <c r="C168" s="33" t="n"/>
       <c r="D168" s="9" t="n"/>
       <c r="E168" s="9" t="n"/>
       <c r="F168" s="9" t="n"/>
@@ -4954,7 +5412,7 @@
     <row r="169">
       <c r="A169" s="9" t="n"/>
       <c r="B169" s="9" t="n"/>
-      <c r="C169" s="31" t="n"/>
+      <c r="C169" s="33" t="n"/>
       <c r="D169" s="9" t="n"/>
       <c r="E169" s="9" t="n"/>
       <c r="F169" s="9" t="n"/>
@@ -4963,7 +5421,7 @@
     <row r="170">
       <c r="A170" s="9" t="n"/>
       <c r="B170" s="9" t="n"/>
-      <c r="C170" s="31" t="n"/>
+      <c r="C170" s="33" t="n"/>
       <c r="D170" s="9" t="n"/>
       <c r="E170" s="9" t="n"/>
       <c r="F170" s="9" t="n"/>
@@ -4972,7 +5430,7 @@
     <row r="171">
       <c r="A171" s="9" t="n"/>
       <c r="B171" s="9" t="n"/>
-      <c r="C171" s="31" t="n"/>
+      <c r="C171" s="33" t="n"/>
       <c r="D171" s="9" t="n"/>
       <c r="E171" s="9" t="n"/>
       <c r="F171" s="9" t="n"/>
@@ -4981,7 +5439,7 @@
     <row r="172">
       <c r="A172" s="9" t="n"/>
       <c r="B172" s="9" t="n"/>
-      <c r="C172" s="31" t="n"/>
+      <c r="C172" s="33" t="n"/>
       <c r="D172" s="9" t="n"/>
       <c r="E172" s="9" t="n"/>
       <c r="F172" s="9" t="n"/>
@@ -4990,7 +5448,7 @@
     <row r="173">
       <c r="A173" s="9" t="n"/>
       <c r="B173" s="9" t="n"/>
-      <c r="C173" s="31" t="n"/>
+      <c r="C173" s="33" t="n"/>
       <c r="D173" s="9" t="n"/>
       <c r="E173" s="9" t="n"/>
       <c r="F173" s="9" t="n"/>
@@ -4999,7 +5457,7 @@
     <row r="174">
       <c r="A174" s="9" t="n"/>
       <c r="B174" s="9" t="n"/>
-      <c r="C174" s="31" t="n"/>
+      <c r="C174" s="33" t="n"/>
       <c r="D174" s="9" t="n"/>
       <c r="E174" s="9" t="n"/>
       <c r="F174" s="9" t="n"/>
@@ -5008,7 +5466,7 @@
     <row r="175">
       <c r="A175" s="9" t="n"/>
       <c r="B175" s="9" t="n"/>
-      <c r="C175" s="31" t="n"/>
+      <c r="C175" s="33" t="n"/>
       <c r="D175" s="9" t="n"/>
       <c r="E175" s="9" t="n"/>
       <c r="F175" s="9" t="n"/>
@@ -5017,7 +5475,7 @@
     <row r="176">
       <c r="A176" s="9" t="n"/>
       <c r="B176" s="9" t="n"/>
-      <c r="C176" s="31" t="n"/>
+      <c r="C176" s="33" t="n"/>
       <c r="D176" s="9" t="n"/>
       <c r="E176" s="9" t="n"/>
       <c r="F176" s="9" t="n"/>
@@ -5026,7 +5484,7 @@
     <row r="177">
       <c r="A177" s="9" t="n"/>
       <c r="B177" s="9" t="n"/>
-      <c r="C177" s="31" t="n"/>
+      <c r="C177" s="33" t="n"/>
       <c r="D177" s="9" t="n"/>
       <c r="E177" s="9" t="n"/>
       <c r="F177" s="9" t="n"/>
@@ -5035,7 +5493,7 @@
     <row r="178">
       <c r="A178" s="9" t="n"/>
       <c r="B178" s="9" t="n"/>
-      <c r="C178" s="31" t="n"/>
+      <c r="C178" s="33" t="n"/>
       <c r="D178" s="9" t="n"/>
       <c r="E178" s="9" t="n"/>
       <c r="F178" s="9" t="n"/>
@@ -5044,7 +5502,7 @@
     <row r="179">
       <c r="A179" s="9" t="n"/>
       <c r="B179" s="9" t="n"/>
-      <c r="C179" s="31" t="n"/>
+      <c r="C179" s="33" t="n"/>
       <c r="D179" s="9" t="n"/>
       <c r="E179" s="9" t="n"/>
       <c r="F179" s="9" t="n"/>
@@ -5053,7 +5511,7 @@
     <row r="180">
       <c r="A180" s="9" t="n"/>
       <c r="B180" s="9" t="n"/>
-      <c r="C180" s="31" t="n"/>
+      <c r="C180" s="33" t="n"/>
       <c r="D180" s="9" t="n"/>
       <c r="E180" s="9" t="n"/>
       <c r="F180" s="9" t="n"/>
@@ -5062,7 +5520,7 @@
     <row r="181">
       <c r="A181" s="9" t="n"/>
       <c r="B181" s="9" t="n"/>
-      <c r="C181" s="31" t="n"/>
+      <c r="C181" s="33" t="n"/>
       <c r="D181" s="9" t="n"/>
       <c r="E181" s="9" t="n"/>
       <c r="F181" s="9" t="n"/>
@@ -5071,7 +5529,7 @@
     <row r="182">
       <c r="A182" s="9" t="n"/>
       <c r="B182" s="9" t="n"/>
-      <c r="C182" s="31" t="n"/>
+      <c r="C182" s="33" t="n"/>
       <c r="D182" s="9" t="n"/>
       <c r="E182" s="9" t="n"/>
       <c r="F182" s="9" t="n"/>
@@ -5080,7 +5538,7 @@
     <row r="183">
       <c r="A183" s="9" t="n"/>
       <c r="B183" s="9" t="n"/>
-      <c r="C183" s="31" t="n"/>
+      <c r="C183" s="33" t="n"/>
       <c r="D183" s="9" t="n"/>
       <c r="E183" s="9" t="n"/>
       <c r="F183" s="9" t="n"/>
@@ -5089,7 +5547,7 @@
     <row r="184">
       <c r="A184" s="9" t="n"/>
       <c r="B184" s="9" t="n"/>
-      <c r="C184" s="31" t="n"/>
+      <c r="C184" s="33" t="n"/>
       <c r="D184" s="9" t="n"/>
       <c r="E184" s="9" t="n"/>
       <c r="F184" s="9" t="n"/>
@@ -5098,7 +5556,7 @@
     <row r="185">
       <c r="A185" s="9" t="n"/>
       <c r="B185" s="9" t="n"/>
-      <c r="C185" s="31" t="n"/>
+      <c r="C185" s="33" t="n"/>
       <c r="D185" s="9" t="n"/>
       <c r="E185" s="9" t="n"/>
       <c r="F185" s="9" t="n"/>
@@ -5107,7 +5565,7 @@
     <row r="186">
       <c r="A186" s="9" t="n"/>
       <c r="B186" s="9" t="n"/>
-      <c r="C186" s="31" t="n"/>
+      <c r="C186" s="33" t="n"/>
       <c r="D186" s="9" t="n"/>
       <c r="E186" s="9" t="n"/>
       <c r="F186" s="9" t="n"/>
@@ -5116,7 +5574,7 @@
     <row r="187">
       <c r="A187" s="9" t="n"/>
       <c r="B187" s="9" t="n"/>
-      <c r="C187" s="31" t="n"/>
+      <c r="C187" s="33" t="n"/>
       <c r="D187" s="9" t="n"/>
       <c r="E187" s="9" t="n"/>
       <c r="F187" s="9" t="n"/>
@@ -5125,7 +5583,7 @@
     <row r="188">
       <c r="A188" s="9" t="n"/>
       <c r="B188" s="9" t="n"/>
-      <c r="C188" s="31" t="n"/>
+      <c r="C188" s="33" t="n"/>
       <c r="D188" s="9" t="n"/>
       <c r="E188" s="9" t="n"/>
       <c r="F188" s="9" t="n"/>
@@ -5134,7 +5592,7 @@
     <row r="189">
       <c r="A189" s="9" t="n"/>
       <c r="B189" s="9" t="n"/>
-      <c r="C189" s="31" t="n"/>
+      <c r="C189" s="33" t="n"/>
       <c r="D189" s="9" t="n"/>
       <c r="E189" s="9" t="n"/>
       <c r="F189" s="9" t="n"/>
@@ -5143,7 +5601,7 @@
     <row r="190">
       <c r="A190" s="9" t="n"/>
       <c r="B190" s="9" t="n"/>
-      <c r="C190" s="31" t="n"/>
+      <c r="C190" s="33" t="n"/>
       <c r="D190" s="9" t="n"/>
       <c r="E190" s="9" t="n"/>
       <c r="F190" s="9" t="n"/>
@@ -5152,7 +5610,7 @@
     <row r="191">
       <c r="A191" s="9" t="n"/>
       <c r="B191" s="9" t="n"/>
-      <c r="C191" s="31" t="n"/>
+      <c r="C191" s="33" t="n"/>
       <c r="D191" s="9" t="n"/>
       <c r="E191" s="9" t="n"/>
       <c r="F191" s="9" t="n"/>
@@ -5161,7 +5619,7 @@
     <row r="192">
       <c r="A192" s="9" t="n"/>
       <c r="B192" s="9" t="n"/>
-      <c r="C192" s="31" t="n"/>
+      <c r="C192" s="33" t="n"/>
       <c r="D192" s="9" t="n"/>
       <c r="E192" s="9" t="n"/>
       <c r="F192" s="9" t="n"/>
@@ -5170,7 +5628,7 @@
     <row r="193">
       <c r="A193" s="9" t="n"/>
       <c r="B193" s="9" t="n"/>
-      <c r="C193" s="31" t="n"/>
+      <c r="C193" s="33" t="n"/>
       <c r="D193" s="9" t="n"/>
       <c r="E193" s="9" t="n"/>
       <c r="F193" s="9" t="n"/>
@@ -5179,7 +5637,7 @@
     <row r="194">
       <c r="A194" s="9" t="n"/>
       <c r="B194" s="9" t="n"/>
-      <c r="C194" s="31" t="n"/>
+      <c r="C194" s="33" t="n"/>
       <c r="D194" s="9" t="n"/>
       <c r="E194" s="9" t="n"/>
       <c r="F194" s="9" t="n"/>
@@ -5188,7 +5646,7 @@
     <row r="195">
       <c r="A195" s="9" t="n"/>
       <c r="B195" s="9" t="n"/>
-      <c r="C195" s="31" t="n"/>
+      <c r="C195" s="33" t="n"/>
       <c r="D195" s="9" t="n"/>
       <c r="E195" s="9" t="n"/>
       <c r="F195" s="9" t="n"/>
@@ -5197,7 +5655,7 @@
     <row r="196">
       <c r="A196" s="9" t="n"/>
       <c r="B196" s="9" t="n"/>
-      <c r="C196" s="31" t="n"/>
+      <c r="C196" s="33" t="n"/>
       <c r="D196" s="9" t="n"/>
       <c r="E196" s="9" t="n"/>
       <c r="F196" s="9" t="n"/>
@@ -5206,7 +5664,7 @@
     <row r="197">
       <c r="A197" s="9" t="n"/>
       <c r="B197" s="9" t="n"/>
-      <c r="C197" s="31" t="n"/>
+      <c r="C197" s="33" t="n"/>
       <c r="D197" s="9" t="n"/>
       <c r="E197" s="9" t="n"/>
       <c r="F197" s="9" t="n"/>
@@ -5215,7 +5673,7 @@
     <row r="198">
       <c r="A198" s="9" t="n"/>
       <c r="B198" s="9" t="n"/>
-      <c r="C198" s="31" t="n"/>
+      <c r="C198" s="33" t="n"/>
       <c r="D198" s="9" t="n"/>
       <c r="E198" s="9" t="n"/>
       <c r="F198" s="9" t="n"/>
@@ -5224,7 +5682,7 @@
     <row r="199">
       <c r="A199" s="9" t="n"/>
       <c r="B199" s="9" t="n"/>
-      <c r="C199" s="31" t="n"/>
+      <c r="C199" s="33" t="n"/>
       <c r="D199" s="9" t="n"/>
       <c r="E199" s="9" t="n"/>
       <c r="F199" s="9" t="n"/>
@@ -5233,7 +5691,7 @@
     <row r="200">
       <c r="A200" s="9" t="n"/>
       <c r="B200" s="9" t="n"/>
-      <c r="C200" s="31" t="n"/>
+      <c r="C200" s="33" t="n"/>
       <c r="D200" s="9" t="n"/>
       <c r="E200" s="9" t="n"/>
       <c r="F200" s="9" t="n"/>
@@ -5242,7 +5700,7 @@
     <row r="201">
       <c r="A201" s="9" t="n"/>
       <c r="B201" s="9" t="n"/>
-      <c r="C201" s="31" t="n"/>
+      <c r="C201" s="33" t="n"/>
       <c r="D201" s="9" t="n"/>
       <c r="E201" s="9" t="n"/>
       <c r="F201" s="9" t="n"/>
@@ -5251,7 +5709,7 @@
     <row r="202">
       <c r="A202" s="9" t="n"/>
       <c r="B202" s="9" t="n"/>
-      <c r="C202" s="31" t="n"/>
+      <c r="C202" s="33" t="n"/>
       <c r="D202" s="9" t="n"/>
       <c r="E202" s="9" t="n"/>
       <c r="F202" s="9" t="n"/>
@@ -5260,7 +5718,7 @@
     <row r="203">
       <c r="A203" s="9" t="n"/>
       <c r="B203" s="9" t="n"/>
-      <c r="C203" s="31" t="n"/>
+      <c r="C203" s="33" t="n"/>
       <c r="D203" s="9" t="n"/>
       <c r="E203" s="9" t="n"/>
       <c r="F203" s="9" t="n"/>
@@ -5269,7 +5727,7 @@
     <row r="204">
       <c r="A204" s="9" t="n"/>
       <c r="B204" s="9" t="n"/>
-      <c r="C204" s="31" t="n"/>
+      <c r="C204" s="33" t="n"/>
       <c r="D204" s="9" t="n"/>
       <c r="E204" s="9" t="n"/>
       <c r="F204" s="9" t="n"/>
@@ -5278,7 +5736,7 @@
     <row r="205">
       <c r="A205" s="9" t="n"/>
       <c r="B205" s="9" t="n"/>
-      <c r="C205" s="31" t="n"/>
+      <c r="C205" s="33" t="n"/>
       <c r="D205" s="9" t="n"/>
       <c r="E205" s="9" t="n"/>
       <c r="F205" s="9" t="n"/>
@@ -5287,7 +5745,7 @@
     <row r="206">
       <c r="A206" s="9" t="n"/>
       <c r="B206" s="9" t="n"/>
-      <c r="C206" s="31" t="n"/>
+      <c r="C206" s="33" t="n"/>
       <c r="D206" s="9" t="n"/>
       <c r="E206" s="9" t="n"/>
       <c r="F206" s="9" t="n"/>
@@ -5296,7 +5754,7 @@
     <row r="207">
       <c r="A207" s="9" t="n"/>
       <c r="B207" s="9" t="n"/>
-      <c r="C207" s="31" t="n"/>
+      <c r="C207" s="33" t="n"/>
       <c r="D207" s="9" t="n"/>
       <c r="E207" s="9" t="n"/>
       <c r="F207" s="9" t="n"/>
@@ -5305,7 +5763,7 @@
     <row r="208">
       <c r="A208" s="9" t="n"/>
       <c r="B208" s="9" t="n"/>
-      <c r="C208" s="31" t="n"/>
+      <c r="C208" s="33" t="n"/>
       <c r="D208" s="9" t="n"/>
       <c r="E208" s="9" t="n"/>
       <c r="F208" s="9" t="n"/>
@@ -5314,7 +5772,7 @@
     <row r="209">
       <c r="A209" s="9" t="n"/>
       <c r="B209" s="9" t="n"/>
-      <c r="C209" s="31" t="n"/>
+      <c r="C209" s="33" t="n"/>
       <c r="D209" s="9" t="n"/>
       <c r="E209" s="9" t="n"/>
       <c r="F209" s="9" t="n"/>
@@ -5323,7 +5781,7 @@
     <row r="210">
       <c r="A210" s="9" t="n"/>
       <c r="B210" s="9" t="n"/>
-      <c r="C210" s="31" t="n"/>
+      <c r="C210" s="33" t="n"/>
       <c r="D210" s="9" t="n"/>
       <c r="E210" s="9" t="n"/>
       <c r="F210" s="9" t="n"/>
@@ -5332,7 +5790,7 @@
     <row r="211">
       <c r="A211" s="9" t="n"/>
       <c r="B211" s="9" t="n"/>
-      <c r="C211" s="31" t="n"/>
+      <c r="C211" s="33" t="n"/>
       <c r="D211" s="9" t="n"/>
       <c r="E211" s="9" t="n"/>
       <c r="F211" s="9" t="n"/>
@@ -5341,7 +5799,7 @@
     <row r="212">
       <c r="A212" s="9" t="n"/>
       <c r="B212" s="9" t="n"/>
-      <c r="C212" s="31" t="n"/>
+      <c r="C212" s="33" t="n"/>
       <c r="D212" s="9" t="n"/>
       <c r="E212" s="9" t="n"/>
       <c r="F212" s="9" t="n"/>
@@ -5350,7 +5808,7 @@
     <row r="213">
       <c r="A213" s="9" t="n"/>
       <c r="B213" s="9" t="n"/>
-      <c r="C213" s="31" t="n"/>
+      <c r="C213" s="33" t="n"/>
       <c r="D213" s="9" t="n"/>
       <c r="E213" s="9" t="n"/>
       <c r="F213" s="9" t="n"/>
@@ -5359,7 +5817,7 @@
     <row r="214">
       <c r="A214" s="9" t="n"/>
       <c r="B214" s="9" t="n"/>
-      <c r="C214" s="31" t="n"/>
+      <c r="C214" s="33" t="n"/>
       <c r="D214" s="9" t="n"/>
       <c r="E214" s="9" t="n"/>
       <c r="F214" s="9" t="n"/>
@@ -5368,7 +5826,7 @@
     <row r="215">
       <c r="A215" s="9" t="n"/>
       <c r="B215" s="9" t="n"/>
-      <c r="C215" s="31" t="n"/>
+      <c r="C215" s="33" t="n"/>
       <c r="D215" s="9" t="n"/>
       <c r="E215" s="9" t="n"/>
       <c r="F215" s="9" t="n"/>
@@ -5377,7 +5835,7 @@
     <row r="216">
       <c r="A216" s="9" t="n"/>
       <c r="B216" s="9" t="n"/>
-      <c r="C216" s="31" t="n"/>
+      <c r="C216" s="33" t="n"/>
       <c r="D216" s="9" t="n"/>
       <c r="E216" s="9" t="n"/>
       <c r="F216" s="9" t="n"/>
@@ -5386,7 +5844,7 @@
     <row r="217">
       <c r="A217" s="9" t="n"/>
       <c r="B217" s="9" t="n"/>
-      <c r="C217" s="31" t="n"/>
+      <c r="C217" s="33" t="n"/>
       <c r="D217" s="9" t="n"/>
       <c r="E217" s="9" t="n"/>
       <c r="F217" s="9" t="n"/>
@@ -5395,7 +5853,7 @@
     <row r="218">
       <c r="A218" s="9" t="n"/>
       <c r="B218" s="9" t="n"/>
-      <c r="C218" s="31" t="n"/>
+      <c r="C218" s="33" t="n"/>
       <c r="D218" s="9" t="n"/>
       <c r="E218" s="9" t="n"/>
       <c r="F218" s="9" t="n"/>
@@ -5404,7 +5862,7 @@
     <row r="219">
       <c r="A219" s="9" t="n"/>
       <c r="B219" s="9" t="n"/>
-      <c r="C219" s="31" t="n"/>
+      <c r="C219" s="33" t="n"/>
       <c r="D219" s="9" t="n"/>
       <c r="E219" s="9" t="n"/>
       <c r="F219" s="9" t="n"/>
@@ -5413,7 +5871,7 @@
     <row r="220">
       <c r="A220" s="9" t="n"/>
       <c r="B220" s="9" t="n"/>
-      <c r="C220" s="31" t="n"/>
+      <c r="C220" s="33" t="n"/>
       <c r="D220" s="9" t="n"/>
       <c r="E220" s="9" t="n"/>
       <c r="F220" s="9" t="n"/>
@@ -5422,7 +5880,7 @@
     <row r="221">
       <c r="A221" s="9" t="n"/>
       <c r="B221" s="9" t="n"/>
-      <c r="C221" s="31" t="n"/>
+      <c r="C221" s="33" t="n"/>
       <c r="D221" s="9" t="n"/>
       <c r="E221" s="9" t="n"/>
       <c r="F221" s="9" t="n"/>
@@ -5431,7 +5889,7 @@
     <row r="222">
       <c r="A222" s="9" t="n"/>
       <c r="B222" s="9" t="n"/>
-      <c r="C222" s="31" t="n"/>
+      <c r="C222" s="33" t="n"/>
       <c r="D222" s="9" t="n"/>
       <c r="E222" s="9" t="n"/>
       <c r="F222" s="9" t="n"/>
@@ -5440,7 +5898,7 @@
     <row r="223">
       <c r="A223" s="9" t="n"/>
       <c r="B223" s="9" t="n"/>
-      <c r="C223" s="31" t="n"/>
+      <c r="C223" s="33" t="n"/>
       <c r="D223" s="9" t="n"/>
       <c r="E223" s="9" t="n"/>
       <c r="F223" s="9" t="n"/>
@@ -5449,7 +5907,7 @@
     <row r="224">
       <c r="A224" s="9" t="n"/>
       <c r="B224" s="9" t="n"/>
-      <c r="C224" s="31" t="n"/>
+      <c r="C224" s="33" t="n"/>
       <c r="D224" s="9" t="n"/>
       <c r="E224" s="9" t="n"/>
       <c r="F224" s="9" t="n"/>
@@ -5458,7 +5916,7 @@
     <row r="225">
       <c r="A225" s="9" t="n"/>
       <c r="B225" s="9" t="n"/>
-      <c r="C225" s="31" t="n"/>
+      <c r="C225" s="33" t="n"/>
       <c r="D225" s="9" t="n"/>
       <c r="E225" s="9" t="n"/>
       <c r="F225" s="9" t="n"/>
@@ -5467,7 +5925,7 @@
     <row r="226">
       <c r="A226" s="9" t="n"/>
       <c r="B226" s="9" t="n"/>
-      <c r="C226" s="31" t="n"/>
+      <c r="C226" s="33" t="n"/>
       <c r="D226" s="9" t="n"/>
       <c r="E226" s="9" t="n"/>
       <c r="F226" s="9" t="n"/>
@@ -5476,7 +5934,7 @@
     <row r="227">
       <c r="A227" s="9" t="n"/>
       <c r="B227" s="9" t="n"/>
-      <c r="C227" s="31" t="n"/>
+      <c r="C227" s="33" t="n"/>
       <c r="D227" s="9" t="n"/>
       <c r="E227" s="9" t="n"/>
       <c r="F227" s="9" t="n"/>
@@ -5485,7 +5943,7 @@
     <row r="228">
       <c r="A228" s="9" t="n"/>
       <c r="B228" s="9" t="n"/>
-      <c r="C228" s="31" t="n"/>
+      <c r="C228" s="33" t="n"/>
       <c r="D228" s="9" t="n"/>
       <c r="E228" s="9" t="n"/>
       <c r="F228" s="9" t="n"/>
@@ -5494,7 +5952,7 @@
     <row r="229">
       <c r="A229" s="9" t="n"/>
       <c r="B229" s="9" t="n"/>
-      <c r="C229" s="31" t="n"/>
+      <c r="C229" s="33" t="n"/>
       <c r="D229" s="9" t="n"/>
       <c r="E229" s="9" t="n"/>
       <c r="F229" s="9" t="n"/>
@@ -5503,7 +5961,7 @@
     <row r="230">
       <c r="A230" s="9" t="n"/>
       <c r="B230" s="9" t="n"/>
-      <c r="C230" s="31" t="n"/>
+      <c r="C230" s="33" t="n"/>
       <c r="D230" s="9" t="n"/>
       <c r="E230" s="9" t="n"/>
       <c r="F230" s="9" t="n"/>
@@ -5512,7 +5970,7 @@
     <row r="231">
       <c r="A231" s="9" t="n"/>
       <c r="B231" s="9" t="n"/>
-      <c r="C231" s="31" t="n"/>
+      <c r="C231" s="33" t="n"/>
       <c r="D231" s="9" t="n"/>
       <c r="E231" s="9" t="n"/>
       <c r="F231" s="9" t="n"/>
@@ -5521,7 +5979,7 @@
     <row r="232">
       <c r="A232" s="9" t="n"/>
       <c r="B232" s="9" t="n"/>
-      <c r="C232" s="31" t="n"/>
+      <c r="C232" s="33" t="n"/>
       <c r="D232" s="9" t="n"/>
       <c r="E232" s="9" t="n"/>
       <c r="F232" s="9" t="n"/>
@@ -5530,7 +5988,7 @@
     <row r="233">
       <c r="A233" s="9" t="n"/>
       <c r="B233" s="9" t="n"/>
-      <c r="C233" s="31" t="n"/>
+      <c r="C233" s="33" t="n"/>
       <c r="D233" s="9" t="n"/>
       <c r="E233" s="9" t="n"/>
       <c r="F233" s="9" t="n"/>
@@ -5539,7 +5997,7 @@
     <row r="234">
       <c r="A234" s="9" t="n"/>
       <c r="B234" s="9" t="n"/>
-      <c r="C234" s="31" t="n"/>
+      <c r="C234" s="33" t="n"/>
       <c r="D234" s="9" t="n"/>
       <c r="E234" s="9" t="n"/>
       <c r="F234" s="9" t="n"/>
@@ -5548,7 +6006,7 @@
     <row r="235">
       <c r="A235" s="9" t="n"/>
       <c r="B235" s="9" t="n"/>
-      <c r="C235" s="31" t="n"/>
+      <c r="C235" s="33" t="n"/>
       <c r="D235" s="9" t="n"/>
       <c r="E235" s="9" t="n"/>
       <c r="F235" s="9" t="n"/>
@@ -5557,7 +6015,7 @@
     <row r="236">
       <c r="A236" s="9" t="n"/>
       <c r="B236" s="9" t="n"/>
-      <c r="C236" s="31" t="n"/>
+      <c r="C236" s="33" t="n"/>
       <c r="D236" s="9" t="n"/>
       <c r="E236" s="9" t="n"/>
       <c r="F236" s="9" t="n"/>
@@ -5566,7 +6024,7 @@
     <row r="237">
       <c r="A237" s="9" t="n"/>
       <c r="B237" s="9" t="n"/>
-      <c r="C237" s="31" t="n"/>
+      <c r="C237" s="33" t="n"/>
       <c r="D237" s="9" t="n"/>
       <c r="E237" s="9" t="n"/>
       <c r="F237" s="9" t="n"/>
@@ -5575,7 +6033,7 @@
     <row r="238">
       <c r="A238" s="9" t="n"/>
       <c r="B238" s="9" t="n"/>
-      <c r="C238" s="31" t="n"/>
+      <c r="C238" s="33" t="n"/>
       <c r="D238" s="9" t="n"/>
       <c r="E238" s="9" t="n"/>
       <c r="F238" s="9" t="n"/>
@@ -5584,7 +6042,7 @@
     <row r="239">
       <c r="A239" s="9" t="n"/>
       <c r="B239" s="9" t="n"/>
-      <c r="C239" s="31" t="n"/>
+      <c r="C239" s="33" t="n"/>
       <c r="D239" s="9" t="n"/>
       <c r="E239" s="9" t="n"/>
       <c r="F239" s="9" t="n"/>
@@ -5593,7 +6051,7 @@
     <row r="240">
       <c r="A240" s="9" t="n"/>
       <c r="B240" s="9" t="n"/>
-      <c r="C240" s="31" t="n"/>
+      <c r="C240" s="33" t="n"/>
       <c r="D240" s="9" t="n"/>
       <c r="E240" s="9" t="n"/>
       <c r="F240" s="9" t="n"/>
@@ -5602,7 +6060,7 @@
     <row r="241">
       <c r="A241" s="9" t="n"/>
       <c r="B241" s="9" t="n"/>
-      <c r="C241" s="31" t="n"/>
+      <c r="C241" s="33" t="n"/>
       <c r="D241" s="9" t="n"/>
       <c r="E241" s="9" t="n"/>
       <c r="F241" s="9" t="n"/>
@@ -5611,7 +6069,7 @@
     <row r="242">
       <c r="A242" s="9" t="n"/>
       <c r="B242" s="9" t="n"/>
-      <c r="C242" s="31" t="n"/>
+      <c r="C242" s="33" t="n"/>
       <c r="D242" s="9" t="n"/>
       <c r="E242" s="9" t="n"/>
       <c r="F242" s="9" t="n"/>
@@ -5620,7 +6078,7 @@
     <row r="243">
       <c r="A243" s="9" t="n"/>
       <c r="B243" s="9" t="n"/>
-      <c r="C243" s="31" t="n"/>
+      <c r="C243" s="33" t="n"/>
       <c r="D243" s="9" t="n"/>
       <c r="E243" s="9" t="n"/>
       <c r="F243" s="9" t="n"/>
@@ -5629,7 +6087,7 @@
     <row r="244">
       <c r="A244" s="9" t="n"/>
       <c r="B244" s="9" t="n"/>
-      <c r="C244" s="31" t="n"/>
+      <c r="C244" s="33" t="n"/>
       <c r="D244" s="9" t="n"/>
       <c r="E244" s="9" t="n"/>
       <c r="F244" s="9" t="n"/>
@@ -5638,7 +6096,7 @@
     <row r="245">
       <c r="A245" s="9" t="n"/>
       <c r="B245" s="9" t="n"/>
-      <c r="C245" s="31" t="n"/>
+      <c r="C245" s="33" t="n"/>
       <c r="D245" s="9" t="n"/>
       <c r="E245" s="9" t="n"/>
       <c r="F245" s="9" t="n"/>
@@ -5647,7 +6105,7 @@
     <row r="246">
       <c r="A246" s="9" t="n"/>
       <c r="B246" s="9" t="n"/>
-      <c r="C246" s="31" t="n"/>
+      <c r="C246" s="33" t="n"/>
       <c r="D246" s="9" t="n"/>
       <c r="E246" s="9" t="n"/>
       <c r="F246" s="9" t="n"/>
@@ -5656,7 +6114,7 @@
     <row r="247">
       <c r="A247" s="9" t="n"/>
       <c r="B247" s="9" t="n"/>
-      <c r="C247" s="31" t="n"/>
+      <c r="C247" s="33" t="n"/>
       <c r="D247" s="9" t="n"/>
       <c r="E247" s="9" t="n"/>
       <c r="F247" s="9" t="n"/>
@@ -5665,7 +6123,7 @@
     <row r="248">
       <c r="A248" s="9" t="n"/>
       <c r="B248" s="9" t="n"/>
-      <c r="C248" s="31" t="n"/>
+      <c r="C248" s="33" t="n"/>
       <c r="D248" s="9" t="n"/>
       <c r="E248" s="9" t="n"/>
       <c r="F248" s="9" t="n"/>
@@ -5674,7 +6132,7 @@
     <row r="249">
       <c r="A249" s="9" t="n"/>
       <c r="B249" s="9" t="n"/>
-      <c r="C249" s="31" t="n"/>
+      <c r="C249" s="33" t="n"/>
       <c r="D249" s="9" t="n"/>
       <c r="E249" s="9" t="n"/>
       <c r="F249" s="9" t="n"/>
@@ -5683,7 +6141,7 @@
     <row r="250">
       <c r="A250" s="9" t="n"/>
       <c r="B250" s="9" t="n"/>
-      <c r="C250" s="31" t="n"/>
+      <c r="C250" s="33" t="n"/>
       <c r="D250" s="9" t="n"/>
       <c r="E250" s="9" t="n"/>
       <c r="F250" s="9" t="n"/>
@@ -5692,7 +6150,7 @@
     <row r="251">
       <c r="A251" s="9" t="n"/>
       <c r="B251" s="9" t="n"/>
-      <c r="C251" s="31" t="n"/>
+      <c r="C251" s="33" t="n"/>
       <c r="D251" s="9" t="n"/>
       <c r="E251" s="9" t="n"/>
       <c r="F251" s="9" t="n"/>
@@ -5701,7 +6159,7 @@
     <row r="252">
       <c r="A252" s="9" t="n"/>
       <c r="B252" s="9" t="n"/>
-      <c r="C252" s="31" t="n"/>
+      <c r="C252" s="33" t="n"/>
       <c r="D252" s="9" t="n"/>
       <c r="E252" s="9" t="n"/>
       <c r="F252" s="9" t="n"/>
@@ -5710,7 +6168,7 @@
     <row r="253">
       <c r="A253" s="9" t="n"/>
       <c r="B253" s="9" t="n"/>
-      <c r="C253" s="31" t="n"/>
+      <c r="C253" s="33" t="n"/>
       <c r="D253" s="9" t="n"/>
       <c r="E253" s="9" t="n"/>
       <c r="F253" s="9" t="n"/>
@@ -5719,7 +6177,7 @@
     <row r="254">
       <c r="A254" s="9" t="n"/>
       <c r="B254" s="9" t="n"/>
-      <c r="C254" s="31" t="n"/>
+      <c r="C254" s="33" t="n"/>
       <c r="D254" s="9" t="n"/>
       <c r="E254" s="9" t="n"/>
       <c r="F254" s="9" t="n"/>
@@ -5728,7 +6186,7 @@
     <row r="255">
       <c r="A255" s="9" t="n"/>
       <c r="B255" s="9" t="n"/>
-      <c r="C255" s="31" t="n"/>
+      <c r="C255" s="33" t="n"/>
       <c r="D255" s="9" t="n"/>
       <c r="E255" s="9" t="n"/>
       <c r="F255" s="9" t="n"/>
@@ -5737,7 +6195,7 @@
     <row r="256">
       <c r="A256" s="9" t="n"/>
       <c r="B256" s="9" t="n"/>
-      <c r="C256" s="31" t="n"/>
+      <c r="C256" s="33" t="n"/>
       <c r="D256" s="9" t="n"/>
       <c r="E256" s="9" t="n"/>
       <c r="F256" s="9" t="n"/>
@@ -5746,7 +6204,7 @@
     <row r="257">
       <c r="A257" s="9" t="n"/>
       <c r="B257" s="9" t="n"/>
-      <c r="C257" s="31" t="n"/>
+      <c r="C257" s="33" t="n"/>
       <c r="D257" s="9" t="n"/>
       <c r="E257" s="9" t="n"/>
       <c r="F257" s="9" t="n"/>
@@ -5755,7 +6213,7 @@
     <row r="258">
       <c r="A258" s="9" t="n"/>
       <c r="B258" s="9" t="n"/>
-      <c r="C258" s="31" t="n"/>
+      <c r="C258" s="33" t="n"/>
       <c r="D258" s="9" t="n"/>
       <c r="E258" s="9" t="n"/>
       <c r="F258" s="9" t="n"/>
@@ -5764,7 +6222,7 @@
     <row r="259">
       <c r="A259" s="9" t="n"/>
       <c r="B259" s="9" t="n"/>
-      <c r="C259" s="31" t="n"/>
+      <c r="C259" s="33" t="n"/>
       <c r="D259" s="9" t="n"/>
       <c r="E259" s="9" t="n"/>
       <c r="F259" s="9" t="n"/>
@@ -5773,7 +6231,7 @@
     <row r="260">
       <c r="A260" s="9" t="n"/>
       <c r="B260" s="9" t="n"/>
-      <c r="C260" s="31" t="n"/>
+      <c r="C260" s="33" t="n"/>
       <c r="D260" s="9" t="n"/>
       <c r="E260" s="9" t="n"/>
       <c r="F260" s="9" t="n"/>
@@ -5782,7 +6240,7 @@
     <row r="261">
       <c r="A261" s="9" t="n"/>
       <c r="B261" s="9" t="n"/>
-      <c r="C261" s="31" t="n"/>
+      <c r="C261" s="33" t="n"/>
       <c r="D261" s="9" t="n"/>
       <c r="E261" s="9" t="n"/>
       <c r="F261" s="9" t="n"/>
@@ -5791,7 +6249,7 @@
     <row r="262">
       <c r="A262" s="9" t="n"/>
       <c r="B262" s="9" t="n"/>
-      <c r="C262" s="31" t="n"/>
+      <c r="C262" s="33" t="n"/>
       <c r="D262" s="9" t="n"/>
       <c r="E262" s="9" t="n"/>
       <c r="F262" s="9" t="n"/>
@@ -5800,7 +6258,7 @@
     <row r="263">
       <c r="A263" s="9" t="n"/>
       <c r="B263" s="9" t="n"/>
-      <c r="C263" s="31" t="n"/>
+      <c r="C263" s="33" t="n"/>
       <c r="D263" s="9" t="n"/>
       <c r="E263" s="9" t="n"/>
       <c r="F263" s="9" t="n"/>
@@ -5809,7 +6267,7 @@
     <row r="264">
       <c r="A264" s="9" t="n"/>
       <c r="B264" s="9" t="n"/>
-      <c r="C264" s="31" t="n"/>
+      <c r="C264" s="33" t="n"/>
       <c r="D264" s="9" t="n"/>
       <c r="E264" s="9" t="n"/>
       <c r="F264" s="9" t="n"/>
@@ -5818,7 +6276,7 @@
     <row r="265">
       <c r="A265" s="9" t="n"/>
       <c r="B265" s="9" t="n"/>
-      <c r="C265" s="31" t="n"/>
+      <c r="C265" s="33" t="n"/>
       <c r="D265" s="9" t="n"/>
       <c r="E265" s="9" t="n"/>
       <c r="F265" s="9" t="n"/>
@@ -5827,7 +6285,7 @@
     <row r="266">
       <c r="A266" s="9" t="n"/>
       <c r="B266" s="9" t="n"/>
-      <c r="C266" s="31" t="n"/>
+      <c r="C266" s="33" t="n"/>
       <c r="D266" s="9" t="n"/>
       <c r="E266" s="9" t="n"/>
       <c r="F266" s="9" t="n"/>
@@ -5836,7 +6294,7 @@
     <row r="267">
       <c r="A267" s="9" t="n"/>
       <c r="B267" s="9" t="n"/>
-      <c r="C267" s="31" t="n"/>
+      <c r="C267" s="33" t="n"/>
       <c r="D267" s="9" t="n"/>
       <c r="E267" s="9" t="n"/>
       <c r="F267" s="9" t="n"/>
@@ -5845,7 +6303,7 @@
     <row r="268">
       <c r="A268" s="9" t="n"/>
       <c r="B268" s="9" t="n"/>
-      <c r="C268" s="31" t="n"/>
+      <c r="C268" s="33" t="n"/>
       <c r="D268" s="9" t="n"/>
       <c r="E268" s="9" t="n"/>
       <c r="F268" s="9" t="n"/>
@@ -5854,7 +6312,7 @@
     <row r="269">
       <c r="A269" s="9" t="n"/>
       <c r="B269" s="9" t="n"/>
-      <c r="C269" s="31" t="n"/>
+      <c r="C269" s="33" t="n"/>
       <c r="D269" s="9" t="n"/>
       <c r="E269" s="9" t="n"/>
       <c r="F269" s="9" t="n"/>
@@ -5863,7 +6321,7 @@
     <row r="270">
       <c r="A270" s="9" t="n"/>
       <c r="B270" s="9" t="n"/>
-      <c r="C270" s="31" t="n"/>
+      <c r="C270" s="33" t="n"/>
       <c r="D270" s="9" t="n"/>
       <c r="E270" s="9" t="n"/>
       <c r="F270" s="9" t="n"/>
@@ -5872,7 +6330,7 @@
     <row r="271">
       <c r="A271" s="9" t="n"/>
       <c r="B271" s="9" t="n"/>
-      <c r="C271" s="31" t="n"/>
+      <c r="C271" s="33" t="n"/>
       <c r="D271" s="9" t="n"/>
       <c r="E271" s="9" t="n"/>
       <c r="F271" s="9" t="n"/>
@@ -5881,7 +6339,7 @@
     <row r="272">
       <c r="A272" s="9" t="n"/>
       <c r="B272" s="9" t="n"/>
-      <c r="C272" s="31" t="n"/>
+      <c r="C272" s="33" t="n"/>
       <c r="D272" s="9" t="n"/>
       <c r="E272" s="9" t="n"/>
       <c r="F272" s="9" t="n"/>
@@ -5890,7 +6348,7 @@
     <row r="273">
       <c r="A273" s="9" t="n"/>
       <c r="B273" s="9" t="n"/>
-      <c r="C273" s="31" t="n"/>
+      <c r="C273" s="33" t="n"/>
       <c r="D273" s="9" t="n"/>
       <c r="E273" s="9" t="n"/>
       <c r="F273" s="9" t="n"/>
@@ -5899,7 +6357,7 @@
     <row r="274">
       <c r="A274" s="9" t="n"/>
       <c r="B274" s="9" t="n"/>
-      <c r="C274" s="31" t="n"/>
+      <c r="C274" s="33" t="n"/>
       <c r="D274" s="9" t="n"/>
       <c r="E274" s="9" t="n"/>
       <c r="F274" s="9" t="n"/>
@@ -5908,7 +6366,7 @@
     <row r="275">
       <c r="A275" s="9" t="n"/>
       <c r="B275" s="9" t="n"/>
-      <c r="C275" s="31" t="n"/>
+      <c r="C275" s="33" t="n"/>
       <c r="D275" s="9" t="n"/>
       <c r="E275" s="9" t="n"/>
       <c r="F275" s="9" t="n"/>
@@ -5917,7 +6375,7 @@
     <row r="276">
       <c r="A276" s="9" t="n"/>
       <c r="B276" s="9" t="n"/>
-      <c r="C276" s="31" t="n"/>
+      <c r="C276" s="33" t="n"/>
       <c r="D276" s="9" t="n"/>
       <c r="E276" s="9" t="n"/>
       <c r="F276" s="9" t="n"/>
@@ -5926,7 +6384,7 @@
     <row r="277">
       <c r="A277" s="9" t="n"/>
       <c r="B277" s="9" t="n"/>
-      <c r="C277" s="31" t="n"/>
+      <c r="C277" s="33" t="n"/>
       <c r="D277" s="9" t="n"/>
       <c r="E277" s="9" t="n"/>
       <c r="F277" s="9" t="n"/>
@@ -5935,7 +6393,7 @@
     <row r="278">
       <c r="A278" s="9" t="n"/>
       <c r="B278" s="9" t="n"/>
-      <c r="C278" s="31" t="n"/>
+      <c r="C278" s="33" t="n"/>
       <c r="D278" s="9" t="n"/>
       <c r="E278" s="9" t="n"/>
       <c r="F278" s="9" t="n"/>
@@ -5944,7 +6402,7 @@
     <row r="279">
       <c r="A279" s="9" t="n"/>
       <c r="B279" s="9" t="n"/>
-      <c r="C279" s="31" t="n"/>
+      <c r="C279" s="33" t="n"/>
       <c r="D279" s="9" t="n"/>
       <c r="E279" s="9" t="n"/>
       <c r="F279" s="9" t="n"/>
@@ -5953,7 +6411,7 @@
     <row r="280">
       <c r="A280" s="9" t="n"/>
       <c r="B280" s="9" t="n"/>
-      <c r="C280" s="31" t="n"/>
+      <c r="C280" s="33" t="n"/>
       <c r="D280" s="9" t="n"/>
       <c r="E280" s="9" t="n"/>
       <c r="F280" s="9" t="n"/>
@@ -5962,7 +6420,7 @@
     <row r="281">
       <c r="A281" s="9" t="n"/>
       <c r="B281" s="9" t="n"/>
-      <c r="C281" s="31" t="n"/>
+      <c r="C281" s="33" t="n"/>
       <c r="D281" s="9" t="n"/>
       <c r="E281" s="9" t="n"/>
       <c r="F281" s="9" t="n"/>
@@ -5971,7 +6429,7 @@
     <row r="282">
       <c r="A282" s="9" t="n"/>
       <c r="B282" s="9" t="n"/>
-      <c r="C282" s="31" t="n"/>
+      <c r="C282" s="33" t="n"/>
       <c r="D282" s="9" t="n"/>
       <c r="E282" s="9" t="n"/>
       <c r="F282" s="9" t="n"/>
@@ -5980,7 +6438,7 @@
     <row r="283">
       <c r="A283" s="9" t="n"/>
       <c r="B283" s="9" t="n"/>
-      <c r="C283" s="31" t="n"/>
+      <c r="C283" s="33" t="n"/>
       <c r="D283" s="9" t="n"/>
       <c r="E283" s="9" t="n"/>
       <c r="F283" s="9" t="n"/>
@@ -5989,7 +6447,7 @@
     <row r="284">
       <c r="A284" s="9" t="n"/>
       <c r="B284" s="9" t="n"/>
-      <c r="C284" s="31" t="n"/>
+      <c r="C284" s="33" t="n"/>
       <c r="D284" s="9" t="n"/>
       <c r="E284" s="9" t="n"/>
       <c r="F284" s="9" t="n"/>
@@ -5998,7 +6456,7 @@
     <row r="285">
       <c r="A285" s="9" t="n"/>
       <c r="B285" s="9" t="n"/>
-      <c r="C285" s="31" t="n"/>
+      <c r="C285" s="33" t="n"/>
       <c r="D285" s="9" t="n"/>
       <c r="E285" s="9" t="n"/>
       <c r="F285" s="9" t="n"/>
@@ -6007,7 +6465,7 @@
     <row r="286">
       <c r="A286" s="9" t="n"/>
       <c r="B286" s="9" t="n"/>
-      <c r="C286" s="31" t="n"/>
+      <c r="C286" s="33" t="n"/>
       <c r="D286" s="9" t="n"/>
       <c r="E286" s="9" t="n"/>
       <c r="F286" s="9" t="n"/>
@@ -6016,7 +6474,7 @@
     <row r="287">
       <c r="A287" s="9" t="n"/>
       <c r="B287" s="9" t="n"/>
-      <c r="C287" s="31" t="n"/>
+      <c r="C287" s="33" t="n"/>
       <c r="D287" s="9" t="n"/>
       <c r="E287" s="9" t="n"/>
       <c r="F287" s="9" t="n"/>
@@ -6025,7 +6483,7 @@
     <row r="288">
       <c r="A288" s="9" t="n"/>
       <c r="B288" s="9" t="n"/>
-      <c r="C288" s="31" t="n"/>
+      <c r="C288" s="33" t="n"/>
       <c r="D288" s="9" t="n"/>
       <c r="E288" s="9" t="n"/>
       <c r="F288" s="9" t="n"/>
@@ -6034,7 +6492,7 @@
     <row r="289">
       <c r="A289" s="9" t="n"/>
       <c r="B289" s="9" t="n"/>
-      <c r="C289" s="31" t="n"/>
+      <c r="C289" s="33" t="n"/>
       <c r="D289" s="9" t="n"/>
       <c r="E289" s="9" t="n"/>
       <c r="F289" s="9" t="n"/>
@@ -6043,7 +6501,7 @@
     <row r="290">
       <c r="A290" s="9" t="n"/>
       <c r="B290" s="9" t="n"/>
-      <c r="C290" s="31" t="n"/>
+      <c r="C290" s="33" t="n"/>
       <c r="D290" s="9" t="n"/>
       <c r="E290" s="9" t="n"/>
       <c r="F290" s="9" t="n"/>
@@ -6052,7 +6510,7 @@
     <row r="291">
       <c r="A291" s="9" t="n"/>
       <c r="B291" s="9" t="n"/>
-      <c r="C291" s="31" t="n"/>
+      <c r="C291" s="33" t="n"/>
       <c r="D291" s="9" t="n"/>
       <c r="E291" s="9" t="n"/>
       <c r="F291" s="9" t="n"/>
@@ -6061,7 +6519,7 @@
     <row r="292">
       <c r="A292" s="9" t="n"/>
       <c r="B292" s="9" t="n"/>
-      <c r="C292" s="31" t="n"/>
+      <c r="C292" s="33" t="n"/>
       <c r="D292" s="9" t="n"/>
       <c r="E292" s="9" t="n"/>
       <c r="F292" s="9" t="n"/>
@@ -6070,7 +6528,7 @@
     <row r="293">
       <c r="A293" s="9" t="n"/>
       <c r="B293" s="9" t="n"/>
-      <c r="C293" s="31" t="n"/>
+      <c r="C293" s="33" t="n"/>
       <c r="D293" s="9" t="n"/>
       <c r="E293" s="9" t="n"/>
       <c r="F293" s="9" t="n"/>
@@ -6079,7 +6537,7 @@
     <row r="294">
       <c r="A294" s="9" t="n"/>
       <c r="B294" s="9" t="n"/>
-      <c r="C294" s="31" t="n"/>
+      <c r="C294" s="33" t="n"/>
       <c r="D294" s="9" t="n"/>
       <c r="E294" s="9" t="n"/>
       <c r="F294" s="9" t="n"/>
@@ -6088,7 +6546,7 @@
     <row r="295">
       <c r="A295" s="9" t="n"/>
       <c r="B295" s="9" t="n"/>
-      <c r="C295" s="31" t="n"/>
+      <c r="C295" s="33" t="n"/>
       <c r="D295" s="9" t="n"/>
       <c r="E295" s="9" t="n"/>
       <c r="F295" s="9" t="n"/>
@@ -6097,7 +6555,7 @@
     <row r="296">
       <c r="A296" s="9" t="n"/>
       <c r="B296" s="9" t="n"/>
-      <c r="C296" s="31" t="n"/>
+      <c r="C296" s="33" t="n"/>
       <c r="D296" s="9" t="n"/>
       <c r="E296" s="9" t="n"/>
       <c r="F296" s="9" t="n"/>
@@ -6106,7 +6564,7 @@
     <row r="297">
       <c r="A297" s="9" t="n"/>
       <c r="B297" s="9" t="n"/>
-      <c r="C297" s="31" t="n"/>
+      <c r="C297" s="33" t="n"/>
       <c r="D297" s="9" t="n"/>
       <c r="E297" s="9" t="n"/>
       <c r="F297" s="9" t="n"/>
@@ -6115,7 +6573,7 @@
     <row r="298">
       <c r="A298" s="9" t="n"/>
       <c r="B298" s="9" t="n"/>
-      <c r="C298" s="31" t="n"/>
+      <c r="C298" s="33" t="n"/>
       <c r="D298" s="9" t="n"/>
       <c r="E298" s="9" t="n"/>
       <c r="F298" s="9" t="n"/>
@@ -6124,7 +6582,7 @@
     <row r="299">
       <c r="A299" s="9" t="n"/>
       <c r="B299" s="9" t="n"/>
-      <c r="C299" s="31" t="n"/>
+      <c r="C299" s="33" t="n"/>
       <c r="D299" s="9" t="n"/>
       <c r="E299" s="9" t="n"/>
       <c r="F299" s="9" t="n"/>
@@ -6133,7 +6591,7 @@
     <row r="300">
       <c r="A300" s="9" t="n"/>
       <c r="B300" s="9" t="n"/>
-      <c r="C300" s="31" t="n"/>
+      <c r="C300" s="33" t="n"/>
       <c r="D300" s="9" t="n"/>
       <c r="E300" s="9" t="n"/>
       <c r="F300" s="9" t="n"/>
@@ -6142,7 +6600,7 @@
     <row r="301">
       <c r="A301" s="9" t="n"/>
       <c r="B301" s="9" t="n"/>
-      <c r="C301" s="31" t="n"/>
+      <c r="C301" s="33" t="n"/>
       <c r="D301" s="9" t="n"/>
       <c r="E301" s="9" t="n"/>
       <c r="F301" s="9" t="n"/>
@@ -6151,7 +6609,7 @@
     <row r="302">
       <c r="A302" s="9" t="n"/>
       <c r="B302" s="9" t="n"/>
-      <c r="C302" s="31" t="n"/>
+      <c r="C302" s="33" t="n"/>
       <c r="D302" s="9" t="n"/>
       <c r="E302" s="9" t="n"/>
       <c r="F302" s="9" t="n"/>
@@ -6160,7 +6618,7 @@
     <row r="303">
       <c r="A303" s="9" t="n"/>
       <c r="B303" s="9" t="n"/>
-      <c r="C303" s="31" t="n"/>
+      <c r="C303" s="33" t="n"/>
       <c r="D303" s="9" t="n"/>
       <c r="E303" s="9" t="n"/>
       <c r="F303" s="9" t="n"/>
@@ -6169,7 +6627,7 @@
     <row r="304">
       <c r="A304" s="9" t="n"/>
       <c r="B304" s="9" t="n"/>
-      <c r="C304" s="31" t="n"/>
+      <c r="C304" s="33" t="n"/>
       <c r="D304" s="9" t="n"/>
       <c r="E304" s="9" t="n"/>
       <c r="F304" s="9" t="n"/>
@@ -6178,7 +6636,7 @@
     <row r="305">
       <c r="A305" s="9" t="n"/>
       <c r="B305" s="9" t="n"/>
-      <c r="C305" s="31" t="n"/>
+      <c r="C305" s="33" t="n"/>
       <c r="D305" s="9" t="n"/>
       <c r="E305" s="9" t="n"/>
       <c r="F305" s="9" t="n"/>
@@ -6187,7 +6645,7 @@
     <row r="306">
       <c r="A306" s="9" t="n"/>
       <c r="B306" s="9" t="n"/>
-      <c r="C306" s="31" t="n"/>
+      <c r="C306" s="33" t="n"/>
       <c r="D306" s="9" t="n"/>
       <c r="E306" s="9" t="n"/>
       <c r="F306" s="9" t="n"/>
@@ -6196,7 +6654,7 @@
     <row r="307">
       <c r="A307" s="9" t="n"/>
       <c r="B307" s="9" t="n"/>
-      <c r="C307" s="31" t="n"/>
+      <c r="C307" s="33" t="n"/>
       <c r="D307" s="9" t="n"/>
       <c r="E307" s="9" t="n"/>
       <c r="F307" s="9" t="n"/>
@@ -6205,7 +6663,7 @@
     <row r="308">
       <c r="A308" s="9" t="n"/>
       <c r="B308" s="9" t="n"/>
-      <c r="C308" s="31" t="n"/>
+      <c r="C308" s="33" t="n"/>
       <c r="D308" s="9" t="n"/>
       <c r="E308" s="9" t="n"/>
       <c r="F308" s="9" t="n"/>
@@ -6214,7 +6672,7 @@
     <row r="309">
       <c r="A309" s="9" t="n"/>
       <c r="B309" s="9" t="n"/>
-      <c r="C309" s="31" t="n"/>
+      <c r="C309" s="33" t="n"/>
       <c r="D309" s="9" t="n"/>
       <c r="E309" s="9" t="n"/>
       <c r="F309" s="9" t="n"/>
@@ -6223,7 +6681,7 @@
     <row r="310">
       <c r="A310" s="9" t="n"/>
       <c r="B310" s="9" t="n"/>
-      <c r="C310" s="31" t="n"/>
+      <c r="C310" s="33" t="n"/>
       <c r="D310" s="9" t="n"/>
       <c r="E310" s="9" t="n"/>
       <c r="F310" s="9" t="n"/>
@@ -6232,7 +6690,7 @@
     <row r="311">
       <c r="A311" s="9" t="n"/>
       <c r="B311" s="9" t="n"/>
-      <c r="C311" s="31" t="n"/>
+      <c r="C311" s="33" t="n"/>
       <c r="D311" s="9" t="n"/>
       <c r="E311" s="9" t="n"/>
       <c r="F311" s="9" t="n"/>
@@ -6241,7 +6699,7 @@
     <row r="312">
       <c r="A312" s="9" t="n"/>
       <c r="B312" s="9" t="n"/>
-      <c r="C312" s="31" t="n"/>
+      <c r="C312" s="33" t="n"/>
       <c r="D312" s="9" t="n"/>
       <c r="E312" s="9" t="n"/>
       <c r="F312" s="9" t="n"/>
@@ -6250,7 +6708,7 @@
     <row r="313">
       <c r="A313" s="9" t="n"/>
       <c r="B313" s="9" t="n"/>
-      <c r="C313" s="31" t="n"/>
+      <c r="C313" s="33" t="n"/>
       <c r="D313" s="9" t="n"/>
       <c r="E313" s="9" t="n"/>
       <c r="F313" s="9" t="n"/>
@@ -6259,7 +6717,7 @@
     <row r="314">
       <c r="A314" s="9" t="n"/>
       <c r="B314" s="9" t="n"/>
-      <c r="C314" s="31" t="n"/>
+      <c r="C314" s="33" t="n"/>
       <c r="D314" s="9" t="n"/>
       <c r="E314" s="9" t="n"/>
       <c r="F314" s="9" t="n"/>
@@ -6268,7 +6726,7 @@
     <row r="315">
       <c r="A315" s="9" t="n"/>
       <c r="B315" s="9" t="n"/>
-      <c r="C315" s="31" t="n"/>
+      <c r="C315" s="33" t="n"/>
       <c r="D315" s="9" t="n"/>
       <c r="E315" s="9" t="n"/>
       <c r="F315" s="9" t="n"/>
@@ -6277,7 +6735,7 @@
     <row r="316">
       <c r="A316" s="9" t="n"/>
       <c r="B316" s="9" t="n"/>
-      <c r="C316" s="31" t="n"/>
+      <c r="C316" s="33" t="n"/>
       <c r="D316" s="9" t="n"/>
       <c r="E316" s="9" t="n"/>
       <c r="F316" s="9" t="n"/>
@@ -6286,7 +6744,7 @@
     <row r="317">
       <c r="A317" s="9" t="n"/>
       <c r="B317" s="9" t="n"/>
-      <c r="C317" s="31" t="n"/>
+      <c r="C317" s="33" t="n"/>
       <c r="D317" s="9" t="n"/>
       <c r="E317" s="9" t="n"/>
       <c r="F317" s="9" t="n"/>
@@ -6295,7 +6753,7 @@
     <row r="318">
       <c r="A318" s="9" t="n"/>
       <c r="B318" s="9" t="n"/>
-      <c r="C318" s="31" t="n"/>
+      <c r="C318" s="33" t="n"/>
       <c r="D318" s="9" t="n"/>
       <c r="E318" s="9" t="n"/>
       <c r="F318" s="9" t="n"/>
@@ -6304,7 +6762,7 @@
     <row r="319">
       <c r="A319" s="9" t="n"/>
       <c r="B319" s="9" t="n"/>
-      <c r="C319" s="31" t="n"/>
+      <c r="C319" s="33" t="n"/>
       <c r="D319" s="9" t="n"/>
       <c r="E319" s="9" t="n"/>
       <c r="F319" s="9" t="n"/>
@@ -6313,7 +6771,7 @@
     <row r="320">
       <c r="A320" s="9" t="n"/>
       <c r="B320" s="9" t="n"/>
-      <c r="C320" s="31" t="n"/>
+      <c r="C320" s="33" t="n"/>
       <c r="D320" s="9" t="n"/>
       <c r="E320" s="9" t="n"/>
       <c r="F320" s="9" t="n"/>
@@ -6322,7 +6780,7 @@
     <row r="321">
       <c r="A321" s="9" t="n"/>
       <c r="B321" s="9" t="n"/>
-      <c r="C321" s="31" t="n"/>
+      <c r="C321" s="33" t="n"/>
       <c r="D321" s="9" t="n"/>
       <c r="E321" s="9" t="n"/>
       <c r="F321" s="9" t="n"/>
@@ -6331,7 +6789,7 @@
     <row r="322">
       <c r="A322" s="9" t="n"/>
       <c r="B322" s="9" t="n"/>
-      <c r="C322" s="31" t="n"/>
+      <c r="C322" s="33" t="n"/>
       <c r="D322" s="9" t="n"/>
       <c r="E322" s="9" t="n"/>
       <c r="F322" s="9" t="n"/>
@@ -6340,7 +6798,7 @@
     <row r="323">
       <c r="A323" s="9" t="n"/>
       <c r="B323" s="9" t="n"/>
-      <c r="C323" s="31" t="n"/>
+      <c r="C323" s="33" t="n"/>
       <c r="D323" s="9" t="n"/>
       <c r="E323" s="9" t="n"/>
       <c r="F323" s="9" t="n"/>
@@ -6349,7 +6807,7 @@
     <row r="324">
       <c r="A324" s="9" t="n"/>
       <c r="B324" s="9" t="n"/>
-      <c r="C324" s="31" t="n"/>
+      <c r="C324" s="33" t="n"/>
       <c r="D324" s="9" t="n"/>
       <c r="E324" s="9" t="n"/>
       <c r="F324" s="9" t="n"/>
@@ -6358,7 +6816,7 @@
     <row r="325">
       <c r="A325" s="9" t="n"/>
       <c r="B325" s="9" t="n"/>
-      <c r="C325" s="31" t="n"/>
+      <c r="C325" s="33" t="n"/>
       <c r="D325" s="9" t="n"/>
       <c r="E325" s="9" t="n"/>
       <c r="F325" s="9" t="n"/>
@@ -6367,7 +6825,7 @@
     <row r="326">
       <c r="A326" s="9" t="n"/>
       <c r="B326" s="9" t="n"/>
-      <c r="C326" s="31" t="n"/>
+      <c r="C326" s="33" t="n"/>
       <c r="D326" s="9" t="n"/>
       <c r="E326" s="9" t="n"/>
       <c r="F326" s="9" t="n"/>
@@ -6376,7 +6834,7 @@
     <row r="327">
       <c r="A327" s="9" t="n"/>
       <c r="B327" s="9" t="n"/>
-      <c r="C327" s="31" t="n"/>
+      <c r="C327" s="33" t="n"/>
       <c r="D327" s="9" t="n"/>
       <c r="E327" s="9" t="n"/>
       <c r="F327" s="9" t="n"/>
@@ -6385,7 +6843,7 @@
     <row r="328">
       <c r="A328" s="9" t="n"/>
       <c r="B328" s="9" t="n"/>
-      <c r="C328" s="31" t="n"/>
+      <c r="C328" s="33" t="n"/>
       <c r="D328" s="9" t="n"/>
       <c r="E328" s="9" t="n"/>
       <c r="F328" s="9" t="n"/>
@@ -6394,7 +6852,7 @@
     <row r="329">
       <c r="A329" s="9" t="n"/>
       <c r="B329" s="9" t="n"/>
-      <c r="C329" s="31" t="n"/>
+      <c r="C329" s="33" t="n"/>
       <c r="D329" s="9" t="n"/>
       <c r="E329" s="9" t="n"/>
       <c r="F329" s="9" t="n"/>
@@ -6403,7 +6861,7 @@
     <row r="330">
       <c r="A330" s="9" t="n"/>
       <c r="B330" s="9" t="n"/>
-      <c r="C330" s="31" t="n"/>
+      <c r="C330" s="33" t="n"/>
       <c r="D330" s="9" t="n"/>
       <c r="E330" s="9" t="n"/>
       <c r="F330" s="9" t="n"/>
@@ -6412,7 +6870,7 @@
     <row r="331">
       <c r="A331" s="9" t="n"/>
       <c r="B331" s="9" t="n"/>
-      <c r="C331" s="31" t="n"/>
+      <c r="C331" s="33" t="n"/>
       <c r="D331" s="9" t="n"/>
       <c r="E331" s="9" t="n"/>
       <c r="F331" s="9" t="n"/>
@@ -6421,7 +6879,7 @@
     <row r="332">
       <c r="A332" s="9" t="n"/>
       <c r="B332" s="9" t="n"/>
-      <c r="C332" s="31" t="n"/>
+      <c r="C332" s="33" t="n"/>
       <c r="D332" s="9" t="n"/>
       <c r="E332" s="9" t="n"/>
       <c r="F332" s="9" t="n"/>
@@ -6430,7 +6888,7 @@
     <row r="333">
       <c r="A333" s="9" t="n"/>
       <c r="B333" s="9" t="n"/>
-      <c r="C333" s="31" t="n"/>
+      <c r="C333" s="33" t="n"/>
       <c r="D333" s="9" t="n"/>
       <c r="E333" s="9" t="n"/>
       <c r="F333" s="9" t="n"/>
@@ -6439,7 +6897,7 @@
     <row r="334">
       <c r="A334" s="9" t="n"/>
       <c r="B334" s="9" t="n"/>
-      <c r="C334" s="31" t="n"/>
+      <c r="C334" s="33" t="n"/>
       <c r="D334" s="9" t="n"/>
       <c r="E334" s="9" t="n"/>
       <c r="F334" s="9" t="n"/>
@@ -6448,7 +6906,7 @@
     <row r="335">
       <c r="A335" s="9" t="n"/>
       <c r="B335" s="9" t="n"/>
-      <c r="C335" s="31" t="n"/>
+      <c r="C335" s="33" t="n"/>
       <c r="D335" s="9" t="n"/>
       <c r="E335" s="9" t="n"/>
       <c r="F335" s="9" t="n"/>
@@ -6457,7 +6915,7 @@
     <row r="336">
       <c r="A336" s="9" t="n"/>
       <c r="B336" s="9" t="n"/>
-      <c r="C336" s="31" t="n"/>
+      <c r="C336" s="33" t="n"/>
       <c r="D336" s="9" t="n"/>
       <c r="E336" s="9" t="n"/>
       <c r="F336" s="9" t="n"/>
@@ -6466,7 +6924,7 @@
     <row r="337">
       <c r="A337" s="9" t="n"/>
       <c r="B337" s="9" t="n"/>
-      <c r="C337" s="31" t="n"/>
+      <c r="C337" s="33" t="n"/>
       <c r="D337" s="9" t="n"/>
       <c r="E337" s="9" t="n"/>
       <c r="F337" s="9" t="n"/>
@@ -6475,7 +6933,7 @@
     <row r="338">
       <c r="A338" s="9" t="n"/>
       <c r="B338" s="9" t="n"/>
-      <c r="C338" s="31" t="n"/>
+      <c r="C338" s="33" t="n"/>
       <c r="D338" s="9" t="n"/>
       <c r="E338" s="9" t="n"/>
       <c r="F338" s="9" t="n"/>
@@ -6484,7 +6942,7 @@
     <row r="339">
       <c r="A339" s="9" t="n"/>
       <c r="B339" s="9" t="n"/>
-      <c r="C339" s="31" t="n"/>
+      <c r="C339" s="33" t="n"/>
       <c r="D339" s="9" t="n"/>
       <c r="E339" s="9" t="n"/>
       <c r="F339" s="9" t="n"/>
@@ -6493,7 +6951,7 @@
     <row r="340">
       <c r="A340" s="9" t="n"/>
       <c r="B340" s="9" t="n"/>
-      <c r="C340" s="31" t="n"/>
+      <c r="C340" s="33" t="n"/>
       <c r="D340" s="9" t="n"/>
       <c r="E340" s="9" t="n"/>
       <c r="F340" s="9" t="n"/>
@@ -6502,7 +6960,7 @@
     <row r="341">
       <c r="A341" s="9" t="n"/>
       <c r="B341" s="9" t="n"/>
-      <c r="C341" s="31" t="n"/>
+      <c r="C341" s="33" t="n"/>
       <c r="D341" s="9" t="n"/>
       <c r="E341" s="9" t="n"/>
       <c r="F341" s="9" t="n"/>
@@ -6511,7 +6969,7 @@
     <row r="342">
       <c r="A342" s="9" t="n"/>
       <c r="B342" s="9" t="n"/>
-      <c r="C342" s="31" t="n"/>
+      <c r="C342" s="33" t="n"/>
       <c r="D342" s="9" t="n"/>
       <c r="E342" s="9" t="n"/>
       <c r="F342" s="9" t="n"/>
@@ -6520,7 +6978,7 @@
     <row r="343">
       <c r="A343" s="9" t="n"/>
       <c r="B343" s="9" t="n"/>
-      <c r="C343" s="31" t="n"/>
+      <c r="C343" s="33" t="n"/>
       <c r="D343" s="9" t="n"/>
       <c r="E343" s="9" t="n"/>
       <c r="F343" s="9" t="n"/>
@@ -6529,7 +6987,7 @@
     <row r="344">
       <c r="A344" s="9" t="n"/>
       <c r="B344" s="9" t="n"/>
-      <c r="C344" s="31" t="n"/>
+      <c r="C344" s="33" t="n"/>
       <c r="D344" s="9" t="n"/>
       <c r="E344" s="9" t="n"/>
       <c r="F344" s="9" t="n"/>
@@ -6538,7 +6996,7 @@
     <row r="345">
       <c r="A345" s="9" t="n"/>
       <c r="B345" s="9" t="n"/>
-      <c r="C345" s="31" t="n"/>
+      <c r="C345" s="33" t="n"/>
       <c r="D345" s="9" t="n"/>
       <c r="E345" s="9" t="n"/>
       <c r="F345" s="9" t="n"/>
@@ -6547,7 +7005,7 @@
     <row r="346">
       <c r="A346" s="9" t="n"/>
       <c r="B346" s="9" t="n"/>
-      <c r="C346" s="31" t="n"/>
+      <c r="C346" s="33" t="n"/>
       <c r="D346" s="9" t="n"/>
       <c r="E346" s="9" t="n"/>
       <c r="F346" s="9" t="n"/>
@@ -6556,7 +7014,7 @@
     <row r="347">
       <c r="A347" s="9" t="n"/>
       <c r="B347" s="9" t="n"/>
-      <c r="C347" s="31" t="n"/>
+      <c r="C347" s="33" t="n"/>
       <c r="D347" s="9" t="n"/>
       <c r="E347" s="9" t="n"/>
       <c r="F347" s="9" t="n"/>
@@ -6565,7 +7023,7 @@
     <row r="348">
       <c r="A348" s="9" t="n"/>
       <c r="B348" s="9" t="n"/>
-      <c r="C348" s="31" t="n"/>
+      <c r="C348" s="33" t="n"/>
       <c r="D348" s="9" t="n"/>
       <c r="E348" s="9" t="n"/>
       <c r="F348" s="9" t="n"/>
@@ -6574,7 +7032,7 @@
     <row r="349">
       <c r="A349" s="9" t="n"/>
       <c r="B349" s="9" t="n"/>
-      <c r="C349" s="31" t="n"/>
+      <c r="C349" s="33" t="n"/>
       <c r="D349" s="9" t="n"/>
       <c r="E349" s="9" t="n"/>
       <c r="F349" s="9" t="n"/>
@@ -6583,7 +7041,7 @@
     <row r="350">
       <c r="A350" s="9" t="n"/>
       <c r="B350" s="9" t="n"/>
-      <c r="C350" s="31" t="n"/>
+      <c r="C350" s="33" t="n"/>
       <c r="D350" s="9" t="n"/>
       <c r="E350" s="9" t="n"/>
       <c r="F350" s="9" t="n"/>
@@ -6592,7 +7050,7 @@
     <row r="351">
       <c r="A351" s="9" t="n"/>
       <c r="B351" s="9" t="n"/>
-      <c r="C351" s="31" t="n"/>
+      <c r="C351" s="33" t="n"/>
       <c r="D351" s="9" t="n"/>
       <c r="E351" s="9" t="n"/>
       <c r="F351" s="9" t="n"/>
@@ -6601,7 +7059,7 @@
     <row r="352">
       <c r="A352" s="9" t="n"/>
       <c r="B352" s="9" t="n"/>
-      <c r="C352" s="31" t="n"/>
+      <c r="C352" s="33" t="n"/>
       <c r="D352" s="9" t="n"/>
       <c r="E352" s="9" t="n"/>
       <c r="F352" s="9" t="n"/>
@@ -6610,7 +7068,7 @@
     <row r="353">
       <c r="A353" s="9" t="n"/>
       <c r="B353" s="9" t="n"/>
-      <c r="C353" s="31" t="n"/>
+      <c r="C353" s="33" t="n"/>
       <c r="D353" s="9" t="n"/>
       <c r="E353" s="9" t="n"/>
       <c r="F353" s="9" t="n"/>
@@ -6619,7 +7077,7 @@
     <row r="354">
       <c r="A354" s="9" t="n"/>
       <c r="B354" s="9" t="n"/>
-      <c r="C354" s="31" t="n"/>
+      <c r="C354" s="33" t="n"/>
       <c r="D354" s="9" t="n"/>
       <c r="E354" s="9" t="n"/>
       <c r="F354" s="9" t="n"/>
@@ -6628,7 +7086,7 @@
     <row r="355">
       <c r="A355" s="9" t="n"/>
       <c r="B355" s="9" t="n"/>
-      <c r="C355" s="31" t="n"/>
+      <c r="C355" s="33" t="n"/>
       <c r="D355" s="9" t="n"/>
       <c r="E355" s="9" t="n"/>
       <c r="F355" s="9" t="n"/>
@@ -6637,7 +7095,7 @@
     <row r="356">
       <c r="A356" s="9" t="n"/>
       <c r="B356" s="9" t="n"/>
-      <c r="C356" s="31" t="n"/>
+      <c r="C356" s="33" t="n"/>
       <c r="D356" s="9" t="n"/>
       <c r="E356" s="9" t="n"/>
       <c r="F356" s="9" t="n"/>
@@ -6646,7 +7104,7 @@
     <row r="357">
       <c r="A357" s="9" t="n"/>
       <c r="B357" s="9" t="n"/>
-      <c r="C357" s="31" t="n"/>
+      <c r="C357" s="33" t="n"/>
       <c r="D357" s="9" t="n"/>
       <c r="E357" s="9" t="n"/>
       <c r="F357" s="9" t="n"/>
@@ -6655,7 +7113,7 @@
     <row r="358">
       <c r="A358" s="9" t="n"/>
       <c r="B358" s="9" t="n"/>
-      <c r="C358" s="31" t="n"/>
+      <c r="C358" s="33" t="n"/>
       <c r="D358" s="9" t="n"/>
       <c r="E358" s="9" t="n"/>
       <c r="F358" s="9" t="n"/>
@@ -6664,7 +7122,7 @@
     <row r="359">
       <c r="A359" s="9" t="n"/>
       <c r="B359" s="9" t="n"/>
-      <c r="C359" s="31" t="n"/>
+      <c r="C359" s="33" t="n"/>
       <c r="D359" s="9" t="n"/>
       <c r="E359" s="9" t="n"/>
       <c r="F359" s="9" t="n"/>
@@ -6673,7 +7131,7 @@
     <row r="360">
       <c r="A360" s="9" t="n"/>
       <c r="B360" s="9" t="n"/>
-      <c r="C360" s="31" t="n"/>
+      <c r="C360" s="33" t="n"/>
       <c r="D360" s="9" t="n"/>
       <c r="E360" s="9" t="n"/>
       <c r="F360" s="9" t="n"/>
@@ -6682,7 +7140,7 @@
     <row r="361">
       <c r="A361" s="9" t="n"/>
       <c r="B361" s="9" t="n"/>
-      <c r="C361" s="31" t="n"/>
+      <c r="C361" s="33" t="n"/>
       <c r="D361" s="9" t="n"/>
       <c r="E361" s="9" t="n"/>
       <c r="F361" s="9" t="n"/>
@@ -6691,7 +7149,7 @@
     <row r="362">
       <c r="A362" s="9" t="n"/>
       <c r="B362" s="9" t="n"/>
-      <c r="C362" s="31" t="n"/>
+      <c r="C362" s="33" t="n"/>
       <c r="D362" s="9" t="n"/>
       <c r="E362" s="9" t="n"/>
       <c r="F362" s="9" t="n"/>
@@ -6700,7 +7158,7 @@
     <row r="363">
       <c r="A363" s="9" t="n"/>
       <c r="B363" s="9" t="n"/>
-      <c r="C363" s="31" t="n"/>
+      <c r="C363" s="33" t="n"/>
       <c r="D363" s="9" t="n"/>
       <c r="E363" s="9" t="n"/>
       <c r="F363" s="9" t="n"/>
@@ -6709,7 +7167,7 @@
     <row r="364">
       <c r="A364" s="9" t="n"/>
       <c r="B364" s="9" t="n"/>
-      <c r="C364" s="31" t="n"/>
+      <c r="C364" s="33" t="n"/>
       <c r="D364" s="9" t="n"/>
       <c r="E364" s="9" t="n"/>
       <c r="F364" s="9" t="n"/>
@@ -6718,7 +7176,7 @@
     <row r="365">
       <c r="A365" s="9" t="n"/>
       <c r="B365" s="9" t="n"/>
-      <c r="C365" s="31" t="n"/>
+      <c r="C365" s="33" t="n"/>
       <c r="D365" s="9" t="n"/>
       <c r="E365" s="9" t="n"/>
       <c r="F365" s="9" t="n"/>
@@ -6727,7 +7185,7 @@
     <row r="366">
       <c r="A366" s="9" t="n"/>
       <c r="B366" s="9" t="n"/>
-      <c r="C366" s="31" t="n"/>
+      <c r="C366" s="33" t="n"/>
       <c r="D366" s="9" t="n"/>
       <c r="E366" s="9" t="n"/>
       <c r="F366" s="9" t="n"/>
@@ -6736,7 +7194,7 @@
     <row r="367">
       <c r="A367" s="9" t="n"/>
       <c r="B367" s="9" t="n"/>
-      <c r="C367" s="31" t="n"/>
+      <c r="C367" s="33" t="n"/>
       <c r="D367" s="9" t="n"/>
       <c r="E367" s="9" t="n"/>
       <c r="F367" s="9" t="n"/>
@@ -6745,7 +7203,7 @@
     <row r="368">
       <c r="A368" s="9" t="n"/>
       <c r="B368" s="9" t="n"/>
-      <c r="C368" s="31" t="n"/>
+      <c r="C368" s="33" t="n"/>
       <c r="D368" s="9" t="n"/>
       <c r="E368" s="9" t="n"/>
       <c r="F368" s="9" t="n"/>
@@ -6754,7 +7212,7 @@
     <row r="369">
       <c r="A369" s="9" t="n"/>
       <c r="B369" s="9" t="n"/>
-      <c r="C369" s="31" t="n"/>
+      <c r="C369" s="33" t="n"/>
       <c r="D369" s="9" t="n"/>
       <c r="E369" s="9" t="n"/>
       <c r="F369" s="9" t="n"/>
@@ -6763,7 +7221,7 @@
     <row r="370">
       <c r="A370" s="9" t="n"/>
       <c r="B370" s="9" t="n"/>
-      <c r="C370" s="31" t="n"/>
+      <c r="C370" s="33" t="n"/>
       <c r="D370" s="9" t="n"/>
       <c r="E370" s="9" t="n"/>
       <c r="F370" s="9" t="n"/>
@@ -6772,7 +7230,7 @@
     <row r="371">
       <c r="A371" s="9" t="n"/>
       <c r="B371" s="9" t="n"/>
-      <c r="C371" s="31" t="n"/>
+      <c r="C371" s="33" t="n"/>
       <c r="D371" s="9" t="n"/>
       <c r="E371" s="9" t="n"/>
       <c r="F371" s="9" t="n"/>
@@ -6781,7 +7239,7 @@
     <row r="372">
       <c r="A372" s="9" t="n"/>
       <c r="B372" s="9" t="n"/>
-      <c r="C372" s="31" t="n"/>
+      <c r="C372" s="33" t="n"/>
       <c r="D372" s="9" t="n"/>
       <c r="E372" s="9" t="n"/>
       <c r="F372" s="9" t="n"/>
@@ -6790,7 +7248,7 @@
     <row r="373">
       <c r="A373" s="9" t="n"/>
       <c r="B373" s="9" t="n"/>
-      <c r="C373" s="31" t="n"/>
+      <c r="C373" s="33" t="n"/>
       <c r="D373" s="9" t="n"/>
       <c r="E373" s="9" t="n"/>
       <c r="F373" s="9" t="n"/>
@@ -6799,7 +7257,7 @@
     <row r="374">
       <c r="A374" s="9" t="n"/>
       <c r="B374" s="9" t="n"/>
-      <c r="C374" s="31" t="n"/>
+      <c r="C374" s="33" t="n"/>
       <c r="D374" s="9" t="n"/>
       <c r="E374" s="9" t="n"/>
       <c r="F374" s="9" t="n"/>
@@ -6808,7 +7266,7 @@
     <row r="375">
       <c r="A375" s="9" t="n"/>
       <c r="B375" s="9" t="n"/>
-      <c r="C375" s="31" t="n"/>
+      <c r="C375" s="33" t="n"/>
       <c r="D375" s="9" t="n"/>
       <c r="E375" s="9" t="n"/>
       <c r="F375" s="9" t="n"/>
@@ -6817,7 +7275,7 @@
     <row r="376">
       <c r="A376" s="9" t="n"/>
       <c r="B376" s="9" t="n"/>
-      <c r="C376" s="31" t="n"/>
+      <c r="C376" s="33" t="n"/>
       <c r="D376" s="9" t="n"/>
       <c r="E376" s="9" t="n"/>
       <c r="F376" s="9" t="n"/>
@@ -6826,7 +7284,7 @@
     <row r="377">
       <c r="A377" s="9" t="n"/>
       <c r="B377" s="9" t="n"/>
-      <c r="C377" s="31" t="n"/>
+      <c r="C377" s="33" t="n"/>
       <c r="D377" s="9" t="n"/>
       <c r="E377" s="9" t="n"/>
       <c r="F377" s="9" t="n"/>
@@ -6835,7 +7293,7 @@
     <row r="378">
       <c r="A378" s="9" t="n"/>
       <c r="B378" s="9" t="n"/>
-      <c r="C378" s="31" t="n"/>
+      <c r="C378" s="33" t="n"/>
       <c r="D378" s="9" t="n"/>
       <c r="E378" s="9" t="n"/>
       <c r="F378" s="9" t="n"/>
@@ -6844,7 +7302,7 @@
     <row r="379">
       <c r="A379" s="9" t="n"/>
       <c r="B379" s="9" t="n"/>
-      <c r="C379" s="31" t="n"/>
+      <c r="C379" s="33" t="n"/>
       <c r="D379" s="9" t="n"/>
       <c r="E379" s="9" t="n"/>
       <c r="F379" s="9" t="n"/>
@@ -6853,7 +7311,7 @@
     <row r="380">
       <c r="A380" s="9" t="n"/>
       <c r="B380" s="9" t="n"/>
-      <c r="C380" s="31" t="n"/>
+      <c r="C380" s="33" t="n"/>
       <c r="D380" s="9" t="n"/>
       <c r="E380" s="9" t="n"/>
       <c r="F380" s="9" t="n"/>
@@ -6862,7 +7320,7 @@
     <row r="381">
       <c r="A381" s="9" t="n"/>
       <c r="B381" s="9" t="n"/>
-      <c r="C381" s="31" t="n"/>
+      <c r="C381" s="33" t="n"/>
       <c r="D381" s="9" t="n"/>
       <c r="E381" s="9" t="n"/>
       <c r="F381" s="9" t="n"/>
@@ -6871,7 +7329,7 @@
     <row r="382">
       <c r="A382" s="9" t="n"/>
       <c r="B382" s="9" t="n"/>
-      <c r="C382" s="31" t="n"/>
+      <c r="C382" s="33" t="n"/>
       <c r="D382" s="9" t="n"/>
       <c r="E382" s="9" t="n"/>
       <c r="F382" s="9" t="n"/>
@@ -6880,7 +7338,7 @@
     <row r="383">
       <c r="A383" s="9" t="n"/>
       <c r="B383" s="9" t="n"/>
-      <c r="C383" s="31" t="n"/>
+      <c r="C383" s="33" t="n"/>
       <c r="D383" s="9" t="n"/>
       <c r="E383" s="9" t="n"/>
       <c r="F383" s="9" t="n"/>
@@ -6889,7 +7347,7 @@
     <row r="384">
       <c r="A384" s="9" t="n"/>
       <c r="B384" s="9" t="n"/>
-      <c r="C384" s="31" t="n"/>
+      <c r="C384" s="33" t="n"/>
       <c r="D384" s="9" t="n"/>
       <c r="E384" s="9" t="n"/>
       <c r="F384" s="9" t="n"/>
@@ -6898,7 +7356,7 @@
     <row r="385">
       <c r="A385" s="9" t="n"/>
       <c r="B385" s="9" t="n"/>
-      <c r="C385" s="31" t="n"/>
+      <c r="C385" s="33" t="n"/>
       <c r="D385" s="9" t="n"/>
       <c r="E385" s="9" t="n"/>
       <c r="F385" s="9" t="n"/>
@@ -6907,7 +7365,7 @@
     <row r="386">
       <c r="A386" s="9" t="n"/>
       <c r="B386" s="9" t="n"/>
-      <c r="C386" s="31" t="n"/>
+      <c r="C386" s="33" t="n"/>
       <c r="D386" s="9" t="n"/>
       <c r="E386" s="9" t="n"/>
       <c r="F386" s="9" t="n"/>
@@ -6916,7 +7374,7 @@
     <row r="387">
       <c r="A387" s="9" t="n"/>
       <c r="B387" s="9" t="n"/>
-      <c r="C387" s="31" t="n"/>
+      <c r="C387" s="33" t="n"/>
       <c r="D387" s="9" t="n"/>
       <c r="E387" s="9" t="n"/>
       <c r="F387" s="9" t="n"/>
@@ -6925,7 +7383,7 @@
     <row r="388">
       <c r="A388" s="9" t="n"/>
       <c r="B388" s="9" t="n"/>
-      <c r="C388" s="31" t="n"/>
+      <c r="C388" s="33" t="n"/>
       <c r="D388" s="9" t="n"/>
       <c r="E388" s="9" t="n"/>
       <c r="F388" s="9" t="n"/>
@@ -6934,7 +7392,7 @@
     <row r="389">
       <c r="A389" s="9" t="n"/>
       <c r="B389" s="9" t="n"/>
-      <c r="C389" s="31" t="n"/>
+      <c r="C389" s="33" t="n"/>
       <c r="D389" s="9" t="n"/>
       <c r="E389" s="9" t="n"/>
       <c r="F389" s="9" t="n"/>
@@ -6943,7 +7401,7 @@
     <row r="390">
       <c r="A390" s="9" t="n"/>
       <c r="B390" s="9" t="n"/>
-      <c r="C390" s="31" t="n"/>
+      <c r="C390" s="33" t="n"/>
       <c r="D390" s="9" t="n"/>
       <c r="E390" s="9" t="n"/>
       <c r="F390" s="9" t="n"/>
@@ -6952,7 +7410,7 @@
     <row r="391">
       <c r="A391" s="9" t="n"/>
       <c r="B391" s="9" t="n"/>
-      <c r="C391" s="31" t="n"/>
+      <c r="C391" s="33" t="n"/>
       <c r="D391" s="9" t="n"/>
       <c r="E391" s="9" t="n"/>
       <c r="F391" s="9" t="n"/>
@@ -6961,7 +7419,7 @@
     <row r="392">
       <c r="A392" s="9" t="n"/>
       <c r="B392" s="9" t="n"/>
-      <c r="C392" s="31" t="n"/>
+      <c r="C392" s="33" t="n"/>
       <c r="D392" s="9" t="n"/>
       <c r="E392" s="9" t="n"/>
       <c r="F392" s="9" t="n"/>
@@ -6970,7 +7428,7 @@
     <row r="393">
       <c r="A393" s="9" t="n"/>
       <c r="B393" s="9" t="n"/>
-      <c r="C393" s="31" t="n"/>
+      <c r="C393" s="33" t="n"/>
       <c r="D393" s="9" t="n"/>
       <c r="E393" s="9" t="n"/>
       <c r="F393" s="9" t="n"/>
@@ -6979,7 +7437,7 @@
     <row r="394">
       <c r="A394" s="9" t="n"/>
       <c r="B394" s="9" t="n"/>
-      <c r="C394" s="31" t="n"/>
+      <c r="C394" s="33" t="n"/>
       <c r="D394" s="9" t="n"/>
       <c r="E394" s="9" t="n"/>
       <c r="F394" s="9" t="n"/>
@@ -6988,7 +7446,7 @@
     <row r="395">
       <c r="A395" s="9" t="n"/>
       <c r="B395" s="9" t="n"/>
-      <c r="C395" s="31" t="n"/>
+      <c r="C395" s="33" t="n"/>
       <c r="D395" s="9" t="n"/>
       <c r="E395" s="9" t="n"/>
       <c r="F395" s="9" t="n"/>
@@ -6997,7 +7455,7 @@
     <row r="396">
       <c r="A396" s="9" t="n"/>
       <c r="B396" s="9" t="n"/>
-      <c r="C396" s="31" t="n"/>
+      <c r="C396" s="33" t="n"/>
       <c r="D396" s="9" t="n"/>
       <c r="E396" s="9" t="n"/>
       <c r="F396" s="9" t="n"/>
@@ -7006,7 +7464,7 @@
     <row r="397">
       <c r="A397" s="9" t="n"/>
       <c r="B397" s="9" t="n"/>
-      <c r="C397" s="31" t="n"/>
+      <c r="C397" s="33" t="n"/>
       <c r="D397" s="9" t="n"/>
       <c r="E397" s="9" t="n"/>
       <c r="F397" s="9" t="n"/>
@@ -7015,7 +7473,7 @@
     <row r="398">
       <c r="A398" s="9" t="n"/>
       <c r="B398" s="9" t="n"/>
-      <c r="C398" s="31" t="n"/>
+      <c r="C398" s="33" t="n"/>
       <c r="D398" s="9" t="n"/>
       <c r="E398" s="9" t="n"/>
       <c r="F398" s="9" t="n"/>
@@ -7024,7 +7482,7 @@
     <row r="399">
       <c r="A399" s="9" t="n"/>
       <c r="B399" s="9" t="n"/>
-      <c r="C399" s="31" t="n"/>
+      <c r="C399" s="33" t="n"/>
       <c r="D399" s="9" t="n"/>
       <c r="E399" s="9" t="n"/>
       <c r="F399" s="9" t="n"/>
@@ -7033,7 +7491,7 @@
     <row r="400">
       <c r="A400" s="9" t="n"/>
       <c r="B400" s="9" t="n"/>
-      <c r="C400" s="31" t="n"/>
+      <c r="C400" s="33" t="n"/>
       <c r="D400" s="9" t="n"/>
       <c r="E400" s="9" t="n"/>
       <c r="F400" s="9" t="n"/>
@@ -7042,7 +7500,7 @@
     <row r="401">
       <c r="A401" s="9" t="n"/>
       <c r="B401" s="9" t="n"/>
-      <c r="C401" s="31" t="n"/>
+      <c r="C401" s="33" t="n"/>
       <c r="D401" s="9" t="n"/>
       <c r="E401" s="9" t="n"/>
       <c r="F401" s="9" t="n"/>
@@ -7051,7 +7509,7 @@
     <row r="402">
       <c r="A402" s="9" t="n"/>
       <c r="B402" s="9" t="n"/>
-      <c r="C402" s="31" t="n"/>
+      <c r="C402" s="33" t="n"/>
       <c r="D402" s="9" t="n"/>
       <c r="E402" s="9" t="n"/>
       <c r="F402" s="9" t="n"/>
@@ -7060,7 +7518,7 @@
     <row r="403">
       <c r="A403" s="9" t="n"/>
       <c r="B403" s="9" t="n"/>
-      <c r="C403" s="31" t="n"/>
+      <c r="C403" s="33" t="n"/>
       <c r="D403" s="9" t="n"/>
       <c r="E403" s="9" t="n"/>
       <c r="F403" s="9" t="n"/>
@@ -7069,7 +7527,7 @@
     <row r="404">
       <c r="A404" s="9" t="n"/>
       <c r="B404" s="9" t="n"/>
-      <c r="C404" s="31" t="n"/>
+      <c r="C404" s="33" t="n"/>
       <c r="D404" s="9" t="n"/>
       <c r="E404" s="9" t="n"/>
       <c r="F404" s="9" t="n"/>
@@ -7078,7 +7536,7 @@
     <row r="405">
       <c r="A405" s="9" t="n"/>
       <c r="B405" s="9" t="n"/>
-      <c r="C405" s="31" t="n"/>
+      <c r="C405" s="33" t="n"/>
       <c r="D405" s="9" t="n"/>
       <c r="E405" s="9" t="n"/>
       <c r="F405" s="9" t="n"/>
@@ -7087,7 +7545,7 @@
     <row r="406">
       <c r="A406" s="9" t="n"/>
       <c r="B406" s="9" t="n"/>
-      <c r="C406" s="31" t="n"/>
+      <c r="C406" s="33" t="n"/>
       <c r="D406" s="9" t="n"/>
       <c r="E406" s="9" t="n"/>
       <c r="F406" s="9" t="n"/>
@@ -7096,7 +7554,7 @@
     <row r="407">
       <c r="A407" s="9" t="n"/>
       <c r="B407" s="9" t="n"/>
-      <c r="C407" s="31" t="n"/>
+      <c r="C407" s="33" t="n"/>
       <c r="D407" s="9" t="n"/>
       <c r="E407" s="9" t="n"/>
       <c r="F407" s="9" t="n"/>
@@ -7105,7 +7563,7 @@
     <row r="408">
       <c r="A408" s="9" t="n"/>
       <c r="B408" s="9" t="n"/>
-      <c r="C408" s="31" t="n"/>
+      <c r="C408" s="33" t="n"/>
       <c r="D408" s="9" t="n"/>
       <c r="E408" s="9" t="n"/>
       <c r="F408" s="9" t="n"/>
@@ -7114,7 +7572,7 @@
     <row r="409">
       <c r="A409" s="9" t="n"/>
       <c r="B409" s="9" t="n"/>
-      <c r="C409" s="31" t="n"/>
+      <c r="C409" s="33" t="n"/>
       <c r="D409" s="9" t="n"/>
       <c r="E409" s="9" t="n"/>
       <c r="F409" s="9" t="n"/>
@@ -7123,7 +7581,7 @@
     <row r="410">
       <c r="A410" s="9" t="n"/>
       <c r="B410" s="9" t="n"/>
-      <c r="C410" s="31" t="n"/>
+      <c r="C410" s="33" t="n"/>
       <c r="D410" s="9" t="n"/>
       <c r="E410" s="9" t="n"/>
       <c r="F410" s="9" t="n"/>
@@ -7132,7 +7590,7 @@
     <row r="411">
       <c r="A411" s="9" t="n"/>
       <c r="B411" s="9" t="n"/>
-      <c r="C411" s="31" t="n"/>
+      <c r="C411" s="33" t="n"/>
       <c r="D411" s="9" t="n"/>
       <c r="E411" s="9" t="n"/>
       <c r="F411" s="9" t="n"/>
@@ -7141,7 +7599,7 @@
     <row r="412">
       <c r="A412" s="9" t="n"/>
       <c r="B412" s="9" t="n"/>
-      <c r="C412" s="31" t="n"/>
+      <c r="C412" s="33" t="n"/>
       <c r="D412" s="9" t="n"/>
       <c r="E412" s="9" t="n"/>
       <c r="F412" s="9" t="n"/>
@@ -7150,7 +7608,7 @@
     <row r="413">
       <c r="A413" s="9" t="n"/>
       <c r="B413" s="9" t="n"/>
-      <c r="C413" s="31" t="n"/>
+      <c r="C413" s="33" t="n"/>
       <c r="D413" s="9" t="n"/>
       <c r="E413" s="9" t="n"/>
       <c r="F413" s="9" t="n"/>
@@ -7159,7 +7617,7 @@
     <row r="414">
       <c r="A414" s="9" t="n"/>
       <c r="B414" s="9" t="n"/>
-      <c r="C414" s="31" t="n"/>
+      <c r="C414" s="33" t="n"/>
       <c r="D414" s="9" t="n"/>
       <c r="E414" s="9" t="n"/>
       <c r="F414" s="9" t="n"/>
@@ -7168,7 +7626,7 @@
     <row r="415">
       <c r="A415" s="9" t="n"/>
       <c r="B415" s="9" t="n"/>
-      <c r="C415" s="31" t="n"/>
+      <c r="C415" s="33" t="n"/>
       <c r="D415" s="9" t="n"/>
       <c r="E415" s="9" t="n"/>
       <c r="F415" s="9" t="n"/>
@@ -7177,7 +7635,7 @@
     <row r="416">
       <c r="A416" s="9" t="n"/>
       <c r="B416" s="9" t="n"/>
-      <c r="C416" s="31" t="n"/>
+      <c r="C416" s="33" t="n"/>
       <c r="D416" s="9" t="n"/>
       <c r="E416" s="9" t="n"/>
       <c r="F416" s="9" t="n"/>
@@ -7186,7 +7644,7 @@
     <row r="417">
       <c r="A417" s="9" t="n"/>
       <c r="B417" s="9" t="n"/>
-      <c r="C417" s="31" t="n"/>
+      <c r="C417" s="33" t="n"/>
       <c r="D417" s="9" t="n"/>
       <c r="E417" s="9" t="n"/>
       <c r="F417" s="9" t="n"/>
@@ -7195,7 +7653,7 @@
     <row r="418">
       <c r="A418" s="9" t="n"/>
       <c r="B418" s="9" t="n"/>
-      <c r="C418" s="31" t="n"/>
+      <c r="C418" s="33" t="n"/>
       <c r="D418" s="9" t="n"/>
       <c r="E418" s="9" t="n"/>
       <c r="F418" s="9" t="n"/>
@@ -7204,7 +7662,7 @@
     <row r="419">
       <c r="A419" s="9" t="n"/>
       <c r="B419" s="9" t="n"/>
-      <c r="C419" s="31" t="n"/>
+      <c r="C419" s="33" t="n"/>
       <c r="D419" s="9" t="n"/>
       <c r="E419" s="9" t="n"/>
       <c r="F419" s="9" t="n"/>
@@ -7213,7 +7671,7 @@
     <row r="420">
       <c r="A420" s="9" t="n"/>
       <c r="B420" s="9" t="n"/>
-      <c r="C420" s="31" t="n"/>
+      <c r="C420" s="33" t="n"/>
       <c r="D420" s="9" t="n"/>
       <c r="E420" s="9" t="n"/>
       <c r="F420" s="9" t="n"/>
@@ -7222,7 +7680,7 @@
     <row r="421">
       <c r="A421" s="9" t="n"/>
       <c r="B421" s="9" t="n"/>
-      <c r="C421" s="31" t="n"/>
+      <c r="C421" s="33" t="n"/>
       <c r="D421" s="9" t="n"/>
       <c r="E421" s="9" t="n"/>
       <c r="F421" s="9" t="n"/>
@@ -7231,7 +7689,7 @@
     <row r="422">
       <c r="A422" s="9" t="n"/>
       <c r="B422" s="9" t="n"/>
-      <c r="C422" s="31" t="n"/>
+      <c r="C422" s="33" t="n"/>
       <c r="D422" s="9" t="n"/>
       <c r="E422" s="9" t="n"/>
       <c r="F422" s="9" t="n"/>
@@ -7240,7 +7698,7 @@
     <row r="423">
       <c r="A423" s="9" t="n"/>
       <c r="B423" s="9" t="n"/>
-      <c r="C423" s="31" t="n"/>
+      <c r="C423" s="33" t="n"/>
       <c r="D423" s="9" t="n"/>
       <c r="E423" s="9" t="n"/>
       <c r="F423" s="9" t="n"/>
@@ -7249,7 +7707,7 @@
     <row r="424">
       <c r="A424" s="9" t="n"/>
       <c r="B424" s="9" t="n"/>
-      <c r="C424" s="31" t="n"/>
+      <c r="C424" s="33" t="n"/>
       <c r="D424" s="9" t="n"/>
       <c r="E424" s="9" t="n"/>
       <c r="F424" s="9" t="n"/>
@@ -7258,7 +7716,7 @@
     <row r="425">
       <c r="A425" s="9" t="n"/>
       <c r="B425" s="9" t="n"/>
-      <c r="C425" s="31" t="n"/>
+      <c r="C425" s="33" t="n"/>
       <c r="D425" s="9" t="n"/>
       <c r="E425" s="9" t="n"/>
       <c r="F425" s="9" t="n"/>
@@ -7267,7 +7725,7 @@
     <row r="426">
       <c r="A426" s="9" t="n"/>
       <c r="B426" s="9" t="n"/>
-      <c r="C426" s="31" t="n"/>
+      <c r="C426" s="33" t="n"/>
       <c r="D426" s="9" t="n"/>
       <c r="E426" s="9" t="n"/>
       <c r="F426" s="9" t="n"/>
@@ -7276,7 +7734,7 @@
     <row r="427">
       <c r="A427" s="9" t="n"/>
       <c r="B427" s="9" t="n"/>
-      <c r="C427" s="31" t="n"/>
+      <c r="C427" s="33" t="n"/>
       <c r="D427" s="9" t="n"/>
       <c r="E427" s="9" t="n"/>
       <c r="F427" s="9" t="n"/>
@@ -7285,7 +7743,7 @@
     <row r="428">
       <c r="A428" s="9" t="n"/>
       <c r="B428" s="9" t="n"/>
-      <c r="C428" s="31" t="n"/>
+      <c r="C428" s="33" t="n"/>
       <c r="D428" s="9" t="n"/>
       <c r="E428" s="9" t="n"/>
       <c r="F428" s="9" t="n"/>
@@ -7294,7 +7752,7 @@
     <row r="429">
       <c r="A429" s="9" t="n"/>
       <c r="B429" s="9" t="n"/>
-      <c r="C429" s="31" t="n"/>
+      <c r="C429" s="33" t="n"/>
       <c r="D429" s="9" t="n"/>
       <c r="E429" s="9" t="n"/>
       <c r="F429" s="9" t="n"/>
@@ -7303,7 +7761,7 @@
     <row r="430">
       <c r="A430" s="9" t="n"/>
       <c r="B430" s="9" t="n"/>
-      <c r="C430" s="31" t="n"/>
+      <c r="C430" s="33" t="n"/>
       <c r="D430" s="9" t="n"/>
       <c r="E430" s="9" t="n"/>
       <c r="F430" s="9" t="n"/>
@@ -7312,7 +7770,7 @@
     <row r="431">
       <c r="A431" s="9" t="n"/>
       <c r="B431" s="9" t="n"/>
-      <c r="C431" s="31" t="n"/>
+      <c r="C431" s="33" t="n"/>
       <c r="D431" s="9" t="n"/>
       <c r="E431" s="9" t="n"/>
       <c r="F431" s="9" t="n"/>
@@ -7321,7 +7779,7 @@
     <row r="432">
       <c r="A432" s="9" t="n"/>
       <c r="B432" s="9" t="n"/>
-      <c r="C432" s="31" t="n"/>
+      <c r="C432" s="33" t="n"/>
       <c r="D432" s="9" t="n"/>
       <c r="E432" s="9" t="n"/>
       <c r="F432" s="9" t="n"/>
@@ -7330,7 +7788,7 @@
     <row r="433">
       <c r="A433" s="9" t="n"/>
       <c r="B433" s="9" t="n"/>
-      <c r="C433" s="31" t="n"/>
+      <c r="C433" s="33" t="n"/>
       <c r="D433" s="9" t="n"/>
       <c r="E433" s="9" t="n"/>
       <c r="F433" s="9" t="n"/>
@@ -7339,7 +7797,7 @@
     <row r="434">
       <c r="A434" s="9" t="n"/>
       <c r="B434" s="9" t="n"/>
-      <c r="C434" s="31" t="n"/>
+      <c r="C434" s="33" t="n"/>
       <c r="D434" s="9" t="n"/>
       <c r="E434" s="9" t="n"/>
       <c r="F434" s="9" t="n"/>
@@ -7348,7 +7806,7 @@
     <row r="435">
       <c r="A435" s="9" t="n"/>
       <c r="B435" s="9" t="n"/>
-      <c r="C435" s="31" t="n"/>
+      <c r="C435" s="33" t="n"/>
       <c r="D435" s="9" t="n"/>
       <c r="E435" s="9" t="n"/>
       <c r="F435" s="9" t="n"/>
@@ -7357,7 +7815,7 @@
     <row r="436">
       <c r="A436" s="9" t="n"/>
       <c r="B436" s="9" t="n"/>
-      <c r="C436" s="31" t="n"/>
+      <c r="C436" s="33" t="n"/>
       <c r="D436" s="9" t="n"/>
       <c r="E436" s="9" t="n"/>
       <c r="F436" s="9" t="n"/>
@@ -7366,7 +7824,7 @@
     <row r="437">
       <c r="A437" s="9" t="n"/>
       <c r="B437" s="9" t="n"/>
-      <c r="C437" s="31" t="n"/>
+      <c r="C437" s="33" t="n"/>
       <c r="D437" s="9" t="n"/>
       <c r="E437" s="9" t="n"/>
       <c r="F437" s="9" t="n"/>
@@ -7375,7 +7833,7 @@
     <row r="438">
       <c r="A438" s="9" t="n"/>
       <c r="B438" s="9" t="n"/>
-      <c r="C438" s="31" t="n"/>
+      <c r="C438" s="33" t="n"/>
       <c r="D438" s="9" t="n"/>
       <c r="E438" s="9" t="n"/>
       <c r="F438" s="9" t="n"/>
@@ -7384,7 +7842,7 @@
     <row r="439">
       <c r="A439" s="9" t="n"/>
       <c r="B439" s="9" t="n"/>
-      <c r="C439" s="31" t="n"/>
+      <c r="C439" s="33" t="n"/>
       <c r="D439" s="9" t="n"/>
       <c r="E439" s="9" t="n"/>
       <c r="F439" s="9" t="n"/>
@@ -7393,7 +7851,7 @@
     <row r="440">
       <c r="A440" s="9" t="n"/>
       <c r="B440" s="9" t="n"/>
-      <c r="C440" s="31" t="n"/>
+      <c r="C440" s="33" t="n"/>
       <c r="D440" s="9" t="n"/>
       <c r="E440" s="9" t="n"/>
       <c r="F440" s="9" t="n"/>
@@ -7402,7 +7860,7 @@
     <row r="441">
       <c r="A441" s="9" t="n"/>
       <c r="B441" s="9" t="n"/>
-      <c r="C441" s="31" t="n"/>
+      <c r="C441" s="33" t="n"/>
       <c r="D441" s="9" t="n"/>
       <c r="E441" s="9" t="n"/>
       <c r="F441" s="9" t="n"/>
@@ -7411,7 +7869,7 @@
     <row r="442">
       <c r="A442" s="9" t="n"/>
       <c r="B442" s="9" t="n"/>
-      <c r="C442" s="31" t="n"/>
+      <c r="C442" s="33" t="n"/>
       <c r="D442" s="9" t="n"/>
       <c r="E442" s="9" t="n"/>
       <c r="F442" s="9" t="n"/>
@@ -7420,7 +7878,7 @@
     <row r="443">
       <c r="A443" s="9" t="n"/>
       <c r="B443" s="9" t="n"/>
-      <c r="C443" s="31" t="n"/>
+      <c r="C443" s="33" t="n"/>
       <c r="D443" s="9" t="n"/>
       <c r="E443" s="9" t="n"/>
       <c r="F443" s="9" t="n"/>
@@ -7429,7 +7887,7 @@
     <row r="444">
       <c r="A444" s="9" t="n"/>
       <c r="B444" s="9" t="n"/>
-      <c r="C444" s="31" t="n"/>
+      <c r="C444" s="33" t="n"/>
       <c r="D444" s="9" t="n"/>
       <c r="E444" s="9" t="n"/>
       <c r="F444" s="9" t="n"/>
@@ -7438,7 +7896,7 @@
     <row r="445">
       <c r="A445" s="9" t="n"/>
       <c r="B445" s="9" t="n"/>
-      <c r="C445" s="31" t="n"/>
+      <c r="C445" s="33" t="n"/>
       <c r="D445" s="9" t="n"/>
       <c r="E445" s="9" t="n"/>
       <c r="F445" s="9" t="n"/>
@@ -7447,7 +7905,7 @@
     <row r="446">
       <c r="A446" s="9" t="n"/>
       <c r="B446" s="9" t="n"/>
-      <c r="C446" s="31" t="n"/>
+      <c r="C446" s="33" t="n"/>
       <c r="D446" s="9" t="n"/>
       <c r="E446" s="9" t="n"/>
       <c r="F446" s="9" t="n"/>
@@ -7456,7 +7914,7 @@
     <row r="447">
       <c r="A447" s="9" t="n"/>
       <c r="B447" s="9" t="n"/>
-      <c r="C447" s="31" t="n"/>
+      <c r="C447" s="33" t="n"/>
       <c r="D447" s="9" t="n"/>
       <c r="E447" s="9" t="n"/>
       <c r="F447" s="9" t="n"/>
@@ -7465,7 +7923,7 @@
     <row r="448">
       <c r="A448" s="9" t="n"/>
       <c r="B448" s="9" t="n"/>
-      <c r="C448" s="31" t="n"/>
+      <c r="C448" s="33" t="n"/>
       <c r="D448" s="9" t="n"/>
       <c r="E448" s="9" t="n"/>
       <c r="F448" s="9" t="n"/>
@@ -7474,7 +7932,7 @@
     <row r="449">
       <c r="A449" s="9" t="n"/>
       <c r="B449" s="9" t="n"/>
-      <c r="C449" s="31" t="n"/>
+      <c r="C449" s="33" t="n"/>
       <c r="D449" s="9" t="n"/>
       <c r="E449" s="9" t="n"/>
       <c r="F449" s="9" t="n"/>
@@ -7483,7 +7941,7 @@
     <row r="450">
       <c r="A450" s="9" t="n"/>
       <c r="B450" s="9" t="n"/>
-      <c r="C450" s="31" t="n"/>
+      <c r="C450" s="33" t="n"/>
       <c r="D450" s="9" t="n"/>
       <c r="E450" s="9" t="n"/>
       <c r="F450" s="9" t="n"/>
@@ -7492,7 +7950,7 @@
     <row r="451">
       <c r="A451" s="9" t="n"/>
       <c r="B451" s="9" t="n"/>
-      <c r="C451" s="31" t="n"/>
+      <c r="C451" s="33" t="n"/>
       <c r="D451" s="9" t="n"/>
       <c r="E451" s="9" t="n"/>
       <c r="F451" s="9" t="n"/>
@@ -7501,7 +7959,7 @@
     <row r="452">
       <c r="A452" s="9" t="n"/>
       <c r="B452" s="9" t="n"/>
-      <c r="C452" s="31" t="n"/>
+      <c r="C452" s="33" t="n"/>
       <c r="D452" s="9" t="n"/>
       <c r="E452" s="9" t="n"/>
       <c r="F452" s="9" t="n"/>
@@ -7510,7 +7968,7 @@
     <row r="453">
       <c r="A453" s="9" t="n"/>
       <c r="B453" s="9" t="n"/>
-      <c r="C453" s="31" t="n"/>
+      <c r="C453" s="33" t="n"/>
       <c r="D453" s="9" t="n"/>
       <c r="E453" s="9" t="n"/>
       <c r="F453" s="9" t="n"/>
@@ -7519,7 +7977,7 @@
     <row r="454">
       <c r="A454" s="9" t="n"/>
       <c r="B454" s="9" t="n"/>
-      <c r="C454" s="31" t="n"/>
+      <c r="C454" s="33" t="n"/>
       <c r="D454" s="9" t="n"/>
       <c r="E454" s="9" t="n"/>
       <c r="F454" s="9" t="n"/>
@@ -7528,7 +7986,7 @@
     <row r="455">
       <c r="A455" s="9" t="n"/>
       <c r="B455" s="9" t="n"/>
-      <c r="C455" s="31" t="n"/>
+      <c r="C455" s="33" t="n"/>
       <c r="D455" s="9" t="n"/>
       <c r="E455" s="9" t="n"/>
       <c r="F455" s="9" t="n"/>
@@ -7537,7 +7995,7 @@
     <row r="456">
       <c r="A456" s="9" t="n"/>
       <c r="B456" s="9" t="n"/>
-      <c r="C456" s="31" t="n"/>
+      <c r="C456" s="33" t="n"/>
       <c r="D456" s="9" t="n"/>
       <c r="E456" s="9" t="n"/>
       <c r="F456" s="9" t="n"/>
@@ -7546,7 +8004,7 @@
     <row r="457">
       <c r="A457" s="9" t="n"/>
       <c r="B457" s="9" t="n"/>
-      <c r="C457" s="31" t="n"/>
+      <c r="C457" s="33" t="n"/>
       <c r="D457" s="9" t="n"/>
       <c r="E457" s="9" t="n"/>
       <c r="F457" s="9" t="n"/>
@@ -7555,7 +8013,7 @@
     <row r="458">
       <c r="A458" s="9" t="n"/>
       <c r="B458" s="9" t="n"/>
-      <c r="C458" s="31" t="n"/>
+      <c r="C458" s="33" t="n"/>
       <c r="D458" s="9" t="n"/>
       <c r="E458" s="9" t="n"/>
       <c r="F458" s="9" t="n"/>
@@ -7564,7 +8022,7 @@
     <row r="459">
       <c r="A459" s="9" t="n"/>
       <c r="B459" s="9" t="n"/>
-      <c r="C459" s="31" t="n"/>
+      <c r="C459" s="33" t="n"/>
       <c r="D459" s="9" t="n"/>
       <c r="E459" s="9" t="n"/>
       <c r="F459" s="9" t="n"/>
@@ -7573,7 +8031,7 @@
     <row r="460">
       <c r="A460" s="9" t="n"/>
       <c r="B460" s="9" t="n"/>
-      <c r="C460" s="31" t="n"/>
+      <c r="C460" s="33" t="n"/>
       <c r="D460" s="9" t="n"/>
       <c r="E460" s="9" t="n"/>
       <c r="F460" s="9" t="n"/>
@@ -7582,7 +8040,7 @@
     <row r="461">
       <c r="A461" s="9" t="n"/>
       <c r="B461" s="9" t="n"/>
-      <c r="C461" s="31" t="n"/>
+      <c r="C461" s="33" t="n"/>
       <c r="D461" s="9" t="n"/>
       <c r="E461" s="9" t="n"/>
       <c r="F461" s="9" t="n"/>
@@ -7591,7 +8049,7 @@
     <row r="462">
       <c r="A462" s="9" t="n"/>
       <c r="B462" s="9" t="n"/>
-      <c r="C462" s="31" t="n"/>
+      <c r="C462" s="33" t="n"/>
       <c r="D462" s="9" t="n"/>
       <c r="E462" s="9" t="n"/>
       <c r="F462" s="9" t="n"/>
@@ -7600,7 +8058,7 @@
     <row r="463">
       <c r="A463" s="9" t="n"/>
       <c r="B463" s="9" t="n"/>
-      <c r="C463" s="31" t="n"/>
+      <c r="C463" s="33" t="n"/>
       <c r="D463" s="9" t="n"/>
       <c r="E463" s="9" t="n"/>
       <c r="F463" s="9" t="n"/>
@@ -7609,7 +8067,7 @@
     <row r="464">
       <c r="A464" s="9" t="n"/>
       <c r="B464" s="9" t="n"/>
-      <c r="C464" s="31" t="n"/>
+      <c r="C464" s="33" t="n"/>
       <c r="D464" s="9" t="n"/>
       <c r="E464" s="9" t="n"/>
       <c r="F464" s="9" t="n"/>
@@ -7618,7 +8076,7 @@
     <row r="465">
       <c r="A465" s="9" t="n"/>
       <c r="B465" s="9" t="n"/>
-      <c r="C465" s="31" t="n"/>
+      <c r="C465" s="33" t="n"/>
       <c r="D465" s="9" t="n"/>
       <c r="E465" s="9" t="n"/>
       <c r="F465" s="9" t="n"/>
@@ -7627,7 +8085,7 @@
     <row r="466">
       <c r="A466" s="9" t="n"/>
       <c r="B466" s="9" t="n"/>
-      <c r="C466" s="31" t="n"/>
+      <c r="C466" s="33" t="n"/>
       <c r="D466" s="9" t="n"/>
       <c r="E466" s="9" t="n"/>
       <c r="F466" s="9" t="n"/>
@@ -7636,7 +8094,7 @@
     <row r="467">
       <c r="A467" s="9" t="n"/>
       <c r="B467" s="9" t="n"/>
-      <c r="C467" s="31" t="n"/>
+      <c r="C467" s="33" t="n"/>
       <c r="D467" s="9" t="n"/>
       <c r="E467" s="9" t="n"/>
       <c r="F467" s="9" t="n"/>
@@ -7645,7 +8103,7 @@
     <row r="468">
       <c r="A468" s="9" t="n"/>
       <c r="B468" s="9" t="n"/>
-      <c r="C468" s="31" t="n"/>
+      <c r="C468" s="33" t="n"/>
       <c r="D468" s="9" t="n"/>
       <c r="E468" s="9" t="n"/>
       <c r="F468" s="9" t="n"/>
@@ -7654,7 +8112,7 @@
     <row r="469">
       <c r="A469" s="9" t="n"/>
       <c r="B469" s="9" t="n"/>
-      <c r="C469" s="31" t="n"/>
+      <c r="C469" s="33" t="n"/>
       <c r="D469" s="9" t="n"/>
       <c r="E469" s="9" t="n"/>
       <c r="F469" s="9" t="n"/>
@@ -7663,7 +8121,7 @@
     <row r="470">
       <c r="A470" s="9" t="n"/>
       <c r="B470" s="9" t="n"/>
-      <c r="C470" s="31" t="n"/>
+      <c r="C470" s="33" t="n"/>
       <c r="D470" s="9" t="n"/>
       <c r="E470" s="9" t="n"/>
       <c r="F470" s="9" t="n"/>
@@ -7672,7 +8130,7 @@
     <row r="471">
       <c r="A471" s="9" t="n"/>
       <c r="B471" s="9" t="n"/>
-      <c r="C471" s="31" t="n"/>
+      <c r="C471" s="33" t="n"/>
       <c r="D471" s="9" t="n"/>
       <c r="E471" s="9" t="n"/>
       <c r="F471" s="9" t="n"/>
@@ -7681,7 +8139,7 @@
     <row r="472">
       <c r="A472" s="9" t="n"/>
       <c r="B472" s="9" t="n"/>
-      <c r="C472" s="31" t="n"/>
+      <c r="C472" s="33" t="n"/>
       <c r="D472" s="9" t="n"/>
       <c r="E472" s="9" t="n"/>
       <c r="F472" s="9" t="n"/>
@@ -7690,7 +8148,7 @@
     <row r="473">
       <c r="A473" s="9" t="n"/>
       <c r="B473" s="9" t="n"/>
-      <c r="C473" s="31" t="n"/>
+      <c r="C473" s="33" t="n"/>
       <c r="D473" s="9" t="n"/>
       <c r="E473" s="9" t="n"/>
       <c r="F473" s="9" t="n"/>
@@ -7699,7 +8157,7 @@
     <row r="474">
       <c r="A474" s="9" t="n"/>
       <c r="B474" s="9" t="n"/>
-      <c r="C474" s="31" t="n"/>
+      <c r="C474" s="33" t="n"/>
       <c r="D474" s="9" t="n"/>
       <c r="E474" s="9" t="n"/>
       <c r="F474" s="9" t="n"/>
@@ -7708,7 +8166,7 @@
     <row r="475">
       <c r="A475" s="9" t="n"/>
       <c r="B475" s="9" t="n"/>
-      <c r="C475" s="31" t="n"/>
+      <c r="C475" s="33" t="n"/>
       <c r="D475" s="9" t="n"/>
       <c r="E475" s="9" t="n"/>
       <c r="F475" s="9" t="n"/>
@@ -7717,7 +8175,7 @@
     <row r="476">
       <c r="A476" s="9" t="n"/>
       <c r="B476" s="9" t="n"/>
-      <c r="C476" s="31" t="n"/>
+      <c r="C476" s="33" t="n"/>
       <c r="D476" s="9" t="n"/>
       <c r="E476" s="9" t="n"/>
       <c r="F476" s="9" t="n"/>
@@ -7726,7 +8184,7 @@
     <row r="477">
       <c r="A477" s="9" t="n"/>
       <c r="B477" s="9" t="n"/>
-      <c r="C477" s="31" t="n"/>
+      <c r="C477" s="33" t="n"/>
       <c r="D477" s="9" t="n"/>
       <c r="E477" s="9" t="n"/>
       <c r="F477" s="9" t="n"/>
@@ -7735,7 +8193,7 @@
     <row r="478">
       <c r="A478" s="9" t="n"/>
       <c r="B478" s="9" t="n"/>
-      <c r="C478" s="31" t="n"/>
+      <c r="C478" s="33" t="n"/>
       <c r="D478" s="9" t="n"/>
       <c r="E478" s="9" t="n"/>
       <c r="F478" s="9" t="n"/>
@@ -7744,7 +8202,7 @@
     <row r="479">
       <c r="A479" s="9" t="n"/>
       <c r="B479" s="9" t="n"/>
-      <c r="C479" s="31" t="n"/>
+      <c r="C479" s="33" t="n"/>
       <c r="D479" s="9" t="n"/>
       <c r="E479" s="9" t="n"/>
       <c r="F479" s="9" t="n"/>
@@ -7753,7 +8211,7 @@
     <row r="480">
       <c r="A480" s="9" t="n"/>
       <c r="B480" s="9" t="n"/>
-      <c r="C480" s="31" t="n"/>
+      <c r="C480" s="33" t="n"/>
       <c r="D480" s="9" t="n"/>
       <c r="E480" s="9" t="n"/>
       <c r="F480" s="9" t="n"/>
@@ -7762,7 +8220,7 @@
     <row r="481">
       <c r="A481" s="9" t="n"/>
       <c r="B481" s="9" t="n"/>
-      <c r="C481" s="31" t="n"/>
+      <c r="C481" s="33" t="n"/>
       <c r="D481" s="9" t="n"/>
       <c r="E481" s="9" t="n"/>
       <c r="F481" s="9" t="n"/>
@@ -7771,7 +8229,7 @@
     <row r="482">
       <c r="A482" s="9" t="n"/>
       <c r="B482" s="9" t="n"/>
-      <c r="C482" s="31" t="n"/>
+      <c r="C482" s="33" t="n"/>
       <c r="D482" s="9" t="n"/>
       <c r="E482" s="9" t="n"/>
       <c r="F482" s="9" t="n"/>
@@ -7780,7 +8238,7 @@
     <row r="483">
       <c r="A483" s="9" t="n"/>
       <c r="B483" s="9" t="n"/>
-      <c r="C483" s="31" t="n"/>
+      <c r="C483" s="33" t="n"/>
       <c r="D483" s="9" t="n"/>
       <c r="E483" s="9" t="n"/>
       <c r="F483" s="9" t="n"/>
@@ -7789,7 +8247,7 @@
     <row r="484">
       <c r="A484" s="9" t="n"/>
       <c r="B484" s="9" t="n"/>
-      <c r="C484" s="31" t="n"/>
+      <c r="C484" s="33" t="n"/>
       <c r="D484" s="9" t="n"/>
       <c r="E484" s="9" t="n"/>
       <c r="F484" s="9" t="n"/>
@@ -7798,7 +8256,7 @@
     <row r="485">
       <c r="A485" s="9" t="n"/>
       <c r="B485" s="9" t="n"/>
-      <c r="C485" s="31" t="n"/>
+      <c r="C485" s="33" t="n"/>
       <c r="D485" s="9" t="n"/>
       <c r="E485" s="9" t="n"/>
       <c r="F485" s="9" t="n"/>
@@ -7807,7 +8265,7 @@
     <row r="486">
       <c r="A486" s="9" t="n"/>
       <c r="B486" s="9" t="n"/>
-      <c r="C486" s="31" t="n"/>
+      <c r="C486" s="33" t="n"/>
       <c r="D486" s="9" t="n"/>
       <c r="E486" s="9" t="n"/>
       <c r="F486" s="9" t="n"/>
@@ -7816,7 +8274,7 @@
     <row r="487">
       <c r="A487" s="9" t="n"/>
       <c r="B487" s="9" t="n"/>
-      <c r="C487" s="31" t="n"/>
+      <c r="C487" s="33" t="n"/>
       <c r="D487" s="9" t="n"/>
       <c r="E487" s="9" t="n"/>
       <c r="F487" s="9" t="n"/>
@@ -7825,7 +8283,7 @@
     <row r="488">
       <c r="A488" s="9" t="n"/>
       <c r="B488" s="9" t="n"/>
-      <c r="C488" s="31" t="n"/>
+      <c r="C488" s="33" t="n"/>
       <c r="D488" s="9" t="n"/>
       <c r="E488" s="9" t="n"/>
       <c r="F488" s="9" t="n"/>
@@ -7834,7 +8292,7 @@
     <row r="489">
       <c r="A489" s="9" t="n"/>
       <c r="B489" s="9" t="n"/>
-      <c r="C489" s="31" t="n"/>
+      <c r="C489" s="33" t="n"/>
       <c r="D489" s="9" t="n"/>
       <c r="E489" s="9" t="n"/>
       <c r="F489" s="9" t="n"/>
@@ -7843,7 +8301,7 @@
     <row r="490">
       <c r="A490" s="9" t="n"/>
       <c r="B490" s="9" t="n"/>
-      <c r="C490" s="31" t="n"/>
+      <c r="C490" s="33" t="n"/>
       <c r="D490" s="9" t="n"/>
       <c r="E490" s="9" t="n"/>
       <c r="F490" s="9" t="n"/>
@@ -7852,7 +8310,7 @@
     <row r="491">
       <c r="A491" s="9" t="n"/>
       <c r="B491" s="9" t="n"/>
-      <c r="C491" s="31" t="n"/>
+      <c r="C491" s="33" t="n"/>
       <c r="D491" s="9" t="n"/>
       <c r="E491" s="9" t="n"/>
       <c r="F491" s="9" t="n"/>
@@ -7861,7 +8319,7 @@
     <row r="492">
       <c r="A492" s="9" t="n"/>
       <c r="B492" s="9" t="n"/>
-      <c r="C492" s="31" t="n"/>
+      <c r="C492" s="33" t="n"/>
       <c r="D492" s="9" t="n"/>
       <c r="E492" s="9" t="n"/>
       <c r="F492" s="9" t="n"/>
@@ -7870,7 +8328,7 @@
     <row r="493">
       <c r="A493" s="9" t="n"/>
       <c r="B493" s="9" t="n"/>
-      <c r="C493" s="31" t="n"/>
+      <c r="C493" s="33" t="n"/>
       <c r="D493" s="9" t="n"/>
       <c r="E493" s="9" t="n"/>
       <c r="F493" s="9" t="n"/>
@@ -7879,7 +8337,7 @@
     <row r="494">
       <c r="A494" s="9" t="n"/>
       <c r="B494" s="9" t="n"/>
-      <c r="C494" s="31" t="n"/>
+      <c r="C494" s="33" t="n"/>
       <c r="D494" s="9" t="n"/>
       <c r="E494" s="9" t="n"/>
       <c r="F494" s="9" t="n"/>
@@ -7888,7 +8346,7 @@
     <row r="495">
       <c r="A495" s="9" t="n"/>
       <c r="B495" s="9" t="n"/>
-      <c r="C495" s="31" t="n"/>
+      <c r="C495" s="33" t="n"/>
       <c r="D495" s="9" t="n"/>
       <c r="E495" s="9" t="n"/>
       <c r="F495" s="9" t="n"/>
@@ -7897,7 +8355,7 @@
     <row r="496">
       <c r="A496" s="9" t="n"/>
       <c r="B496" s="9" t="n"/>
-      <c r="C496" s="31" t="n"/>
+      <c r="C496" s="33" t="n"/>
       <c r="D496" s="9" t="n"/>
       <c r="E496" s="9" t="n"/>
       <c r="F496" s="9" t="n"/>
@@ -7906,7 +8364,7 @@
     <row r="497">
       <c r="A497" s="9" t="n"/>
       <c r="B497" s="9" t="n"/>
-      <c r="C497" s="31" t="n"/>
+      <c r="C497" s="33" t="n"/>
       <c r="D497" s="9" t="n"/>
       <c r="E497" s="9" t="n"/>
       <c r="F497" s="9" t="n"/>
@@ -7915,7 +8373,7 @@
     <row r="498">
       <c r="A498" s="9" t="n"/>
       <c r="B498" s="9" t="n"/>
-      <c r="C498" s="31" t="n"/>
+      <c r="C498" s="33" t="n"/>
       <c r="D498" s="9" t="n"/>
       <c r="E498" s="9" t="n"/>
       <c r="F498" s="9" t="n"/>
@@ -7924,7 +8382,7 @@
     <row r="499">
       <c r="A499" s="9" t="n"/>
       <c r="B499" s="9" t="n"/>
-      <c r="C499" s="31" t="n"/>
+      <c r="C499" s="33" t="n"/>
       <c r="D499" s="9" t="n"/>
       <c r="E499" s="9" t="n"/>
       <c r="F499" s="9" t="n"/>
@@ -7933,7 +8391,7 @@
     <row r="500">
       <c r="A500" s="9" t="n"/>
       <c r="B500" s="9" t="n"/>
-      <c r="C500" s="31" t="n"/>
+      <c r="C500" s="33" t="n"/>
       <c r="D500" s="9" t="n"/>
       <c r="E500" s="9" t="n"/>
       <c r="F500" s="9" t="n"/>
@@ -7942,7 +8400,7 @@
     <row r="501">
       <c r="A501" s="9" t="n"/>
       <c r="B501" s="9" t="n"/>
-      <c r="C501" s="31" t="n"/>
+      <c r="C501" s="33" t="n"/>
       <c r="D501" s="9" t="n"/>
       <c r="E501" s="9" t="n"/>
       <c r="F501" s="9" t="n"/>
@@ -7951,7 +8409,7 @@
     <row r="502">
       <c r="A502" s="9" t="n"/>
       <c r="B502" s="9" t="n"/>
-      <c r="C502" s="31" t="n"/>
+      <c r="C502" s="33" t="n"/>
       <c r="D502" s="9" t="n"/>
       <c r="E502" s="9" t="n"/>
       <c r="F502" s="9" t="n"/>
@@ -7960,7 +8418,7 @@
     <row r="503">
       <c r="A503" s="9" t="n"/>
       <c r="B503" s="9" t="n"/>
-      <c r="C503" s="31" t="n"/>
+      <c r="C503" s="33" t="n"/>
       <c r="D503" s="9" t="n"/>
       <c r="E503" s="9" t="n"/>
       <c r="F503" s="9" t="n"/>
@@ -7969,7 +8427,7 @@
     <row r="504">
       <c r="A504" s="9" t="n"/>
       <c r="B504" s="9" t="n"/>
-      <c r="C504" s="31" t="n"/>
+      <c r="C504" s="33" t="n"/>
       <c r="D504" s="9" t="n"/>
       <c r="E504" s="9" t="n"/>
       <c r="F504" s="9" t="n"/>
@@ -7978,7 +8436,7 @@
     <row r="505">
       <c r="A505" s="9" t="n"/>
       <c r="B505" s="9" t="n"/>
-      <c r="C505" s="31" t="n"/>
+      <c r="C505" s="33" t="n"/>
       <c r="D505" s="9" t="n"/>
       <c r="E505" s="9" t="n"/>
       <c r="F505" s="9" t="n"/>
@@ -7987,7 +8445,7 @@
     <row r="506">
       <c r="A506" s="9" t="n"/>
       <c r="B506" s="9" t="n"/>
-      <c r="C506" s="31" t="n"/>
+      <c r="C506" s="33" t="n"/>
       <c r="D506" s="9" t="n"/>
       <c r="E506" s="9" t="n"/>
       <c r="F506" s="9" t="n"/>
@@ -7996,7 +8454,7 @@
     <row r="507">
       <c r="A507" s="9" t="n"/>
       <c r="B507" s="9" t="n"/>
-      <c r="C507" s="31" t="n"/>
+      <c r="C507" s="33" t="n"/>
       <c r="D507" s="9" t="n"/>
       <c r="E507" s="9" t="n"/>
       <c r="F507" s="9" t="n"/>
@@ -8005,7 +8463,7 @@
     <row r="508">
       <c r="A508" s="9" t="n"/>
       <c r="B508" s="9" t="n"/>
-      <c r="C508" s="31" t="n"/>
+      <c r="C508" s="33" t="n"/>
       <c r="D508" s="9" t="n"/>
       <c r="E508" s="9" t="n"/>
       <c r="F508" s="9" t="n"/>
@@ -8014,7 +8472,7 @@
     <row r="509">
       <c r="A509" s="9" t="n"/>
       <c r="B509" s="9" t="n"/>
-      <c r="C509" s="31" t="n"/>
+      <c r="C509" s="33" t="n"/>
       <c r="D509" s="9" t="n"/>
       <c r="E509" s="9" t="n"/>
       <c r="F509" s="9" t="n"/>
@@ -8023,7 +8481,7 @@
     <row r="510">
       <c r="A510" s="9" t="n"/>
       <c r="B510" s="9" t="n"/>
-      <c r="C510" s="31" t="n"/>
+      <c r="C510" s="33" t="n"/>
       <c r="D510" s="9" t="n"/>
       <c r="E510" s="9" t="n"/>
       <c r="F510" s="9" t="n"/>
@@ -8032,7 +8490,7 @@
     <row r="511">
       <c r="A511" s="9" t="n"/>
       <c r="B511" s="9" t="n"/>
-      <c r="C511" s="31" t="n"/>
+      <c r="C511" s="33" t="n"/>
       <c r="D511" s="9" t="n"/>
       <c r="E511" s="9" t="n"/>
       <c r="F511" s="9" t="n"/>
@@ -8041,7 +8499,7 @@
     <row r="512">
       <c r="A512" s="9" t="n"/>
       <c r="B512" s="9" t="n"/>
-      <c r="C512" s="31" t="n"/>
+      <c r="C512" s="33" t="n"/>
       <c r="D512" s="9" t="n"/>
       <c r="E512" s="9" t="n"/>
       <c r="F512" s="9" t="n"/>
@@ -8050,7 +8508,7 @@
     <row r="513">
       <c r="A513" s="9" t="n"/>
       <c r="B513" s="9" t="n"/>
-      <c r="C513" s="31" t="n"/>
+      <c r="C513" s="33" t="n"/>
       <c r="D513" s="9" t="n"/>
       <c r="E513" s="9" t="n"/>
       <c r="F513" s="9" t="n"/>
@@ -8059,7 +8517,7 @@
     <row r="514">
       <c r="A514" s="9" t="n"/>
       <c r="B514" s="9" t="n"/>
-      <c r="C514" s="31" t="n"/>
+      <c r="C514" s="33" t="n"/>
       <c r="D514" s="9" t="n"/>
       <c r="E514" s="9" t="n"/>
       <c r="F514" s="9" t="n"/>
@@ -8068,7 +8526,7 @@
     <row r="515">
       <c r="A515" s="9" t="n"/>
       <c r="B515" s="9" t="n"/>
-      <c r="C515" s="31" t="n"/>
+      <c r="C515" s="33" t="n"/>
       <c r="D515" s="9" t="n"/>
       <c r="E515" s="9" t="n"/>
       <c r="F515" s="9" t="n"/>
@@ -8077,7 +8535,7 @@
     <row r="516">
       <c r="A516" s="9" t="n"/>
       <c r="B516" s="9" t="n"/>
-      <c r="C516" s="31" t="n"/>
+      <c r="C516" s="33" t="n"/>
       <c r="D516" s="9" t="n"/>
       <c r="E516" s="9" t="n"/>
       <c r="F516" s="9" t="n"/>
@@ -8086,7 +8544,7 @@
     <row r="517">
       <c r="A517" s="9" t="n"/>
       <c r="B517" s="9" t="n"/>
-      <c r="C517" s="31" t="n"/>
+      <c r="C517" s="33" t="n"/>
       <c r="D517" s="9" t="n"/>
       <c r="E517" s="9" t="n"/>
       <c r="F517" s="9" t="n"/>
@@ -8095,7 +8553,7 @@
     <row r="518">
       <c r="A518" s="9" t="n"/>
       <c r="B518" s="9" t="n"/>
-      <c r="C518" s="31" t="n"/>
+      <c r="C518" s="33" t="n"/>
       <c r="D518" s="9" t="n"/>
       <c r="E518" s="9" t="n"/>
       <c r="F518" s="9" t="n"/>
@@ -8104,7 +8562,7 @@
     <row r="519">
       <c r="A519" s="9" t="n"/>
       <c r="B519" s="9" t="n"/>
-      <c r="C519" s="31" t="n"/>
+      <c r="C519" s="33" t="n"/>
       <c r="D519" s="9" t="n"/>
       <c r="E519" s="9" t="n"/>
       <c r="F519" s="9" t="n"/>
@@ -8113,7 +8571,7 @@
     <row r="520">
       <c r="A520" s="9" t="n"/>
       <c r="B520" s="9" t="n"/>
-      <c r="C520" s="31" t="n"/>
+      <c r="C520" s="33" t="n"/>
       <c r="D520" s="9" t="n"/>
       <c r="E520" s="9" t="n"/>
       <c r="F520" s="9" t="n"/>
@@ -8122,7 +8580,7 @@
     <row r="521">
       <c r="A521" s="9" t="n"/>
       <c r="B521" s="9" t="n"/>
-      <c r="C521" s="31" t="n"/>
+      <c r="C521" s="33" t="n"/>
       <c r="D521" s="9" t="n"/>
       <c r="E521" s="9" t="n"/>
       <c r="F521" s="9" t="n"/>
@@ -8131,7 +8589,7 @@
     <row r="522">
       <c r="A522" s="9" t="n"/>
       <c r="B522" s="9" t="n"/>
-      <c r="C522" s="31" t="n"/>
+      <c r="C522" s="33" t="n"/>
       <c r="D522" s="9" t="n"/>
       <c r="E522" s="9" t="n"/>
       <c r="F522" s="9" t="n"/>
@@ -8140,7 +8598,7 @@
     <row r="523">
       <c r="A523" s="9" t="n"/>
       <c r="B523" s="9" t="n"/>
-      <c r="C523" s="31" t="n"/>
+      <c r="C523" s="33" t="n"/>
       <c r="D523" s="9" t="n"/>
       <c r="E523" s="9" t="n"/>
       <c r="F523" s="9" t="n"/>
@@ -8149,7 +8607,7 @@
     <row r="524">
       <c r="A524" s="9" t="n"/>
       <c r="B524" s="9" t="n"/>
-      <c r="C524" s="31" t="n"/>
+      <c r="C524" s="33" t="n"/>
       <c r="D524" s="9" t="n"/>
       <c r="E524" s="9" t="n"/>
       <c r="F524" s="9" t="n"/>
@@ -8158,7 +8616,7 @@
     <row r="525">
       <c r="A525" s="9" t="n"/>
       <c r="B525" s="9" t="n"/>
-      <c r="C525" s="31" t="n"/>
+      <c r="C525" s="33" t="n"/>
       <c r="D525" s="9" t="n"/>
       <c r="E525" s="9" t="n"/>
       <c r="F525" s="9" t="n"/>
@@ -8167,7 +8625,7 @@
     <row r="526">
       <c r="A526" s="9" t="n"/>
       <c r="B526" s="9" t="n"/>
-      <c r="C526" s="31" t="n"/>
+      <c r="C526" s="33" t="n"/>
       <c r="D526" s="9" t="n"/>
       <c r="E526" s="9" t="n"/>
       <c r="F526" s="9" t="n"/>
@@ -8176,7 +8634,7 @@
     <row r="527">
       <c r="A527" s="9" t="n"/>
       <c r="B527" s="9" t="n"/>
-      <c r="C527" s="31" t="n"/>
+      <c r="C527" s="33" t="n"/>
       <c r="D527" s="9" t="n"/>
       <c r="E527" s="9" t="n"/>
       <c r="F527" s="9" t="n"/>
@@ -8185,7 +8643,7 @@
     <row r="528">
       <c r="A528" s="9" t="n"/>
       <c r="B528" s="9" t="n"/>
-      <c r="C528" s="31" t="n"/>
+      <c r="C528" s="33" t="n"/>
       <c r="D528" s="9" t="n"/>
       <c r="E528" s="9" t="n"/>
       <c r="F528" s="9" t="n"/>
@@ -8194,7 +8652,7 @@
     <row r="529">
       <c r="A529" s="9" t="n"/>
       <c r="B529" s="9" t="n"/>
-      <c r="C529" s="31" t="n"/>
+      <c r="C529" s="33" t="n"/>
       <c r="D529" s="9" t="n"/>
       <c r="E529" s="9" t="n"/>
       <c r="F529" s="9" t="n"/>
@@ -8203,7 +8661,7 @@
     <row r="530">
       <c r="A530" s="9" t="n"/>
       <c r="B530" s="9" t="n"/>
-      <c r="C530" s="31" t="n"/>
+      <c r="C530" s="33" t="n"/>
       <c r="D530" s="9" t="n"/>
       <c r="E530" s="9" t="n"/>
       <c r="F530" s="9" t="n"/>
@@ -8212,7 +8670,7 @@
     <row r="531">
       <c r="A531" s="9" t="n"/>
       <c r="B531" s="9" t="n"/>
-      <c r="C531" s="31" t="n"/>
+      <c r="C531" s="33" t="n"/>
       <c r="D531" s="9" t="n"/>
       <c r="E531" s="9" t="n"/>
       <c r="F531" s="9" t="n"/>
@@ -8221,7 +8679,7 @@
     <row r="532">
       <c r="A532" s="9" t="n"/>
       <c r="B532" s="9" t="n"/>
-      <c r="C532" s="31" t="n"/>
+      <c r="C532" s="33" t="n"/>
       <c r="D532" s="9" t="n"/>
       <c r="E532" s="9" t="n"/>
       <c r="F532" s="9" t="n"/>
@@ -8230,7 +8688,7 @@
     <row r="533">
       <c r="A533" s="9" t="n"/>
       <c r="B533" s="9" t="n"/>
-      <c r="C533" s="31" t="n"/>
+      <c r="C533" s="33" t="n"/>
       <c r="D533" s="9" t="n"/>
       <c r="E533" s="9" t="n"/>
       <c r="F533" s="9" t="n"/>
@@ -8239,7 +8697,7 @@
     <row r="534">
       <c r="A534" s="9" t="n"/>
       <c r="B534" s="9" t="n"/>
-      <c r="C534" s="31" t="n"/>
+      <c r="C534" s="33" t="n"/>
       <c r="D534" s="9" t="n"/>
       <c r="E534" s="9" t="n"/>
       <c r="F534" s="9" t="n"/>
@@ -8248,7 +8706,7 @@
     <row r="535">
       <c r="A535" s="9" t="n"/>
       <c r="B535" s="9" t="n"/>
-      <c r="C535" s="31" t="n"/>
+      <c r="C535" s="33" t="n"/>
       <c r="D535" s="9" t="n"/>
       <c r="E535" s="9" t="n"/>
       <c r="F535" s="9" t="n"/>
@@ -8257,7 +8715,7 @@
     <row r="536">
       <c r="A536" s="9" t="n"/>
       <c r="B536" s="9" t="n"/>
-      <c r="C536" s="31" t="n"/>
+      <c r="C536" s="33" t="n"/>
       <c r="D536" s="9" t="n"/>
       <c r="E536" s="9" t="n"/>
       <c r="F536" s="9" t="n"/>
@@ -8266,7 +8724,7 @@
     <row r="537">
       <c r="A537" s="9" t="n"/>
       <c r="B537" s="9" t="n"/>
-      <c r="C537" s="31" t="n"/>
+      <c r="C537" s="33" t="n"/>
       <c r="D537" s="9" t="n"/>
       <c r="E537" s="9" t="n"/>
       <c r="F537" s="9" t="n"/>
@@ -8275,7 +8733,7 @@
     <row r="538">
       <c r="A538" s="9" t="n"/>
       <c r="B538" s="9" t="n"/>
-      <c r="C538" s="31" t="n"/>
+      <c r="C538" s="33" t="n"/>
       <c r="D538" s="9" t="n"/>
       <c r="E538" s="9" t="n"/>
       <c r="F538" s="9" t="n"/>
@@ -8284,7 +8742,7 @@
     <row r="539">
       <c r="A539" s="9" t="n"/>
       <c r="B539" s="9" t="n"/>
-      <c r="C539" s="31" t="n"/>
+      <c r="C539" s="33" t="n"/>
       <c r="D539" s="9" t="n"/>
       <c r="E539" s="9" t="n"/>
       <c r="F539" s="9" t="n"/>
@@ -8293,7 +8751,7 @@
     <row r="540">
       <c r="A540" s="9" t="n"/>
       <c r="B540" s="9" t="n"/>
-      <c r="C540" s="31" t="n"/>
+      <c r="C540" s="33" t="n"/>
       <c r="D540" s="9" t="n"/>
       <c r="E540" s="9" t="n"/>
       <c r="F540" s="9" t="n"/>
@@ -8302,7 +8760,7 @@
     <row r="541">
       <c r="A541" s="9" t="n"/>
       <c r="B541" s="9" t="n"/>
-      <c r="C541" s="31" t="n"/>
+      <c r="C541" s="33" t="n"/>
       <c r="D541" s="9" t="n"/>
       <c r="E541" s="9" t="n"/>
       <c r="F541" s="9" t="n"/>
@@ -8311,7 +8769,7 @@
     <row r="542">
       <c r="A542" s="9" t="n"/>
       <c r="B542" s="9" t="n"/>
-      <c r="C542" s="31" t="n"/>
+      <c r="C542" s="33" t="n"/>
       <c r="D542" s="9" t="n"/>
       <c r="E542" s="9" t="n"/>
       <c r="F542" s="9" t="n"/>
@@ -8320,7 +8778,7 @@
     <row r="543">
       <c r="A543" s="9" t="n"/>
       <c r="B543" s="9" t="n"/>
-      <c r="C543" s="31" t="n"/>
+      <c r="C543" s="33" t="n"/>
       <c r="D543" s="9" t="n"/>
       <c r="E543" s="9" t="n"/>
       <c r="F543" s="9" t="n"/>
@@ -8329,7 +8787,7 @@
     <row r="544">
       <c r="A544" s="9" t="n"/>
       <c r="B544" s="9" t="n"/>
-      <c r="C544" s="31" t="n"/>
+      <c r="C544" s="33" t="n"/>
       <c r="D544" s="9" t="n"/>
       <c r="E544" s="9" t="n"/>
       <c r="F544" s="9" t="n"/>
@@ -8338,7 +8796,7 @@
     <row r="545">
       <c r="A545" s="9" t="n"/>
       <c r="B545" s="9" t="n"/>
-      <c r="C545" s="31" t="n"/>
+      <c r="C545" s="33" t="n"/>
       <c r="D545" s="9" t="n"/>
       <c r="E545" s="9" t="n"/>
       <c r="F545" s="9" t="n"/>
@@ -8347,7 +8805,7 @@
     <row r="546">
       <c r="A546" s="9" t="n"/>
       <c r="B546" s="9" t="n"/>
-      <c r="C546" s="31" t="n"/>
+      <c r="C546" s="33" t="n"/>
       <c r="D546" s="9" t="n"/>
       <c r="E546" s="9" t="n"/>
       <c r="F546" s="9" t="n"/>
@@ -8356,7 +8814,7 @@
     <row r="547">
       <c r="A547" s="9" t="n"/>
       <c r="B547" s="9" t="n"/>
-      <c r="C547" s="31" t="n"/>
+      <c r="C547" s="33" t="n"/>
       <c r="D547" s="9" t="n"/>
       <c r="E547" s="9" t="n"/>
       <c r="F547" s="9" t="n"/>
@@ -8365,7 +8823,7 @@
     <row r="548">
       <c r="A548" s="9" t="n"/>
       <c r="B548" s="9" t="n"/>
-      <c r="C548" s="31" t="n"/>
+      <c r="C548" s="33" t="n"/>
       <c r="D548" s="9" t="n"/>
       <c r="E548" s="9" t="n"/>
       <c r="F548" s="9" t="n"/>
@@ -8374,7 +8832,7 @@
     <row r="549">
       <c r="A549" s="9" t="n"/>
       <c r="B549" s="9" t="n"/>
-      <c r="C549" s="31" t="n"/>
+      <c r="C549" s="33" t="n"/>
       <c r="D549" s="9" t="n"/>
       <c r="E549" s="9" t="n"/>
       <c r="F549" s="9" t="n"/>
@@ -8383,7 +8841,7 @@
     <row r="550">
       <c r="A550" s="9" t="n"/>
       <c r="B550" s="9" t="n"/>
-      <c r="C550" s="31" t="n"/>
+      <c r="C550" s="33" t="n"/>
       <c r="D550" s="9" t="n"/>
       <c r="E550" s="9" t="n"/>
       <c r="F550" s="9" t="n"/>
@@ -8392,7 +8850,7 @@
     <row r="551">
       <c r="A551" s="9" t="n"/>
       <c r="B551" s="9" t="n"/>
-      <c r="C551" s="31" t="n"/>
+      <c r="C551" s="33" t="n"/>
       <c r="D551" s="9" t="n"/>
       <c r="E551" s="9" t="n"/>
       <c r="F551" s="9" t="n"/>
@@ -8401,7 +8859,7 @@
     <row r="552">
       <c r="A552" s="9" t="n"/>
       <c r="B552" s="9" t="n"/>
-      <c r="C552" s="31" t="n"/>
+      <c r="C552" s="33" t="n"/>
       <c r="D552" s="9" t="n"/>
       <c r="E552" s="9" t="n"/>
       <c r="F552" s="9" t="n"/>
@@ -8410,7 +8868,7 @@
     <row r="553">
       <c r="A553" s="9" t="n"/>
       <c r="B553" s="9" t="n"/>
-      <c r="C553" s="31" t="n"/>
+      <c r="C553" s="33" t="n"/>
       <c r="D553" s="9" t="n"/>
       <c r="E553" s="9" t="n"/>
       <c r="F553" s="9" t="n"/>
@@ -8419,7 +8877,7 @@
     <row r="554">
       <c r="A554" s="9" t="n"/>
       <c r="B554" s="9" t="n"/>
-      <c r="C554" s="31" t="n"/>
+      <c r="C554" s="33" t="n"/>
       <c r="D554" s="9" t="n"/>
       <c r="E554" s="9" t="n"/>
       <c r="F554" s="9" t="n"/>
@@ -8428,7 +8886,7 @@
     <row r="555">
       <c r="A555" s="9" t="n"/>
       <c r="B555" s="9" t="n"/>
-      <c r="C555" s="31" t="n"/>
+      <c r="C555" s="33" t="n"/>
       <c r="D555" s="9" t="n"/>
       <c r="E555" s="9" t="n"/>
       <c r="F555" s="9" t="n"/>
@@ -8437,7 +8895,7 @@
     <row r="556">
       <c r="A556" s="9" t="n"/>
       <c r="B556" s="9" t="n"/>
-      <c r="C556" s="31" t="n"/>
+      <c r="C556" s="33" t="n"/>
       <c r="D556" s="9" t="n"/>
       <c r="E556" s="9" t="n"/>
       <c r="F556" s="9" t="n"/>
@@ -8446,7 +8904,7 @@
     <row r="557">
       <c r="A557" s="9" t="n"/>
       <c r="B557" s="9" t="n"/>
-      <c r="C557" s="31" t="n"/>
+      <c r="C557" s="33" t="n"/>
       <c r="D557" s="9" t="n"/>
       <c r="E557" s="9" t="n"/>
       <c r="F557" s="9" t="n"/>
@@ -8455,7 +8913,7 @@
     <row r="558">
       <c r="A558" s="9" t="n"/>
       <c r="B558" s="9" t="n"/>
-      <c r="C558" s="31" t="n"/>
+      <c r="C558" s="33" t="n"/>
       <c r="D558" s="9" t="n"/>
       <c r="E558" s="9" t="n"/>
       <c r="F558" s="9" t="n"/>
@@ -8464,7 +8922,7 @@
     <row r="559">
       <c r="A559" s="9" t="n"/>
       <c r="B559" s="9" t="n"/>
-      <c r="C559" s="31" t="n"/>
+      <c r="C559" s="33" t="n"/>
       <c r="D559" s="9" t="n"/>
       <c r="E559" s="9" t="n"/>
       <c r="F559" s="9" t="n"/>
@@ -8473,7 +8931,7 @@
     <row r="560">
       <c r="A560" s="9" t="n"/>
       <c r="B560" s="9" t="n"/>
-      <c r="C560" s="31" t="n"/>
+      <c r="C560" s="33" t="n"/>
       <c r="D560" s="9" t="n"/>
       <c r="E560" s="9" t="n"/>
       <c r="F560" s="9" t="n"/>
@@ -8482,7 +8940,7 @@
     <row r="561">
       <c r="A561" s="9" t="n"/>
       <c r="B561" s="9" t="n"/>
-      <c r="C561" s="31" t="n"/>
+      <c r="C561" s="33" t="n"/>
       <c r="D561" s="9" t="n"/>
       <c r="E561" s="9" t="n"/>
       <c r="F561" s="9" t="n"/>
@@ -8491,7 +8949,7 @@
     <row r="562">
       <c r="A562" s="9" t="n"/>
       <c r="B562" s="9" t="n"/>
-      <c r="C562" s="31" t="n"/>
+      <c r="C562" s="33" t="n"/>
       <c r="D562" s="9" t="n"/>
       <c r="E562" s="9" t="n"/>
       <c r="F562" s="9" t="n"/>
@@ -8500,7 +8958,7 @@
     <row r="563">
       <c r="A563" s="9" t="n"/>
       <c r="B563" s="9" t="n"/>
-      <c r="C563" s="31" t="n"/>
+      <c r="C563" s="33" t="n"/>
       <c r="D563" s="9" t="n"/>
       <c r="E563" s="9" t="n"/>
       <c r="F563" s="9" t="n"/>
@@ -8509,7 +8967,7 @@
     <row r="564">
       <c r="A564" s="9" t="n"/>
       <c r="B564" s="9" t="n"/>
-      <c r="C564" s="31" t="n"/>
+      <c r="C564" s="33" t="n"/>
       <c r="D564" s="9" t="n"/>
       <c r="E564" s="9" t="n"/>
       <c r="F564" s="9" t="n"/>
@@ -8518,7 +8976,7 @@
     <row r="565">
       <c r="A565" s="9" t="n"/>
       <c r="B565" s="9" t="n"/>
-      <c r="C565" s="31" t="n"/>
+      <c r="C565" s="33" t="n"/>
       <c r="D565" s="9" t="n"/>
       <c r="E565" s="9" t="n"/>
       <c r="F565" s="9" t="n"/>
@@ -8527,7 +8985,7 @@
     <row r="566">
       <c r="A566" s="9" t="n"/>
       <c r="B566" s="9" t="n"/>
-      <c r="C566" s="31" t="n"/>
+      <c r="C566" s="33" t="n"/>
       <c r="D566" s="9" t="n"/>
       <c r="E566" s="9" t="n"/>
       <c r="F566" s="9" t="n"/>
@@ -8536,7 +8994,7 @@
     <row r="567">
       <c r="A567" s="9" t="n"/>
       <c r="B567" s="9" t="n"/>
-      <c r="C567" s="31" t="n"/>
+      <c r="C567" s="33" t="n"/>
       <c r="D567" s="9" t="n"/>
       <c r="E567" s="9" t="n"/>
       <c r="F567" s="9" t="n"/>
@@ -8545,7 +9003,7 @@
     <row r="568">
       <c r="A568" s="9" t="n"/>
       <c r="B568" s="9" t="n"/>
-      <c r="C568" s="31" t="n"/>
+      <c r="C568" s="33" t="n"/>
       <c r="D568" s="9" t="n"/>
       <c r="E568" s="9" t="n"/>
       <c r="F568" s="9" t="n"/>
@@ -8554,7 +9012,7 @@
     <row r="569">
       <c r="A569" s="9" t="n"/>
       <c r="B569" s="9" t="n"/>
-      <c r="C569" s="31" t="n"/>
+      <c r="C569" s="33" t="n"/>
       <c r="D569" s="9" t="n"/>
       <c r="E569" s="9" t="n"/>
       <c r="F569" s="9" t="n"/>
@@ -8563,7 +9021,7 @@
     <row r="570">
       <c r="A570" s="9" t="n"/>
       <c r="B570" s="9" t="n"/>
-      <c r="C570" s="31" t="n"/>
+      <c r="C570" s="33" t="n"/>
       <c r="D570" s="9" t="n"/>
       <c r="E570" s="9" t="n"/>
       <c r="F570" s="9" t="n"/>
@@ -8572,7 +9030,7 @@
     <row r="571">
       <c r="A571" s="9" t="n"/>
       <c r="B571" s="9" t="n"/>
-      <c r="C571" s="31" t="n"/>
+      <c r="C571" s="33" t="n"/>
       <c r="D571" s="9" t="n"/>
       <c r="E571" s="9" t="n"/>
       <c r="F571" s="9" t="n"/>
@@ -8581,7 +9039,7 @@
     <row r="572">
       <c r="A572" s="9" t="n"/>
       <c r="B572" s="9" t="n"/>
-      <c r="C572" s="31" t="n"/>
+      <c r="C572" s="33" t="n"/>
       <c r="D572" s="9" t="n"/>
       <c r="E572" s="9" t="n"/>
       <c r="F572" s="9" t="n"/>
@@ -8590,7 +9048,7 @@
     <row r="573">
       <c r="A573" s="9" t="n"/>
       <c r="B573" s="9" t="n"/>
-      <c r="C573" s="31" t="n"/>
+      <c r="C573" s="33" t="n"/>
       <c r="D573" s="9" t="n"/>
       <c r="E573" s="9" t="n"/>
       <c r="F573" s="9" t="n"/>
@@ -8599,7 +9057,7 @@
     <row r="574">
       <c r="A574" s="9" t="n"/>
       <c r="B574" s="9" t="n"/>
-      <c r="C574" s="31" t="n"/>
+      <c r="C574" s="33" t="n"/>
       <c r="D574" s="9" t="n"/>
       <c r="E574" s="9" t="n"/>
       <c r="F574" s="9" t="n"/>
@@ -8608,7 +9066,7 @@
     <row r="575">
       <c r="A575" s="9" t="n"/>
       <c r="B575" s="9" t="n"/>
-      <c r="C575" s="31" t="n"/>
+      <c r="C575" s="33" t="n"/>
       <c r="D575" s="9" t="n"/>
       <c r="E575" s="9" t="n"/>
       <c r="F575" s="9" t="n"/>
@@ -8617,7 +9075,7 @@
     <row r="576">
       <c r="A576" s="9" t="n"/>
       <c r="B576" s="9" t="n"/>
-      <c r="C576" s="31" t="n"/>
+      <c r="C576" s="33" t="n"/>
       <c r="D576" s="9" t="n"/>
       <c r="E576" s="9" t="n"/>
       <c r="F576" s="9" t="n"/>
@@ -8626,7 +9084,7 @@
     <row r="577">
       <c r="A577" s="9" t="n"/>
       <c r="B577" s="9" t="n"/>
-      <c r="C577" s="31" t="n"/>
+      <c r="C577" s="33" t="n"/>
       <c r="D577" s="9" t="n"/>
       <c r="E577" s="9" t="n"/>
       <c r="F577" s="9" t="n"/>
@@ -8635,7 +9093,7 @@
     <row r="578">
       <c r="A578" s="9" t="n"/>
       <c r="B578" s="9" t="n"/>
-      <c r="C578" s="31" t="n"/>
+      <c r="C578" s="33" t="n"/>
       <c r="D578" s="9" t="n"/>
       <c r="E578" s="9" t="n"/>
       <c r="F578" s="9" t="n"/>
@@ -8644,7 +9102,7 @@
     <row r="579">
       <c r="A579" s="9" t="n"/>
       <c r="B579" s="9" t="n"/>
-      <c r="C579" s="31" t="n"/>
+      <c r="C579" s="33" t="n"/>
       <c r="D579" s="9" t="n"/>
       <c r="E579" s="9" t="n"/>
       <c r="F579" s="9" t="n"/>
@@ -8653,7 +9111,7 @@
     <row r="580">
       <c r="A580" s="9" t="n"/>
       <c r="B580" s="9" t="n"/>
-      <c r="C580" s="31" t="n"/>
+      <c r="C580" s="33" t="n"/>
       <c r="D580" s="9" t="n"/>
       <c r="E580" s="9" t="n"/>
       <c r="F580" s="9" t="n"/>
@@ -8662,7 +9120,7 @@
     <row r="581">
       <c r="A581" s="9" t="n"/>
       <c r="B581" s="9" t="n"/>
-      <c r="C581" s="31" t="n"/>
+      <c r="C581" s="33" t="n"/>
       <c r="D581" s="9" t="n"/>
       <c r="E581" s="9" t="n"/>
       <c r="F581" s="9" t="n"/>
@@ -8671,7 +9129,7 @@
     <row r="582">
       <c r="A582" s="9" t="n"/>
       <c r="B582" s="9" t="n"/>
-      <c r="C582" s="31" t="n"/>
+      <c r="C582" s="33" t="n"/>
       <c r="D582" s="9" t="n"/>
       <c r="E582" s="9" t="n"/>
       <c r="F582" s="9" t="n"/>
@@ -8680,7 +9138,7 @@
     <row r="583">
       <c r="A583" s="9" t="n"/>
       <c r="B583" s="9" t="n"/>
-      <c r="C583" s="31" t="n"/>
+      <c r="C583" s="33" t="n"/>
       <c r="D583" s="9" t="n"/>
       <c r="E583" s="9" t="n"/>
       <c r="F583" s="9" t="n"/>
@@ -8689,7 +9147,7 @@
     <row r="584">
       <c r="A584" s="9" t="n"/>
       <c r="B584" s="9" t="n"/>
-      <c r="C584" s="31" t="n"/>
+      <c r="C584" s="33" t="n"/>
       <c r="D584" s="9" t="n"/>
       <c r="E584" s="9" t="n"/>
       <c r="F584" s="9" t="n"/>
@@ -8698,7 +9156,7 @@
     <row r="585">
       <c r="A585" s="9" t="n"/>
       <c r="B585" s="9" t="n"/>
-      <c r="C585" s="31" t="n"/>
+      <c r="C585" s="33" t="n"/>
       <c r="D585" s="9" t="n"/>
       <c r="E585" s="9" t="n"/>
       <c r="F585" s="9" t="n"/>
@@ -8707,7 +9165,7 @@
     <row r="586">
       <c r="A586" s="9" t="n"/>
       <c r="B586" s="9" t="n"/>
-      <c r="C586" s="31" t="n"/>
+      <c r="C586" s="33" t="n"/>
       <c r="D586" s="9" t="n"/>
       <c r="E586" s="9" t="n"/>
       <c r="F586" s="9" t="n"/>
@@ -8716,7 +9174,7 @@
     <row r="587">
       <c r="A587" s="9" t="n"/>
       <c r="B587" s="9" t="n"/>
-      <c r="C587" s="31" t="n"/>
+      <c r="C587" s="33" t="n"/>
       <c r="D587" s="9" t="n"/>
       <c r="E587" s="9" t="n"/>
       <c r="F587" s="9" t="n"/>
@@ -8725,7 +9183,7 @@
     <row r="588">
       <c r="A588" s="9" t="n"/>
       <c r="B588" s="9" t="n"/>
-      <c r="C588" s="31" t="n"/>
+      <c r="C588" s="33" t="n"/>
       <c r="D588" s="9" t="n"/>
       <c r="E588" s="9" t="n"/>
       <c r="F588" s="9" t="n"/>
@@ -8734,7 +9192,7 @@
     <row r="589">
       <c r="A589" s="9" t="n"/>
       <c r="B589" s="9" t="n"/>
-      <c r="C589" s="31" t="n"/>
+      <c r="C589" s="33" t="n"/>
       <c r="D589" s="9" t="n"/>
       <c r="E589" s="9" t="n"/>
       <c r="F589" s="9" t="n"/>
@@ -8743,7 +9201,7 @@
     <row r="590">
       <c r="A590" s="9" t="n"/>
       <c r="B590" s="9" t="n"/>
-      <c r="C590" s="31" t="n"/>
+      <c r="C590" s="33" t="n"/>
       <c r="D590" s="9" t="n"/>
       <c r="E590" s="9" t="n"/>
       <c r="F590" s="9" t="n"/>
@@ -8752,7 +9210,7 @@
     <row r="591">
       <c r="A591" s="9" t="n"/>
       <c r="B591" s="9" t="n"/>
-      <c r="C591" s="31" t="n"/>
+      <c r="C591" s="33" t="n"/>
       <c r="D591" s="9" t="n"/>
       <c r="E591" s="9" t="n"/>
       <c r="F591" s="9" t="n"/>
@@ -8761,7 +9219,7 @@
     <row r="592">
       <c r="A592" s="9" t="n"/>
       <c r="B592" s="9" t="n"/>
-      <c r="C592" s="31" t="n"/>
+      <c r="C592" s="33" t="n"/>
       <c r="D592" s="9" t="n"/>
       <c r="E592" s="9" t="n"/>
       <c r="F592" s="9" t="n"/>
@@ -8770,7 +9228,7 @@
     <row r="593">
       <c r="A593" s="9" t="n"/>
       <c r="B593" s="9" t="n"/>
-      <c r="C593" s="31" t="n"/>
+      <c r="C593" s="33" t="n"/>
       <c r="D593" s="9" t="n"/>
       <c r="E593" s="9" t="n"/>
       <c r="F593" s="9" t="n"/>
@@ -8779,7 +9237,7 @@
     <row r="594">
       <c r="A594" s="9" t="n"/>
       <c r="B594" s="9" t="n"/>
-      <c r="C594" s="31" t="n"/>
+      <c r="C594" s="33" t="n"/>
       <c r="D594" s="9" t="n"/>
       <c r="E594" s="9" t="n"/>
       <c r="F594" s="9" t="n"/>
@@ -8788,7 +9246,7 @@
     <row r="595">
       <c r="A595" s="9" t="n"/>
       <c r="B595" s="9" t="n"/>
-      <c r="C595" s="31" t="n"/>
+      <c r="C595" s="33" t="n"/>
       <c r="D595" s="9" t="n"/>
       <c r="E595" s="9" t="n"/>
       <c r="F595" s="9" t="n"/>
@@ -8797,7 +9255,7 @@
     <row r="596">
       <c r="A596" s="9" t="n"/>
       <c r="B596" s="9" t="n"/>
-      <c r="C596" s="31" t="n"/>
+      <c r="C596" s="33" t="n"/>
       <c r="D596" s="9" t="n"/>
       <c r="E596" s="9" t="n"/>
       <c r="F596" s="9" t="n"/>
@@ -8806,7 +9264,7 @@
     <row r="597">
       <c r="A597" s="9" t="n"/>
       <c r="B597" s="9" t="n"/>
-      <c r="C597" s="31" t="n"/>
+      <c r="C597" s="33" t="n"/>
       <c r="D597" s="9" t="n"/>
       <c r="E597" s="9" t="n"/>
       <c r="F597" s="9" t="n"/>
@@ -8815,7 +9273,7 @@
     <row r="598">
       <c r="A598" s="9" t="n"/>
       <c r="B598" s="9" t="n"/>
-      <c r="C598" s="31" t="n"/>
+      <c r="C598" s="33" t="n"/>
       <c r="D598" s="9" t="n"/>
       <c r="E598" s="9" t="n"/>
       <c r="F598" s="9" t="n"/>
@@ -8824,7 +9282,7 @@
     <row r="599">
       <c r="A599" s="9" t="n"/>
       <c r="B599" s="9" t="n"/>
-      <c r="C599" s="31" t="n"/>
+      <c r="C599" s="33" t="n"/>
       <c r="D599" s="9" t="n"/>
       <c r="E599" s="9" t="n"/>
       <c r="F599" s="9" t="n"/>
@@ -8833,7 +9291,7 @@
     <row r="600">
       <c r="A600" s="9" t="n"/>
       <c r="B600" s="9" t="n"/>
-      <c r="C600" s="31" t="n"/>
+      <c r="C600" s="33" t="n"/>
       <c r="D600" s="9" t="n"/>
       <c r="E600" s="9" t="n"/>
       <c r="F600" s="9" t="n"/>
@@ -8842,7 +9300,7 @@
     <row r="601">
       <c r="A601" s="9" t="n"/>
       <c r="B601" s="9" t="n"/>
-      <c r="C601" s="31" t="n"/>
+      <c r="C601" s="33" t="n"/>
       <c r="D601" s="9" t="n"/>
       <c r="E601" s="9" t="n"/>
       <c r="F601" s="9" t="n"/>
@@ -8851,7 +9309,7 @@
     <row r="602">
       <c r="A602" s="9" t="n"/>
       <c r="B602" s="9" t="n"/>
-      <c r="C602" s="31" t="n"/>
+      <c r="C602" s="33" t="n"/>
       <c r="D602" s="9" t="n"/>
       <c r="E602" s="9" t="n"/>
       <c r="F602" s="9" t="n"/>
@@ -8860,7 +9318,7 @@
     <row r="603">
       <c r="A603" s="9" t="n"/>
       <c r="B603" s="9" t="n"/>
-      <c r="C603" s="31" t="n"/>
+      <c r="C603" s="33" t="n"/>
       <c r="D603" s="9" t="n"/>
       <c r="E603" s="9" t="n"/>
       <c r="F603" s="9" t="n"/>
@@ -8869,7 +9327,7 @@
     <row r="604">
       <c r="A604" s="9" t="n"/>
       <c r="B604" s="9" t="n"/>
-      <c r="C604" s="31" t="n"/>
+      <c r="C604" s="33" t="n"/>
       <c r="D604" s="9" t="n"/>
       <c r="E604" s="9" t="n"/>
       <c r="F604" s="9" t="n"/>
@@ -8878,7 +9336,7 @@
     <row r="605">
       <c r="A605" s="9" t="n"/>
       <c r="B605" s="9" t="n"/>
-      <c r="C605" s="31" t="n"/>
+      <c r="C605" s="33" t="n"/>
       <c r="D605" s="9" t="n"/>
       <c r="E605" s="9" t="n"/>
       <c r="F605" s="9" t="n"/>
@@ -8887,7 +9345,7 @@
     <row r="606">
       <c r="A606" s="9" t="n"/>
       <c r="B606" s="9" t="n"/>
-      <c r="C606" s="31" t="n"/>
+      <c r="C606" s="33" t="n"/>
       <c r="D606" s="9" t="n"/>
       <c r="E606" s="9" t="n"/>
       <c r="F606" s="9" t="n"/>
@@ -8896,7 +9354,7 @@
     <row r="607">
       <c r="A607" s="9" t="n"/>
       <c r="B607" s="9" t="n"/>
-      <c r="C607" s="31" t="n"/>
+      <c r="C607" s="33" t="n"/>
       <c r="D607" s="9" t="n"/>
       <c r="E607" s="9" t="n"/>
       <c r="F607" s="9" t="n"/>
@@ -8905,7 +9363,7 @@
     <row r="608">
       <c r="A608" s="9" t="n"/>
       <c r="B608" s="9" t="n"/>
-      <c r="C608" s="31" t="n"/>
+      <c r="C608" s="33" t="n"/>
       <c r="D608" s="9" t="n"/>
       <c r="E608" s="9" t="n"/>
       <c r="F608" s="9" t="n"/>
@@ -8914,7 +9372,7 @@
     <row r="609">
       <c r="A609" s="9" t="n"/>
       <c r="B609" s="9" t="n"/>
-      <c r="C609" s="31" t="n"/>
+      <c r="C609" s="33" t="n"/>
       <c r="D609" s="9" t="n"/>
       <c r="E609" s="9" t="n"/>
       <c r="F609" s="9" t="n"/>
@@ -8923,7 +9381,7 @@
     <row r="610">
       <c r="A610" s="9" t="n"/>
       <c r="B610" s="9" t="n"/>
-      <c r="C610" s="31" t="n"/>
+      <c r="C610" s="33" t="n"/>
       <c r="D610" s="9" t="n"/>
       <c r="E610" s="9" t="n"/>
       <c r="F610" s="9" t="n"/>
@@ -8932,7 +9390,7 @@
     <row r="611">
       <c r="A611" s="9" t="n"/>
       <c r="B611" s="9" t="n"/>
-      <c r="C611" s="31" t="n"/>
+      <c r="C611" s="33" t="n"/>
       <c r="D611" s="9" t="n"/>
       <c r="E611" s="9" t="n"/>
       <c r="F611" s="9" t="n"/>
@@ -8941,7 +9399,7 @@
     <row r="612">
       <c r="A612" s="9" t="n"/>
       <c r="B612" s="9" t="n"/>
-      <c r="C612" s="31" t="n"/>
+      <c r="C612" s="33" t="n"/>
       <c r="D612" s="9" t="n"/>
       <c r="E612" s="9" t="n"/>
       <c r="F612" s="9" t="n"/>
@@ -8950,7 +9408,7 @@
     <row r="613">
       <c r="A613" s="9" t="n"/>
       <c r="B613" s="9" t="n"/>
-      <c r="C613" s="31" t="n"/>
+      <c r="C613" s="33" t="n"/>
       <c r="D613" s="9" t="n"/>
       <c r="E613" s="9" t="n"/>
       <c r="F613" s="9" t="n"/>
@@ -8959,7 +9417,7 @@
     <row r="614">
       <c r="A614" s="9" t="n"/>
       <c r="B614" s="9" t="n"/>
-      <c r="C614" s="31" t="n"/>
+      <c r="C614" s="33" t="n"/>
       <c r="D614" s="9" t="n"/>
       <c r="E614" s="9" t="n"/>
       <c r="F614" s="9" t="n"/>
@@ -8968,7 +9426,7 @@
     <row r="615">
       <c r="A615" s="9" t="n"/>
       <c r="B615" s="9" t="n"/>
-      <c r="C615" s="31" t="n"/>
+      <c r="C615" s="33" t="n"/>
       <c r="D615" s="9" t="n"/>
       <c r="E615" s="9" t="n"/>
       <c r="F615" s="9" t="n"/>
@@ -8977,7 +9435,7 @@
     <row r="616">
       <c r="A616" s="9" t="n"/>
       <c r="B616" s="9" t="n"/>
-      <c r="C616" s="31" t="n"/>
+      <c r="C616" s="33" t="n"/>
       <c r="D616" s="9" t="n"/>
       <c r="E616" s="9" t="n"/>
       <c r="F616" s="9" t="n"/>
@@ -8986,7 +9444,7 @@
     <row r="617">
       <c r="A617" s="9" t="n"/>
       <c r="B617" s="9" t="n"/>
-      <c r="C617" s="31" t="n"/>
+      <c r="C617" s="33" t="n"/>
       <c r="D617" s="9" t="n"/>
       <c r="E617" s="9" t="n"/>
       <c r="F617" s="9" t="n"/>
@@ -8995,7 +9453,7 @@
     <row r="618">
       <c r="A618" s="9" t="n"/>
       <c r="B618" s="9" t="n"/>
-      <c r="C618" s="31" t="n"/>
+      <c r="C618" s="33" t="n"/>
       <c r="D618" s="9" t="n"/>
       <c r="E618" s="9" t="n"/>
       <c r="F618" s="9" t="n"/>
@@ -9004,7 +9462,7 @@
     <row r="619">
       <c r="A619" s="9" t="n"/>
       <c r="B619" s="9" t="n"/>
-      <c r="C619" s="31" t="n"/>
+      <c r="C619" s="33" t="n"/>
       <c r="D619" s="9" t="n"/>
       <c r="E619" s="9" t="n"/>
       <c r="F619" s="9" t="n"/>
@@ -9013,7 +9471,7 @@
     <row r="620">
       <c r="A620" s="9" t="n"/>
       <c r="B620" s="9" t="n"/>
-      <c r="C620" s="31" t="n"/>
+      <c r="C620" s="33" t="n"/>
       <c r="D620" s="9" t="n"/>
       <c r="E620" s="9" t="n"/>
       <c r="F620" s="9" t="n"/>
@@ -9022,7 +9480,7 @@
     <row r="621">
       <c r="A621" s="9" t="n"/>
       <c r="B621" s="9" t="n"/>
-      <c r="C621" s="31" t="n"/>
+      <c r="C621" s="33" t="n"/>
       <c r="D621" s="9" t="n"/>
       <c r="E621" s="9" t="n"/>
       <c r="F621" s="9" t="n"/>
@@ -9031,7 +9489,7 @@
     <row r="622">
       <c r="A622" s="9" t="n"/>
       <c r="B622" s="9" t="n"/>
-      <c r="C622" s="31" t="n"/>
+      <c r="C622" s="33" t="n"/>
       <c r="D622" s="9" t="n"/>
       <c r="E622" s="9" t="n"/>
       <c r="F622" s="9" t="n"/>
@@ -9040,7 +9498,7 @@
     <row r="623">
       <c r="A623" s="9" t="n"/>
       <c r="B623" s="9" t="n"/>
-      <c r="C623" s="31" t="n"/>
+      <c r="C623" s="33" t="n"/>
       <c r="D623" s="9" t="n"/>
       <c r="E623" s="9" t="n"/>
       <c r="F623" s="9" t="n"/>
@@ -9049,7 +9507,7 @@
     <row r="624">
       <c r="A624" s="9" t="n"/>
       <c r="B624" s="9" t="n"/>
-      <c r="C624" s="31" t="n"/>
+      <c r="C624" s="33" t="n"/>
       <c r="D624" s="9" t="n"/>
       <c r="E624" s="9" t="n"/>
       <c r="F624" s="9" t="n"/>
@@ -9058,7 +9516,7 @@
     <row r="625">
       <c r="A625" s="9" t="n"/>
       <c r="B625" s="9" t="n"/>
-      <c r="C625" s="31" t="n"/>
+      <c r="C625" s="33" t="n"/>
       <c r="D625" s="9" t="n"/>
       <c r="E625" s="9" t="n"/>
       <c r="F625" s="9" t="n"/>
@@ -9067,7 +9525,7 @@
     <row r="626">
       <c r="A626" s="9" t="n"/>
       <c r="B626" s="9" t="n"/>
-      <c r="C626" s="31" t="n"/>
+      <c r="C626" s="33" t="n"/>
       <c r="D626" s="9" t="n"/>
       <c r="E626" s="9" t="n"/>
       <c r="F626" s="9" t="n"/>
@@ -9076,7 +9534,7 @@
     <row r="627">
       <c r="A627" s="9" t="n"/>
       <c r="B627" s="9" t="n"/>
-      <c r="C627" s="31" t="n"/>
+      <c r="C627" s="33" t="n"/>
       <c r="D627" s="9" t="n"/>
       <c r="E627" s="9" t="n"/>
       <c r="F627" s="9" t="n"/>
@@ -9085,7 +9543,7 @@
     <row r="628">
       <c r="A628" s="9" t="n"/>
       <c r="B628" s="9" t="n"/>
-      <c r="C628" s="31" t="n"/>
+      <c r="C628" s="33" t="n"/>
       <c r="D628" s="9" t="n"/>
       <c r="E628" s="9" t="n"/>
       <c r="F628" s="9" t="n"/>
@@ -9094,7 +9552,7 @@
     <row r="629">
       <c r="A629" s="9" t="n"/>
       <c r="B629" s="9" t="n"/>
-      <c r="C629" s="31" t="n"/>
+      <c r="C629" s="33" t="n"/>
       <c r="D629" s="9" t="n"/>
       <c r="E629" s="9" t="n"/>
       <c r="F629" s="9" t="n"/>
@@ -9103,7 +9561,7 @@
     <row r="630">
       <c r="A630" s="9" t="n"/>
       <c r="B630" s="9" t="n"/>
-      <c r="C630" s="31" t="n"/>
+      <c r="C630" s="33" t="n"/>
       <c r="D630" s="9" t="n"/>
       <c r="E630" s="9" t="n"/>
       <c r="F630" s="9" t="n"/>
@@ -9112,7 +9570,7 @@
     <row r="631">
       <c r="A631" s="9" t="n"/>
       <c r="B631" s="9" t="n"/>
-      <c r="C631" s="31" t="n"/>
+      <c r="C631" s="33" t="n"/>
       <c r="D631" s="9" t="n"/>
       <c r="E631" s="9" t="n"/>
       <c r="F631" s="9" t="n"/>
@@ -9121,7 +9579,7 @@
     <row r="632">
       <c r="A632" s="9" t="n"/>
       <c r="B632" s="9" t="n"/>
-      <c r="C632" s="31" t="n"/>
+      <c r="C632" s="33" t="n"/>
       <c r="D632" s="9" t="n"/>
       <c r="E632" s="9" t="n"/>
       <c r="F632" s="9" t="n"/>
@@ -9130,7 +9588,7 @@
     <row r="633">
       <c r="A633" s="9" t="n"/>
       <c r="B633" s="9" t="n"/>
-      <c r="C633" s="31" t="n"/>
+      <c r="C633" s="33" t="n"/>
       <c r="D633" s="9" t="n"/>
       <c r="E633" s="9" t="n"/>
       <c r="F633" s="9" t="n"/>
@@ -9224,37 +9682,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>EXAMPLE: rewrote 4 product pages</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>EXAMPLE: clicks on those pages up in week 3, too early to call</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>EXAMPLE: add FAQ sections to the ten highest-traffic pages</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>EXAMPLE: Sam</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>EXAMPLE: more non-branded clicks on question queries</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>planned</t>
         </is>
@@ -9416,7 +9874,7 @@
         <f>'1 Scorecard'!E13</f>
         <v/>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>EXAMPLE: up on last month, held back by lost seasonal blog traffic</t>
         </is>
@@ -9436,7 +9894,7 @@
         <f>'1 Scorecard'!E14</f>
         <v/>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>EXAMPLE: two rewritten product pages reached the top 3</t>
         </is>
@@ -9456,7 +9914,7 @@
         <f>'1 Scorecard'!E19</f>
         <v/>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>EXAMPLE: the growth came from non-branded queries</t>
         </is>
@@ -9476,7 +9934,7 @@
         <f>'1 Scorecard'!E23</f>
         <v/>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>EXAMPLE: a small base, up from 31 to 42 sessions</t>
         </is>
@@ -9488,7 +9946,7 @@
           <t>Prompt panel: citation rate (all engines)</t>
         </is>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="31">
         <f>'5 AI Visibility'!D29</f>
         <v/>
       </c>
@@ -9496,7 +9954,7 @@
         <f>IFERROR(('5 AI Visibility'!D29-'5 AI Visibility'!F29)*100,"n/a")</f>
         <v/>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>EXAMPLE: too few logged runs to read a trend yet</t>
         </is>
@@ -9508,7 +9966,7 @@
           <t>Biggest risk this month</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>EXAMPLE: click-through fell on the pages where an AI answer now appears</t>
         </is>
@@ -9520,7 +9978,7 @@
           <t>Decision we need from you</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>EXAMPLE: approve adding FAQ sections to the ten highest-traffic pages</t>
         </is>
